--- a/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
@@ -18,7 +18,7 @@
     <t>PROGRES PEMUTAKHIRAN KELUARGA - KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 5 Sep 2026, 06.16 | Dicetak: 5 Sep 2026, 06.50</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 6 Sep 2026, 06.16 | Dicetak: 6 Sep 2026, 07.43</t>
   </si>
   <si>
     <t>Kode</t>
@@ -123,7 +123,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>74,05</t>
+    <t>74,24</t>
   </si>
   <si>
     <t>1,87</t>
@@ -132,13 +132,13 @@
     <t>0,07</t>
   </si>
   <si>
-    <t>22,9</t>
+    <t>22,91</t>
   </si>
   <si>
     <t>0,19</t>
   </si>
   <si>
-    <t>87,31</t>
+    <t>87,56</t>
   </si>
   <si>
     <t>1801</t>
@@ -171,7 +171,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>79,12</t>
+    <t>79,38</t>
   </si>
   <si>
     <t>1,06</t>
@@ -183,7 +183,7 @@
     <t>19,11</t>
   </si>
   <si>
-    <t>96,8</t>
+    <t>97,14</t>
   </si>
   <si>
     <t>1803</t>
@@ -192,7 +192,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>73,49</t>
+    <t>73,93</t>
   </si>
   <si>
     <t>1,31</t>
@@ -201,13 +201,13 @@
     <t>0,06</t>
   </si>
   <si>
-    <t>22,84</t>
+    <t>22,89</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>88,34</t>
+    <t>88,86</t>
   </si>
   <si>
     <t>1804</t>
@@ -216,7 +216,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>77,27</t>
+    <t>77,38</t>
   </si>
   <si>
     <t>1,98</t>
@@ -228,7 +228,7 @@
     <t>0,15</t>
   </si>
   <si>
-    <t>87,7</t>
+    <t>87,84</t>
   </si>
   <si>
     <t>1805</t>
@@ -237,7 +237,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>76,16</t>
+    <t>76,24</t>
   </si>
   <si>
     <t>2,86</t>
@@ -246,13 +246,13 @@
     <t>0,09</t>
   </si>
   <si>
-    <t>20,07</t>
+    <t>20,08</t>
   </si>
   <si>
     <t>0,34</t>
   </si>
   <si>
-    <t>86,35</t>
+    <t>86,46</t>
   </si>
   <si>
     <t>1806</t>
@@ -279,7 +279,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>77,8</t>
+    <t>77,95</t>
   </si>
   <si>
     <t>1,78</t>
@@ -288,7 +288,10 @@
     <t>19,69</t>
   </si>
   <si>
-    <t>91,78</t>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>91,97</t>
   </si>
   <si>
     <t>1808</t>
@@ -297,7 +300,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>70,1</t>
+    <t>70,27</t>
   </si>
   <si>
     <t>2,31</t>
@@ -309,7 +312,7 @@
     <t>27,63</t>
   </si>
   <si>
-    <t>84,12</t>
+    <t>84,36</t>
   </si>
   <si>
     <t>1809</t>
@@ -318,16 +321,16 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>75,59</t>
+    <t>75,65</t>
   </si>
   <si>
     <t>3,06</t>
   </si>
   <si>
-    <t>21,76</t>
-  </si>
-  <si>
-    <t>90,41</t>
+    <t>21,71</t>
+  </si>
+  <si>
+    <t>90,56</t>
   </si>
   <si>
     <t>1810</t>
@@ -336,7 +339,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>81,17</t>
+    <t>81,22</t>
   </si>
   <si>
     <t>1,53</t>
@@ -345,13 +348,13 @@
     <t>0,08</t>
   </si>
   <si>
-    <t>17,43</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>91,81</t>
+    <t>17,39</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>91,91</t>
   </si>
   <si>
     <t>1811</t>
@@ -366,10 +369,10 @@
     <t>1,58</t>
   </si>
   <si>
-    <t>24,59</t>
-  </si>
-  <si>
-    <t>91,53</t>
+    <t>24,57</t>
+  </si>
+  <si>
+    <t>91,56</t>
   </si>
   <si>
     <t>1812</t>
@@ -378,19 +381,16 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>74,72</t>
-  </si>
-  <si>
-    <t>2,41</t>
-  </si>
-  <si>
-    <t>23,01</t>
+    <t>2,42</t>
+  </si>
+  <si>
+    <t>22,98</t>
   </si>
   <si>
     <t>0,28</t>
   </si>
   <si>
-    <t>87,83</t>
+    <t>87,87</t>
   </si>
   <si>
     <t>1813</t>
@@ -405,10 +405,10 @@
     <t>0,85</t>
   </si>
   <si>
-    <t>17,07</t>
-  </si>
-  <si>
-    <t>101,76</t>
+    <t>17,06</t>
+  </si>
+  <si>
+    <t>101,8</t>
   </si>
   <si>
     <t>1871</t>
@@ -417,16 +417,16 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>58,1</t>
+    <t>58,69</t>
   </si>
   <si>
     <t>0,95</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>73,9</t>
+    <t>35,16</t>
+  </si>
+  <si>
+    <t>74,68</t>
   </si>
   <si>
     <t>1872</t>
@@ -435,19 +435,19 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>73,44</t>
-  </si>
-  <si>
-    <t>1,52</t>
-  </si>
-  <si>
-    <t>24,19</t>
+    <t>73,69</t>
+  </si>
+  <si>
+    <t>1,51</t>
+  </si>
+  <si>
+    <t>24,11</t>
   </si>
   <si>
     <t>0,04</t>
   </si>
   <si>
-    <t>85,29</t>
+    <t>85,67</t>
   </si>
   <si>
     <t/>
@@ -489,37 +489,37 @@
     <t>Jumlah Bangunan Keluarga Khusus Berpindah-pindah Didata (K2)</t>
   </si>
   <si>
-    <t>42,99</t>
+    <t>42,81</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>16,39</t>
-  </si>
-  <si>
-    <t>34,27</t>
+    <t>15,15</t>
+  </si>
+  <si>
+    <t>33,52</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>49,54</t>
+    <t>48,42</t>
   </si>
   <si>
     <t>78,43</t>
   </si>
   <si>
-    <t>25,33</t>
-  </si>
-  <si>
-    <t>15,69</t>
-  </si>
-  <si>
-    <t>78,29</t>
-  </si>
-  <si>
-    <t>28,41</t>
+    <t>25,68</t>
+  </si>
+  <si>
+    <t>15,84</t>
+  </si>
+  <si>
+    <t>79,61</t>
+  </si>
+  <si>
+    <t>28,74</t>
   </si>
   <si>
     <t>70,37</t>
@@ -531,7 +531,7 @@
     <t>75</t>
   </si>
   <si>
-    <t>11,84</t>
+    <t>12,34</t>
   </si>
   <si>
     <t>87,18</t>
@@ -1195,40 +1195,40 @@
         <v>2730939</v>
       </c>
       <c r="D6" s="6">
-        <v>2022354</v>
+        <v>2027507</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="6">
-        <v>362097</v>
+        <v>363702</v>
       </c>
       <c r="G6" s="6">
-        <v>51129</v>
+        <v>51157</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="6">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="6">
-        <v>625307</v>
+        <v>625692</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="6">
-        <v>5173</v>
+        <v>5251</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="6">
-        <v>2384451</v>
+        <v>2391209</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>41</v>
@@ -1295,13 +1295,13 @@
         <v>172957</v>
       </c>
       <c r="D8" s="9">
-        <v>136843</v>
+        <v>137297</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="9">
-        <v>30584</v>
+        <v>30718</v>
       </c>
       <c r="G8" s="9">
         <v>1834</v>
@@ -1316,19 +1316,19 @@
         <v>54</v>
       </c>
       <c r="K8" s="9">
-        <v>33052</v>
+        <v>33060</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>55</v>
       </c>
       <c r="M8" s="9">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N8" s="10" t="s">
         <v>40</v>
       </c>
       <c r="O8" s="9">
-        <v>167427</v>
+        <v>168015</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>56</v>
@@ -1345,16 +1345,16 @@
         <v>342736</v>
       </c>
       <c r="D9" s="9">
-        <v>251893</v>
+        <v>253394</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F9" s="9">
-        <v>50897</v>
+        <v>51152</v>
       </c>
       <c r="G9" s="9">
-        <v>4500</v>
+        <v>4505</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>60</v>
@@ -1366,19 +1366,19 @@
         <v>61</v>
       </c>
       <c r="K9" s="9">
-        <v>78269</v>
+        <v>78453</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>62</v>
       </c>
       <c r="M9" s="9">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>63</v>
       </c>
       <c r="O9" s="9">
-        <v>302790</v>
+        <v>304546</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>64</v>
@@ -1395,13 +1395,13 @@
         <v>362841</v>
       </c>
       <c r="D10" s="9">
-        <v>280354</v>
+        <v>280749</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>67</v>
       </c>
       <c r="F10" s="9">
-        <v>37865</v>
+        <v>37982</v>
       </c>
       <c r="G10" s="9">
         <v>7195</v>
@@ -1416,19 +1416,19 @@
         <v>61</v>
       </c>
       <c r="K10" s="9">
-        <v>72583</v>
+        <v>72560</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>69</v>
       </c>
       <c r="M10" s="9">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="N10" s="10" t="s">
         <v>70</v>
       </c>
       <c r="O10" s="9">
-        <v>318219</v>
+        <v>318731</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>71</v>
@@ -1445,40 +1445,40 @@
         <v>449576</v>
       </c>
       <c r="D11" s="9">
-        <v>342380</v>
+        <v>342778</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F11" s="9">
-        <v>45833</v>
+        <v>45923</v>
       </c>
       <c r="G11" s="9">
-        <v>12844</v>
+        <v>12847</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I11" s="9">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>76</v>
       </c>
       <c r="K11" s="9">
-        <v>90239</v>
+        <v>90262</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>77</v>
       </c>
       <c r="M11" s="9">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>78</v>
       </c>
       <c r="O11" s="9">
-        <v>388213</v>
+        <v>388701</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>79</v>
@@ -1495,13 +1495,13 @@
         <v>199396</v>
       </c>
       <c r="D12" s="9">
-        <v>141606</v>
+        <v>141607</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>82</v>
       </c>
       <c r="F12" s="9">
-        <v>25384</v>
+        <v>25389</v>
       </c>
       <c r="G12" s="9">
         <v>3930</v>
@@ -1516,7 +1516,7 @@
         <v>46</v>
       </c>
       <c r="K12" s="9">
-        <v>53513</v>
+        <v>53512</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>84</v>
@@ -1528,7 +1528,7 @@
         <v>70</v>
       </c>
       <c r="O12" s="9">
-        <v>166990</v>
+        <v>166996</v>
       </c>
       <c r="P12" s="10" t="s">
         <v>85</v>
@@ -1545,16 +1545,16 @@
         <v>146092</v>
       </c>
       <c r="D13" s="9">
-        <v>113658</v>
+        <v>113875</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>88</v>
       </c>
       <c r="F13" s="9">
-        <v>20418</v>
+        <v>20491</v>
       </c>
       <c r="G13" s="9">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>89</v>
@@ -1566,98 +1566,98 @@
         <v>38</v>
       </c>
       <c r="K13" s="9">
-        <v>28769</v>
+        <v>28764</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>90</v>
       </c>
       <c r="M13" s="9">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="O13" s="9">
-        <v>134076</v>
+        <v>134366</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="9">
         <v>135256</v>
       </c>
       <c r="D14" s="9">
-        <v>94820</v>
+        <v>95043</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F14" s="9">
-        <v>18962</v>
+        <v>19055</v>
       </c>
       <c r="G14" s="9">
         <v>3131</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I14" s="9">
         <v>33</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K14" s="9">
-        <v>37366</v>
+        <v>37367</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M14" s="9">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N14" s="10" t="s">
         <v>54</v>
       </c>
       <c r="O14" s="9">
-        <v>113782</v>
+        <v>114098</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="9">
         <v>152158</v>
       </c>
       <c r="D15" s="9">
-        <v>115014</v>
+        <v>115115</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F15" s="9">
-        <v>22557</v>
+        <v>22673</v>
       </c>
       <c r="G15" s="9">
         <v>4661</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I15" s="9">
         <v>72</v>
@@ -1666,110 +1666,110 @@
         <v>54</v>
       </c>
       <c r="K15" s="9">
-        <v>33113</v>
+        <v>33026</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M15" s="9">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N15" s="10" t="s">
         <v>76</v>
       </c>
       <c r="O15" s="9">
-        <v>137571</v>
+        <v>137788</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="9">
         <v>135741</v>
       </c>
       <c r="D16" s="9">
-        <v>110187</v>
+        <v>110247</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F16" s="9">
-        <v>14443</v>
+        <v>14511</v>
       </c>
       <c r="G16" s="9">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I16" s="9">
         <v>110</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K16" s="9">
-        <v>23661</v>
+        <v>23603</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M16" s="9">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O16" s="9">
-        <v>124630</v>
+        <v>124758</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" s="9">
         <v>75116</v>
       </c>
       <c r="D17" s="9">
-        <v>56140</v>
+        <v>56141</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F17" s="9">
-        <v>12616</v>
+        <v>12636</v>
       </c>
       <c r="G17" s="9">
         <v>1187</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I17" s="9">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>40</v>
       </c>
       <c r="K17" s="9">
-        <v>18468</v>
+        <v>18459</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M17" s="9">
         <v>35</v>
@@ -1778,33 +1778,33 @@
         <v>54</v>
       </c>
       <c r="O17" s="9">
-        <v>68756</v>
+        <v>68777</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="9">
         <v>99169</v>
       </c>
       <c r="D18" s="9">
-        <v>74097</v>
+        <v>74115</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F18" s="9">
-        <v>13006</v>
+        <v>13024</v>
       </c>
       <c r="G18" s="9">
-        <v>2387</v>
+        <v>2396</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>122</v>
@@ -1816,19 +1816,19 @@
         <v>54</v>
       </c>
       <c r="K18" s="9">
-        <v>22823</v>
+        <v>22792</v>
       </c>
       <c r="L18" s="10" t="s">
         <v>123</v>
       </c>
       <c r="M18" s="9">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N18" s="10" t="s">
         <v>124</v>
       </c>
       <c r="O18" s="9">
-        <v>87103</v>
+        <v>87139</v>
       </c>
       <c r="P18" s="10" t="s">
         <v>125</v>
@@ -1845,13 +1845,13 @@
         <v>41772</v>
       </c>
       <c r="D19" s="9">
-        <v>34632</v>
+        <v>34633</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>128</v>
       </c>
       <c r="F19" s="9">
-        <v>7874</v>
+        <v>7891</v>
       </c>
       <c r="G19" s="9">
         <v>357</v>
@@ -1866,7 +1866,7 @@
         <v>61</v>
       </c>
       <c r="K19" s="9">
-        <v>7130</v>
+        <v>7128</v>
       </c>
       <c r="L19" s="10" t="s">
         <v>130</v>
@@ -1878,7 +1878,7 @@
         <v>38</v>
       </c>
       <c r="O19" s="9">
-        <v>42506</v>
+        <v>42524</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>131</v>
@@ -1895,40 +1895,40 @@
         <v>279478</v>
       </c>
       <c r="D20" s="9">
-        <v>162386</v>
+        <v>164039</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>134</v>
       </c>
       <c r="F20" s="9">
-        <v>44140</v>
+        <v>44665</v>
       </c>
       <c r="G20" s="9">
-        <v>2654</v>
+        <v>2664</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>135</v>
       </c>
       <c r="I20" s="9">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>61</v>
       </c>
       <c r="K20" s="9">
-        <v>97828</v>
+        <v>98256</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>136</v>
       </c>
       <c r="M20" s="9">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="O20" s="9">
-        <v>206526</v>
+        <v>208704</v>
       </c>
       <c r="P20" s="10" t="s">
         <v>137</v>
@@ -1945,16 +1945,16 @@
         <v>53506</v>
       </c>
       <c r="D21" s="9">
-        <v>39297</v>
+        <v>39427</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>140</v>
       </c>
       <c r="F21" s="9">
-        <v>6339</v>
+        <v>6413</v>
       </c>
       <c r="G21" s="9">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>141</v>
@@ -1966,7 +1966,7 @@
         <v>48</v>
       </c>
       <c r="K21" s="9">
-        <v>12944</v>
+        <v>12901</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>142</v>
@@ -1978,7 +1978,7 @@
         <v>143</v>
       </c>
       <c r="O21" s="9">
-        <v>45636</v>
+        <v>45840</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>144</v>
@@ -1995,40 +1995,40 @@
         <v>2730939</v>
       </c>
       <c r="D22" s="12">
-        <v>2022354</v>
+        <v>2027507</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="12">
-        <v>362097</v>
+        <v>363702</v>
       </c>
       <c r="G22" s="12">
-        <v>51129</v>
+        <v>51157</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="12">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="12">
-        <v>625307</v>
+        <v>625692</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="12">
-        <v>5173</v>
+        <v>5251</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="O22" s="12">
-        <v>2384451</v>
+        <v>2391209</v>
       </c>
       <c r="P22" s="13" t="s">
         <v>41</v>
@@ -2147,25 +2147,25 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>7184751</v>
+        <v>7198360</v>
       </c>
       <c r="D6" s="6">
-        <v>117648</v>
+        <v>117680</v>
       </c>
       <c r="E6" s="6">
-        <v>76726</v>
+        <v>76827</v>
       </c>
       <c r="F6" s="6">
-        <v>380969</v>
+        <v>381520</v>
       </c>
       <c r="G6" s="6">
-        <v>62670</v>
+        <v>62737</v>
       </c>
       <c r="H6" s="6">
         <v>9848</v>
       </c>
       <c r="I6" s="6">
-        <v>7302399</v>
+        <v>7316040</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2205,25 +2205,25 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>512440</v>
+        <v>513636</v>
       </c>
       <c r="D8" s="9">
-        <v>6541</v>
+        <v>6552</v>
       </c>
       <c r="E8" s="9">
-        <v>4981</v>
+        <v>4989</v>
       </c>
       <c r="F8" s="9">
-        <v>38621</v>
+        <v>38683</v>
       </c>
       <c r="G8" s="9">
-        <v>4537</v>
+        <v>4544</v>
       </c>
       <c r="H8" s="9">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="I8" s="9">
-        <v>518981</v>
+        <v>520188</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2234,25 +2234,25 @@
         <v>58</v>
       </c>
       <c r="C9" s="9">
-        <v>928086</v>
+        <v>931545</v>
       </c>
       <c r="D9" s="9">
-        <v>15292</v>
+        <v>15317</v>
       </c>
       <c r="E9" s="9">
-        <v>10457</v>
+        <v>10484</v>
       </c>
       <c r="F9" s="9">
-        <v>44518</v>
+        <v>44652</v>
       </c>
       <c r="G9" s="9">
-        <v>5511</v>
+        <v>5519</v>
       </c>
       <c r="H9" s="9">
         <v>1134</v>
       </c>
       <c r="I9" s="9">
-        <v>943378</v>
+        <v>946862</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2263,25 +2263,25 @@
         <v>66</v>
       </c>
       <c r="C10" s="9">
-        <v>903779</v>
+        <v>904783</v>
       </c>
       <c r="D10" s="9">
-        <v>16613</v>
+        <v>16620</v>
       </c>
       <c r="E10" s="9">
-        <v>10619</v>
+        <v>10633</v>
       </c>
       <c r="F10" s="9">
-        <v>43929</v>
+        <v>43968</v>
       </c>
       <c r="G10" s="9">
-        <v>22568</v>
+        <v>22590</v>
       </c>
       <c r="H10" s="9">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="I10" s="9">
-        <v>920392</v>
+        <v>921403</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2292,25 +2292,25 @@
         <v>73</v>
       </c>
       <c r="C11" s="9">
-        <v>1137978</v>
+        <v>1138845</v>
       </c>
       <c r="D11" s="9">
-        <v>21576</v>
+        <v>21585</v>
       </c>
       <c r="E11" s="9">
-        <v>13404</v>
+        <v>13415</v>
       </c>
       <c r="F11" s="9">
-        <v>50366</v>
+        <v>50406</v>
       </c>
       <c r="G11" s="9">
-        <v>9051</v>
+        <v>9056</v>
       </c>
       <c r="H11" s="9">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="I11" s="9">
-        <v>1159554</v>
+        <v>1160430</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2321,7 +2321,7 @@
         <v>81</v>
       </c>
       <c r="C12" s="9">
-        <v>518743</v>
+        <v>518747</v>
       </c>
       <c r="D12" s="9">
         <v>6353</v>
@@ -2330,7 +2330,7 @@
         <v>6168</v>
       </c>
       <c r="F12" s="9">
-        <v>29365</v>
+        <v>29369</v>
       </c>
       <c r="G12" s="9">
         <v>2071</v>
@@ -2339,7 +2339,7 @@
         <v>521</v>
       </c>
       <c r="I12" s="9">
-        <v>525096</v>
+        <v>525100</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2350,170 +2350,170 @@
         <v>87</v>
       </c>
       <c r="C13" s="9">
-        <v>402993</v>
+        <v>403509</v>
       </c>
       <c r="D13" s="9">
-        <v>4797</v>
+        <v>4794</v>
       </c>
       <c r="E13" s="9">
-        <v>4508</v>
+        <v>4513</v>
       </c>
       <c r="F13" s="9">
-        <v>28862</v>
+        <v>28925</v>
       </c>
       <c r="G13" s="9">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="H13" s="9">
         <v>489</v>
       </c>
       <c r="I13" s="9">
-        <v>407790</v>
+        <v>408303</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="9">
-        <v>338681</v>
+        <v>339410</v>
       </c>
       <c r="D14" s="9">
-        <v>9533</v>
+        <v>9540</v>
       </c>
       <c r="E14" s="9">
-        <v>3670</v>
+        <v>3675</v>
       </c>
       <c r="F14" s="9">
-        <v>22478</v>
+        <v>22524</v>
       </c>
       <c r="G14" s="9">
-        <v>2226</v>
+        <v>2230</v>
       </c>
       <c r="H14" s="9">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I14" s="9">
-        <v>348214</v>
+        <v>348950</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="9">
-        <v>415332</v>
+        <v>415631</v>
       </c>
       <c r="D15" s="9">
-        <v>7899</v>
+        <v>7900</v>
       </c>
       <c r="E15" s="9">
-        <v>6732</v>
+        <v>6736</v>
       </c>
       <c r="F15" s="9">
-        <v>28039</v>
+        <v>28067</v>
       </c>
       <c r="G15" s="9">
-        <v>4047</v>
+        <v>4054</v>
       </c>
       <c r="H15" s="9">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I15" s="9">
-        <v>423231</v>
+        <v>423531</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="9">
-        <v>369299</v>
+        <v>369523</v>
       </c>
       <c r="D16" s="9">
-        <v>5202</v>
+        <v>5156</v>
       </c>
       <c r="E16" s="9">
         <v>3205</v>
       </c>
       <c r="F16" s="9">
-        <v>21252</v>
+        <v>21263</v>
       </c>
       <c r="G16" s="9">
-        <v>4284</v>
+        <v>4288</v>
       </c>
       <c r="H16" s="9">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I16" s="9">
-        <v>374501</v>
+        <v>374679</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" s="9">
-        <v>199229</v>
+        <v>199285</v>
       </c>
       <c r="D17" s="9">
         <v>4868</v>
       </c>
       <c r="E17" s="9">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="F17" s="9">
-        <v>10356</v>
+        <v>10351</v>
       </c>
       <c r="G17" s="9">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H17" s="9">
         <v>399</v>
       </c>
       <c r="I17" s="9">
-        <v>204097</v>
+        <v>204153</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="9">
-        <v>251410</v>
+        <v>251472</v>
       </c>
       <c r="D18" s="9">
-        <v>5477</v>
+        <v>5472</v>
       </c>
       <c r="E18" s="9">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="F18" s="9">
-        <v>14374</v>
+        <v>14378</v>
       </c>
       <c r="G18" s="9">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="H18" s="9">
         <v>495</v>
       </c>
       <c r="I18" s="9">
-        <v>256887</v>
+        <v>256944</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2524,16 +2524,16 @@
         <v>127</v>
       </c>
       <c r="C19" s="9">
-        <v>139829</v>
+        <v>139846</v>
       </c>
       <c r="D19" s="9">
         <v>1706</v>
       </c>
       <c r="E19" s="9">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F19" s="9">
-        <v>10572</v>
+        <v>10575</v>
       </c>
       <c r="G19" s="9">
         <v>226</v>
@@ -2542,7 +2542,7 @@
         <v>233</v>
       </c>
       <c r="I19" s="9">
-        <v>141535</v>
+        <v>141552</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2553,25 +2553,25 @@
         <v>133</v>
       </c>
       <c r="C20" s="9">
-        <v>677848</v>
+        <v>682609</v>
       </c>
       <c r="D20" s="9">
-        <v>7651</v>
+        <v>7676</v>
       </c>
       <c r="E20" s="9">
-        <v>3960</v>
+        <v>3982</v>
       </c>
       <c r="F20" s="9">
-        <v>18931</v>
+        <v>19039</v>
       </c>
       <c r="G20" s="9">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="H20" s="9">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="I20" s="9">
-        <v>685499</v>
+        <v>690285</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2582,25 +2582,25 @@
         <v>139</v>
       </c>
       <c r="C21" s="9">
-        <v>137447</v>
+        <v>137862</v>
       </c>
       <c r="D21" s="9">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="E21" s="9">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="F21" s="9">
-        <v>5939</v>
+        <v>5953</v>
       </c>
       <c r="G21" s="9">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H21" s="9">
         <v>774</v>
       </c>
       <c r="I21" s="9">
-        <v>138658</v>
+        <v>139074</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2611,25 +2611,25 @@
         <v>146</v>
       </c>
       <c r="C22" s="12">
-        <v>7184751</v>
+        <v>7198360</v>
       </c>
       <c r="D22" s="12">
-        <v>117648</v>
+        <v>117680</v>
       </c>
       <c r="E22" s="12">
-        <v>76726</v>
+        <v>76827</v>
       </c>
       <c r="F22" s="12">
-        <v>380969</v>
+        <v>381520</v>
       </c>
       <c r="G22" s="12">
-        <v>62670</v>
+        <v>62737</v>
       </c>
       <c r="H22" s="12">
         <v>9848</v>
       </c>
       <c r="I22" s="12">
-        <v>7302399</v>
+        <v>7316040</v>
       </c>
     </row>
   </sheetData>
@@ -2723,10 +2723,10 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>1433</v>
+        <v>1446</v>
       </c>
       <c r="D6" s="6">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>158</v>
@@ -2763,7 +2763,7 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D8" s="9">
         <v>10</v>
@@ -2783,7 +2783,7 @@
         <v>58</v>
       </c>
       <c r="C9" s="9">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D9" s="9">
         <v>61</v>
@@ -2823,7 +2823,7 @@
         <v>73</v>
       </c>
       <c r="C11" s="9">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D11" s="9">
         <v>107</v>
@@ -2863,7 +2863,7 @@
         <v>87</v>
       </c>
       <c r="C13" s="9">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="9">
         <v>19</v>
@@ -2877,13 +2877,13 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="9">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14" s="9">
         <v>16</v>
@@ -2897,16 +2897,16 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="9">
         <v>152</v>
       </c>
       <c r="D15" s="9">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>167</v>
@@ -2917,13 +2917,13 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="9">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D16" s="9">
         <v>25</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" s="9">
         <v>27</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="9">
         <v>63</v>
@@ -3003,10 +3003,10 @@
         <v>133</v>
       </c>
       <c r="C20" s="9">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D20" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>172</v>
@@ -3043,10 +3043,10 @@
         <v>146</v>
       </c>
       <c r="C22" s="12">
-        <v>1433</v>
+        <v>1446</v>
       </c>
       <c r="D22" s="12">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>158</v>

--- a/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
@@ -18,7 +18,7 @@
     <t>PROGRES PEMUTAKHIRAN KELUARGA - KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 6 Sep 2026, 06.16 | Dicetak: 6 Sep 2026, 07.43</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 7 Sep 2026, 12.56 | Dicetak: 7 Sep 2026, 15.56</t>
   </si>
   <si>
     <t>Kode</t>
@@ -123,331 +123,331 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>74,24</t>
+    <t>74,38</t>
   </si>
   <si>
     <t>1,87</t>
   </si>
   <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>22,93</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>87,75</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>81,09</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>18,26</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>94,22</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>79,52</t>
+  </si>
+  <si>
+    <t>1,06</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>19,12</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>97,32</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>74,26</t>
+  </si>
+  <si>
+    <t>1,32</t>
+  </si>
+  <si>
+    <t>89,25</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>77,53</t>
+  </si>
+  <si>
+    <t>1,98</t>
+  </si>
+  <si>
+    <t>20,01</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>88,05</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>76,31</t>
+  </si>
+  <si>
+    <t>2,86</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>20,07</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>86,54</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>71,02</t>
+  </si>
+  <si>
+    <t>1,97</t>
+  </si>
+  <si>
+    <t>26,84</t>
+  </si>
+  <si>
+    <t>83,75</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>78,01</t>
+  </si>
+  <si>
+    <t>1,78</t>
+  </si>
+  <si>
+    <t>19,7</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>92,08</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>70,35</t>
+  </si>
+  <si>
+    <t>2,31</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>27,61</t>
+  </si>
+  <si>
+    <t>84,48</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>75,7</t>
+  </si>
+  <si>
+    <t>3,06</t>
+  </si>
+  <si>
+    <t>21,68</t>
+  </si>
+  <si>
+    <t>90,66</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>81,25</t>
+  </si>
+  <si>
+    <t>1,53</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>17,37</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>74,76</t>
+  </si>
+  <si>
+    <t>1,58</t>
+  </si>
+  <si>
+    <t>24,56</t>
+  </si>
+  <si>
+    <t>91,6</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>74,74</t>
+  </si>
+  <si>
+    <t>2,42</t>
+  </si>
+  <si>
+    <t>22,97</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>87,89</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>82,91</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>17,06</t>
+  </si>
+  <si>
     <t>0,07</t>
   </si>
   <si>
-    <t>22,91</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>87,56</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>81,09</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>18,26</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>94,22</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>79,38</t>
-  </si>
-  <si>
-    <t>1,06</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>19,11</t>
-  </si>
-  <si>
-    <t>97,14</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
+    <t>101,82</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>59,1</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>35,31</t>
+  </si>
+  <si>
+    <t>75,21</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
   </si>
   <si>
     <t>73,93</t>
   </si>
   <si>
-    <t>1,31</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>22,89</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>88,86</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>77,38</t>
-  </si>
-  <si>
-    <t>1,98</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>87,84</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>76,24</t>
-  </si>
-  <si>
-    <t>2,86</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>20,08</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>86,46</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>71,02</t>
-  </si>
-  <si>
-    <t>1,97</t>
-  </si>
-  <si>
-    <t>26,84</t>
-  </si>
-  <si>
-    <t>83,75</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>77,95</t>
-  </si>
-  <si>
-    <t>1,78</t>
-  </si>
-  <si>
-    <t>19,69</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>91,97</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>70,27</t>
-  </si>
-  <si>
-    <t>2,31</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>27,63</t>
-  </si>
-  <si>
-    <t>84,36</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>75,65</t>
-  </si>
-  <si>
-    <t>3,06</t>
-  </si>
-  <si>
-    <t>21,71</t>
-  </si>
-  <si>
-    <t>90,56</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>81,22</t>
-  </si>
-  <si>
-    <t>1,53</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>17,39</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>91,91</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>74,74</t>
-  </si>
-  <si>
-    <t>1,58</t>
-  </si>
-  <si>
-    <t>24,57</t>
-  </si>
-  <si>
-    <t>91,56</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>2,42</t>
-  </si>
-  <si>
-    <t>22,98</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>87,87</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>82,91</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>17,06</t>
-  </si>
-  <si>
-    <t>101,8</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>58,69</t>
-  </si>
-  <si>
-    <t>0,95</t>
-  </si>
-  <si>
-    <t>35,16</t>
-  </si>
-  <si>
-    <t>74,68</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>73,69</t>
-  </si>
-  <si>
     <t>1,51</t>
   </si>
   <si>
-    <t>24,11</t>
+    <t>24,14</t>
   </si>
   <si>
     <t>0,04</t>
   </si>
   <si>
-    <t>85,67</t>
+    <t>86,09</t>
   </si>
   <si>
     <t/>
@@ -489,28 +489,28 @@
     <t>Jumlah Bangunan Keluarga Khusus Berpindah-pindah Didata (K2)</t>
   </si>
   <si>
-    <t>42,81</t>
+    <t>44,62</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>15,15</t>
-  </si>
-  <si>
-    <t>33,52</t>
+    <t>15,38</t>
+  </si>
+  <si>
+    <t>42,31</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>48,42</t>
+    <t>47,98</t>
   </si>
   <si>
     <t>78,43</t>
   </si>
   <si>
-    <t>25,68</t>
+    <t>27,03</t>
   </si>
   <si>
     <t>15,84</t>
@@ -519,22 +519,22 @@
     <t>79,61</t>
   </si>
   <si>
-    <t>28,74</t>
-  </si>
-  <si>
-    <t>70,37</t>
-  </si>
-  <si>
-    <t>93,65</t>
+    <t>37,93</t>
+  </si>
+  <si>
+    <t>63,33</t>
+  </si>
+  <si>
+    <t>98,41</t>
   </si>
   <si>
     <t>75</t>
   </si>
   <si>
-    <t>12,34</t>
-  </si>
-  <si>
-    <t>87,18</t>
+    <t>12,18</t>
+  </si>
+  <si>
+    <t>89,47</t>
   </si>
 </sst>
 </file>
@@ -1195,40 +1195,40 @@
         <v>2730939</v>
       </c>
       <c r="D6" s="6">
-        <v>2027507</v>
+        <v>2031308</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="6">
-        <v>363702</v>
+        <v>365025</v>
       </c>
       <c r="G6" s="6">
-        <v>51157</v>
+        <v>51165</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="6">
-        <v>1784</v>
+        <v>1774</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="6">
-        <v>625692</v>
+        <v>626182</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="6">
-        <v>5251</v>
+        <v>5328</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="6">
-        <v>2391209</v>
+        <v>2396333</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>41</v>
@@ -1295,13 +1295,13 @@
         <v>172957</v>
       </c>
       <c r="D8" s="9">
-        <v>137297</v>
+        <v>137531</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="9">
-        <v>30718</v>
+        <v>30788</v>
       </c>
       <c r="G8" s="9">
         <v>1834</v>
@@ -1316,198 +1316,198 @@
         <v>54</v>
       </c>
       <c r="K8" s="9">
-        <v>33060</v>
+        <v>33066</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>55</v>
       </c>
       <c r="M8" s="9">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="O8" s="9">
-        <v>168015</v>
+        <v>168319</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="9">
         <v>342736</v>
       </c>
       <c r="D9" s="9">
-        <v>253394</v>
+        <v>254520</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" s="9">
-        <v>51152</v>
+        <v>51356</v>
       </c>
       <c r="G9" s="9">
-        <v>4505</v>
+        <v>4507</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I9" s="9">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="K9" s="9">
-        <v>78453</v>
+        <v>78589</v>
       </c>
       <c r="L9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="9">
+        <v>698</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="O9" s="9">
+        <v>305876</v>
+      </c>
+      <c r="P9" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="M9" s="9">
-        <v>688</v>
-      </c>
-      <c r="N9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="O9" s="9">
-        <v>304546</v>
-      </c>
-      <c r="P9" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" s="9">
         <v>362841</v>
       </c>
       <c r="D10" s="9">
-        <v>280749</v>
+        <v>281312</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F10" s="9">
-        <v>37982</v>
+        <v>38184</v>
       </c>
       <c r="G10" s="9">
-        <v>7195</v>
+        <v>7196</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I10" s="9">
         <v>215</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="K10" s="9">
-        <v>72560</v>
+        <v>72588</v>
       </c>
       <c r="L10" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M10" s="9">
+        <v>551</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" s="9">
+        <v>319496</v>
+      </c>
+      <c r="P10" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="M10" s="9">
-        <v>545</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O10" s="9">
-        <v>318731</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" s="9">
         <v>449576</v>
       </c>
       <c r="D11" s="9">
-        <v>342778</v>
+        <v>343049</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F11" s="9">
-        <v>45923</v>
+        <v>46006</v>
       </c>
       <c r="G11" s="9">
-        <v>12847</v>
+        <v>12845</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I11" s="9">
         <v>407</v>
       </c>
       <c r="J11" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K11" s="9">
+        <v>90244</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" s="9">
+        <v>1560</v>
+      </c>
+      <c r="N11" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="K11" s="9">
-        <v>90262</v>
-      </c>
-      <c r="L11" s="10" t="s">
+      <c r="O11" s="9">
+        <v>389055</v>
+      </c>
+      <c r="P11" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="M11" s="9">
-        <v>1535</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O11" s="9">
-        <v>388701</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="9">
         <v>199396</v>
       </c>
       <c r="D12" s="9">
-        <v>141607</v>
+        <v>141609</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F12" s="9">
-        <v>25389</v>
+        <v>25388</v>
       </c>
       <c r="G12" s="9">
         <v>3930</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I12" s="9">
         <v>61</v>
@@ -1516,110 +1516,110 @@
         <v>46</v>
       </c>
       <c r="K12" s="9">
-        <v>53512</v>
+        <v>53510</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M12" s="9">
         <v>298</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O12" s="9">
-        <v>166996</v>
+        <v>166997</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C13" s="9">
         <v>146092</v>
       </c>
       <c r="D13" s="9">
-        <v>113875</v>
+        <v>113971</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F13" s="9">
-        <v>20491</v>
+        <v>20547</v>
       </c>
       <c r="G13" s="9">
         <v>2595</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I13" s="9">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>38</v>
       </c>
       <c r="K13" s="9">
-        <v>28764</v>
+        <v>28774</v>
       </c>
       <c r="L13" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="9">
+        <v>302</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O13" s="9">
+        <v>134518</v>
+      </c>
+      <c r="P13" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="M13" s="9">
-        <v>301</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="O13" s="9">
-        <v>134366</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" s="9">
         <v>135256</v>
       </c>
       <c r="D14" s="9">
-        <v>95043</v>
+        <v>95150</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F14" s="9">
-        <v>19055</v>
+        <v>19112</v>
       </c>
       <c r="G14" s="9">
         <v>3131</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I14" s="9">
         <v>33</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K14" s="9">
-        <v>37367</v>
+        <v>37343</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M14" s="9">
         <v>71</v>
@@ -1628,36 +1628,36 @@
         <v>54</v>
       </c>
       <c r="O14" s="9">
-        <v>114098</v>
+        <v>114262</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9">
         <v>152158</v>
       </c>
       <c r="D15" s="9">
-        <v>115115</v>
+        <v>115177</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F15" s="9">
-        <v>22673</v>
+        <v>22765</v>
       </c>
       <c r="G15" s="9">
-        <v>4661</v>
+        <v>4662</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I15" s="9">
         <v>72</v>
@@ -1666,110 +1666,110 @@
         <v>54</v>
       </c>
       <c r="K15" s="9">
-        <v>33026</v>
+        <v>32982</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M15" s="9">
         <v>143</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O15" s="9">
-        <v>137788</v>
+        <v>137942</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C16" s="9">
         <v>135741</v>
       </c>
       <c r="D16" s="9">
-        <v>110247</v>
+        <v>110293</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="9">
-        <v>14511</v>
+        <v>14593</v>
       </c>
       <c r="G16" s="9">
         <v>2074</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I16" s="9">
         <v>110</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K16" s="9">
-        <v>23603</v>
+        <v>23580</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M16" s="9">
         <v>328</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O16" s="9">
-        <v>124758</v>
+        <v>124886</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C17" s="9">
         <v>75116</v>
       </c>
       <c r="D17" s="9">
-        <v>56141</v>
+        <v>56160</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="9">
+        <v>12645</v>
+      </c>
+      <c r="G17" s="9">
+        <v>1188</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="9">
+        <v>144</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17" s="9">
+        <v>18449</v>
+      </c>
+      <c r="L17" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="F17" s="9">
-        <v>12636</v>
-      </c>
-      <c r="G17" s="9">
-        <v>1187</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="I17" s="9">
-        <v>145</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K17" s="9">
-        <v>18459</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="M17" s="9">
         <v>35</v>
@@ -1778,36 +1778,36 @@
         <v>54</v>
       </c>
       <c r="O17" s="9">
-        <v>68777</v>
+        <v>68805</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C18" s="9">
         <v>99169</v>
       </c>
       <c r="D18" s="9">
-        <v>74115</v>
+        <v>74119</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F18" s="9">
-        <v>13024</v>
+        <v>13036</v>
       </c>
       <c r="G18" s="9">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I18" s="9">
         <v>53</v>
@@ -1816,69 +1816,69 @@
         <v>54</v>
       </c>
       <c r="K18" s="9">
-        <v>22792</v>
+        <v>22783</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M18" s="9">
         <v>281</v>
       </c>
       <c r="N18" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="O18" s="9">
+        <v>87155</v>
+      </c>
+      <c r="P18" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="O18" s="9">
-        <v>87139</v>
-      </c>
-      <c r="P18" s="10" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>126</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>127</v>
       </c>
       <c r="C19" s="9">
         <v>41772</v>
       </c>
       <c r="D19" s="9">
-        <v>34633</v>
+        <v>34635</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F19" s="9">
-        <v>7891</v>
+        <v>7898</v>
       </c>
       <c r="G19" s="9">
         <v>357</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I19" s="9">
         <v>27</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="K19" s="9">
-        <v>7128</v>
+        <v>7126</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M19" s="9">
         <v>28</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="O19" s="9">
-        <v>42524</v>
+        <v>42533</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>131</v>
@@ -1895,16 +1895,16 @@
         <v>279478</v>
       </c>
       <c r="D20" s="9">
-        <v>164039</v>
+        <v>165178</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>134</v>
       </c>
       <c r="F20" s="9">
-        <v>44665</v>
+        <v>45021</v>
       </c>
       <c r="G20" s="9">
-        <v>2664</v>
+        <v>2667</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>135</v>
@@ -1913,22 +1913,22 @@
         <v>181</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="K20" s="9">
-        <v>98256</v>
+        <v>98684</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>136</v>
       </c>
       <c r="M20" s="9">
-        <v>559</v>
+        <v>593</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="O20" s="9">
-        <v>208704</v>
+        <v>210199</v>
       </c>
       <c r="P20" s="10" t="s">
         <v>137</v>
@@ -1945,16 +1945,16 @@
         <v>53506</v>
       </c>
       <c r="D21" s="9">
-        <v>39427</v>
+        <v>39557</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>140</v>
       </c>
       <c r="F21" s="9">
-        <v>6413</v>
+        <v>6507</v>
       </c>
       <c r="G21" s="9">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>141</v>
@@ -1966,7 +1966,7 @@
         <v>48</v>
       </c>
       <c r="K21" s="9">
-        <v>12901</v>
+        <v>12915</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>142</v>
@@ -1978,7 +1978,7 @@
         <v>143</v>
       </c>
       <c r="O21" s="9">
-        <v>45840</v>
+        <v>46064</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>144</v>
@@ -1995,40 +1995,40 @@
         <v>2730939</v>
       </c>
       <c r="D22" s="12">
-        <v>2027507</v>
+        <v>2031308</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="12">
-        <v>363702</v>
+        <v>365025</v>
       </c>
       <c r="G22" s="12">
-        <v>51157</v>
+        <v>51165</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="12">
-        <v>1784</v>
+        <v>1774</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="12">
-        <v>625692</v>
+        <v>626182</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="12">
-        <v>5251</v>
+        <v>5328</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="O22" s="12">
-        <v>2391209</v>
+        <v>2396333</v>
       </c>
       <c r="P22" s="13" t="s">
         <v>41</v>
@@ -2147,25 +2147,25 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>7198360</v>
+        <v>7214680</v>
       </c>
       <c r="D6" s="6">
-        <v>117680</v>
+        <v>117846</v>
       </c>
       <c r="E6" s="6">
-        <v>76827</v>
+        <v>76949</v>
       </c>
       <c r="F6" s="6">
-        <v>381520</v>
+        <v>382075</v>
       </c>
       <c r="G6" s="6">
-        <v>62737</v>
+        <v>62850</v>
       </c>
       <c r="H6" s="6">
-        <v>9848</v>
+        <v>9846</v>
       </c>
       <c r="I6" s="6">
-        <v>7316040</v>
+        <v>7332526</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>43</v>
       </c>
       <c r="C7" s="9">
-        <v>251657</v>
+        <v>251660</v>
       </c>
       <c r="D7" s="9">
         <v>2929</v>
@@ -2194,7 +2194,7 @@
         <v>382</v>
       </c>
       <c r="I7" s="9">
-        <v>254586</v>
+        <v>254589</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2205,123 +2205,123 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>513636</v>
+        <v>514556</v>
       </c>
       <c r="D8" s="9">
         <v>6552</v>
       </c>
       <c r="E8" s="9">
-        <v>4989</v>
+        <v>4998</v>
       </c>
       <c r="F8" s="9">
-        <v>38683</v>
+        <v>38724</v>
       </c>
       <c r="G8" s="9">
-        <v>4544</v>
+        <v>4553</v>
       </c>
       <c r="H8" s="9">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I8" s="9">
-        <v>520188</v>
+        <v>521108</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="9">
-        <v>931545</v>
+        <v>936024</v>
       </c>
       <c r="D9" s="9">
-        <v>15317</v>
+        <v>15358</v>
       </c>
       <c r="E9" s="9">
-        <v>10484</v>
+        <v>10522</v>
       </c>
       <c r="F9" s="9">
-        <v>44652</v>
+        <v>44799</v>
       </c>
       <c r="G9" s="9">
-        <v>5519</v>
+        <v>5524</v>
       </c>
       <c r="H9" s="9">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="I9" s="9">
-        <v>946862</v>
+        <v>951382</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" s="9">
-        <v>904783</v>
+        <v>907129</v>
       </c>
       <c r="D10" s="9">
-        <v>16620</v>
+        <v>16662</v>
       </c>
       <c r="E10" s="9">
-        <v>10633</v>
+        <v>10657</v>
       </c>
       <c r="F10" s="9">
-        <v>43968</v>
+        <v>44064</v>
       </c>
       <c r="G10" s="9">
-        <v>22590</v>
+        <v>22650</v>
       </c>
       <c r="H10" s="9">
         <v>1155</v>
       </c>
       <c r="I10" s="9">
-        <v>921403</v>
+        <v>923791</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" s="9">
-        <v>1138845</v>
+        <v>1139935</v>
       </c>
       <c r="D11" s="9">
-        <v>21585</v>
+        <v>21603</v>
       </c>
       <c r="E11" s="9">
-        <v>13415</v>
+        <v>13421</v>
       </c>
       <c r="F11" s="9">
-        <v>50406</v>
+        <v>50447</v>
       </c>
       <c r="G11" s="9">
-        <v>9056</v>
+        <v>9064</v>
       </c>
       <c r="H11" s="9">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="I11" s="9">
-        <v>1160430</v>
+        <v>1161538</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="9">
-        <v>518747</v>
+        <v>518749</v>
       </c>
       <c r="D12" s="9">
         <v>6353</v>
@@ -2330,175 +2330,175 @@
         <v>6168</v>
       </c>
       <c r="F12" s="9">
-        <v>29369</v>
+        <v>29370</v>
       </c>
       <c r="G12" s="9">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="H12" s="9">
         <v>521</v>
       </c>
       <c r="I12" s="9">
-        <v>525100</v>
+        <v>525102</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C13" s="9">
-        <v>403509</v>
+        <v>404030</v>
       </c>
       <c r="D13" s="9">
-        <v>4794</v>
+        <v>4795</v>
       </c>
       <c r="E13" s="9">
-        <v>4513</v>
+        <v>4515</v>
       </c>
       <c r="F13" s="9">
-        <v>28925</v>
+        <v>28951</v>
       </c>
       <c r="G13" s="9">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="H13" s="9">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="I13" s="9">
-        <v>408303</v>
+        <v>408825</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" s="9">
-        <v>339410</v>
+        <v>339896</v>
       </c>
       <c r="D14" s="9">
-        <v>9540</v>
+        <v>9564</v>
       </c>
       <c r="E14" s="9">
-        <v>3675</v>
+        <v>3678</v>
       </c>
       <c r="F14" s="9">
-        <v>22524</v>
+        <v>22554</v>
       </c>
       <c r="G14" s="9">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="H14" s="9">
         <v>391</v>
       </c>
       <c r="I14" s="9">
-        <v>348950</v>
+        <v>349460</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9">
-        <v>415631</v>
+        <v>416078</v>
       </c>
       <c r="D15" s="9">
-        <v>7900</v>
+        <v>7905</v>
       </c>
       <c r="E15" s="9">
-        <v>6736</v>
+        <v>6737</v>
       </c>
       <c r="F15" s="9">
-        <v>28067</v>
+        <v>28100</v>
       </c>
       <c r="G15" s="9">
-        <v>4054</v>
+        <v>4063</v>
       </c>
       <c r="H15" s="9">
         <v>518</v>
       </c>
       <c r="I15" s="9">
-        <v>423531</v>
+        <v>423983</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C16" s="9">
-        <v>369523</v>
+        <v>369781</v>
       </c>
       <c r="D16" s="9">
-        <v>5156</v>
+        <v>5157</v>
       </c>
       <c r="E16" s="9">
         <v>3205</v>
       </c>
       <c r="F16" s="9">
-        <v>21263</v>
+        <v>21271</v>
       </c>
       <c r="G16" s="9">
-        <v>4288</v>
+        <v>4289</v>
       </c>
       <c r="H16" s="9">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I16" s="9">
-        <v>374679</v>
+        <v>374938</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C17" s="9">
-        <v>199285</v>
+        <v>199356</v>
       </c>
       <c r="D17" s="9">
-        <v>4868</v>
+        <v>4869</v>
       </c>
       <c r="E17" s="9">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="F17" s="9">
-        <v>10351</v>
+        <v>10349</v>
       </c>
       <c r="G17" s="9">
         <v>1728</v>
       </c>
       <c r="H17" s="9">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I17" s="9">
-        <v>204153</v>
+        <v>204225</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C18" s="9">
-        <v>251472</v>
+        <v>251515</v>
       </c>
       <c r="D18" s="9">
-        <v>5472</v>
+        <v>5476</v>
       </c>
       <c r="E18" s="9">
         <v>2674</v>
@@ -2513,27 +2513,27 @@
         <v>495</v>
       </c>
       <c r="I18" s="9">
-        <v>256944</v>
+        <v>256991</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="C19" s="9">
-        <v>139846</v>
+        <v>139875</v>
       </c>
       <c r="D19" s="9">
         <v>1706</v>
       </c>
       <c r="E19" s="9">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F19" s="9">
-        <v>10575</v>
+        <v>10576</v>
       </c>
       <c r="G19" s="9">
         <v>226</v>
@@ -2542,7 +2542,7 @@
         <v>233</v>
       </c>
       <c r="I19" s="9">
-        <v>141552</v>
+        <v>141581</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2553,25 +2553,25 @@
         <v>133</v>
       </c>
       <c r="C20" s="9">
-        <v>682609</v>
+        <v>687617</v>
       </c>
       <c r="D20" s="9">
-        <v>7676</v>
+        <v>7704</v>
       </c>
       <c r="E20" s="9">
-        <v>3982</v>
+        <v>4011</v>
       </c>
       <c r="F20" s="9">
-        <v>19039</v>
+        <v>19169</v>
       </c>
       <c r="G20" s="9">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="H20" s="9">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="I20" s="9">
-        <v>690285</v>
+        <v>695321</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2582,25 +2582,25 @@
         <v>139</v>
       </c>
       <c r="C21" s="9">
-        <v>137862</v>
+        <v>138479</v>
       </c>
       <c r="D21" s="9">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="E21" s="9">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="F21" s="9">
-        <v>5953</v>
+        <v>5956</v>
       </c>
       <c r="G21" s="9">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="H21" s="9">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I21" s="9">
-        <v>139074</v>
+        <v>139692</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2611,25 +2611,25 @@
         <v>146</v>
       </c>
       <c r="C22" s="12">
-        <v>7198360</v>
+        <v>7214680</v>
       </c>
       <c r="D22" s="12">
-        <v>117680</v>
+        <v>117846</v>
       </c>
       <c r="E22" s="12">
-        <v>76827</v>
+        <v>76949</v>
       </c>
       <c r="F22" s="12">
-        <v>381520</v>
+        <v>382075</v>
       </c>
       <c r="G22" s="12">
-        <v>62737</v>
+        <v>62850</v>
       </c>
       <c r="H22" s="12">
-        <v>9848</v>
+        <v>9846</v>
       </c>
       <c r="I22" s="12">
-        <v>7316040</v>
+        <v>7332526</v>
       </c>
     </row>
   </sheetData>
@@ -2723,10 +2723,10 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="D6" s="6">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>158</v>
@@ -2763,7 +2763,7 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" s="9">
         <v>10</v>
@@ -2777,16 +2777,16 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="9">
         <v>182</v>
       </c>
       <c r="D9" s="9">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>161</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" s="9">
         <v>160</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" s="9">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D11" s="9">
         <v>107</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="9">
         <v>51</v>
@@ -2857,16 +2857,16 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C13" s="9">
         <v>74</v>
       </c>
       <c r="D13" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>165</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" s="9">
         <v>101</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9">
         <v>152</v>
@@ -2917,16 +2917,16 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C16" s="9">
         <v>87</v>
       </c>
       <c r="D16" s="9">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>168</v>
@@ -2937,13 +2937,13 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C17" s="9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D17" s="9">
         <v>19</v>
@@ -2957,16 +2957,16 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C18" s="9">
         <v>63</v>
       </c>
       <c r="D18" s="9">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>170</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>126</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>127</v>
       </c>
       <c r="C19" s="9">
         <v>20</v>
@@ -3003,7 +3003,7 @@
         <v>133</v>
       </c>
       <c r="C20" s="9">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D20" s="9">
         <v>19</v>
@@ -3023,7 +3023,7 @@
         <v>139</v>
       </c>
       <c r="C21" s="9">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D21" s="9">
         <v>68</v>
@@ -3043,10 +3043,10 @@
         <v>146</v>
       </c>
       <c r="C22" s="12">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="D22" s="12">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>158</v>

--- a/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="176">
   <si>
     <t>PROGRES PEMUTAKHIRAN KELUARGA - KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 7 Sep 2026, 12.56 | Dicetak: 7 Sep 2026, 15.56</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 8 Sep 2026, 06.16 | Dicetak: 8 Sep 2026, 07.17</t>
   </si>
   <si>
     <t>Kode</t>
@@ -123,7 +123,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>74,38</t>
+    <t>74,48</t>
   </si>
   <si>
     <t>1,87</t>
@@ -132,76 +132,82 @@
     <t>0,06</t>
   </si>
   <si>
+    <t>22,94</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>87,87</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>81,09</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>18,26</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>94,22</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>79,55</t>
+  </si>
+  <si>
+    <t>1,06</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>19,11</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>97,37</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>74,52</t>
+  </si>
+  <si>
+    <t>1,32</t>
+  </si>
+  <si>
     <t>22,93</t>
   </si>
   <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>87,75</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>81,09</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>18,26</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>94,22</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>79,52</t>
-  </si>
-  <si>
-    <t>1,06</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>19,12</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>97,32</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>74,26</t>
-  </si>
-  <si>
-    <t>1,32</t>
-  </si>
-  <si>
-    <t>89,25</t>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>89,54</t>
   </si>
   <si>
     <t>1804</t>
@@ -210,7 +216,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>77,53</t>
+    <t>77,59</t>
   </si>
   <si>
     <t>1,98</t>
@@ -222,7 +228,7 @@
     <t>0,15</t>
   </si>
   <si>
-    <t>88,05</t>
+    <t>88,13</t>
   </si>
   <si>
     <t>1805</t>
@@ -231,7 +237,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>76,31</t>
+    <t>76,35</t>
   </si>
   <si>
     <t>2,86</t>
@@ -240,13 +246,13 @@
     <t>0,09</t>
   </si>
   <si>
-    <t>20,07</t>
+    <t>20,08</t>
   </si>
   <si>
     <t>0,35</t>
   </si>
   <si>
-    <t>86,54</t>
+    <t>86,59</t>
   </si>
   <si>
     <t>1806</t>
@@ -261,7 +267,7 @@
     <t>1,97</t>
   </si>
   <si>
-    <t>26,84</t>
+    <t>26,83</t>
   </si>
   <si>
     <t>83,75</t>
@@ -273,7 +279,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>78,01</t>
+    <t>78,05</t>
   </si>
   <si>
     <t>1,78</t>
@@ -282,10 +288,7 @@
     <t>19,7</t>
   </si>
   <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>92,08</t>
+    <t>92,12</t>
   </si>
   <si>
     <t>1808</t>
@@ -294,7 +297,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>70,35</t>
+    <t>70,44</t>
   </si>
   <si>
     <t>2,31</t>
@@ -306,7 +309,7 @@
     <t>27,61</t>
   </si>
   <si>
-    <t>84,48</t>
+    <t>84,6</t>
   </si>
   <si>
     <t>1809</t>
@@ -315,16 +318,22 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>75,7</t>
-  </si>
-  <si>
-    <t>3,06</t>
-  </si>
-  <si>
-    <t>21,68</t>
-  </si>
-  <si>
-    <t>90,66</t>
+    <t>75,72</t>
+  </si>
+  <si>
+    <t>3,07</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>21,66</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>90,73</t>
   </si>
   <si>
     <t>1810</t>
@@ -333,7 +342,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>81,25</t>
+    <t>81,26</t>
   </si>
   <si>
     <t>1,53</t>
@@ -342,13 +351,13 @@
     <t>0,08</t>
   </si>
   <si>
-    <t>17,37</t>
+    <t>17,36</t>
   </si>
   <si>
     <t>0,24</t>
   </si>
   <si>
-    <t>92</t>
+    <t>92,02</t>
   </si>
   <si>
     <t>1811</t>
@@ -357,7 +366,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>74,76</t>
+    <t>74,77</t>
   </si>
   <si>
     <t>1,58</t>
@@ -366,7 +375,7 @@
     <t>24,56</t>
   </si>
   <si>
-    <t>91,6</t>
+    <t>91,62</t>
   </si>
   <si>
     <t>1812</t>
@@ -375,19 +384,19 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>74,74</t>
+    <t>74,75</t>
   </si>
   <si>
     <t>2,42</t>
   </si>
   <si>
-    <t>22,97</t>
+    <t>22,96</t>
   </si>
   <si>
     <t>0,28</t>
   </si>
   <si>
-    <t>87,89</t>
+    <t>87,9</t>
   </si>
   <si>
     <t>1813</t>
@@ -405,10 +414,7 @@
     <t>17,06</t>
   </si>
   <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>101,82</t>
+    <t>101,84</t>
   </si>
   <si>
     <t>1871</t>
@@ -417,16 +423,19 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>59,1</t>
+    <t>59,46</t>
   </si>
   <si>
     <t>0,95</t>
   </si>
   <si>
-    <t>35,31</t>
-  </si>
-  <si>
-    <t>75,21</t>
+    <t>35,41</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>75,69</t>
   </si>
   <si>
     <t>1872</t>
@@ -435,19 +444,16 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>73,93</t>
+    <t>74,05</t>
   </si>
   <si>
     <t>1,51</t>
   </si>
   <si>
-    <t>24,14</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>86,09</t>
+    <t>24,11</t>
+  </si>
+  <si>
+    <t>86,25</t>
   </si>
   <si>
     <t/>
@@ -489,7 +495,7 @@
     <t>Jumlah Bangunan Keluarga Khusus Berpindah-pindah Didata (K2)</t>
   </si>
   <si>
-    <t>44,62</t>
+    <t>45,22</t>
   </si>
   <si>
     <t>0</t>
@@ -498,28 +504,28 @@
     <t>15,38</t>
   </si>
   <si>
-    <t>42,31</t>
+    <t>46,74</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>47,98</t>
-  </si>
-  <si>
-    <t>78,43</t>
-  </si>
-  <si>
-    <t>27,03</t>
+    <t>48,2</t>
+  </si>
+  <si>
+    <t>75,47</t>
+  </si>
+  <si>
+    <t>28,38</t>
   </si>
   <si>
     <t>15,84</t>
   </si>
   <si>
-    <t>79,61</t>
-  </si>
-  <si>
-    <t>37,93</t>
+    <t>80,26</t>
+  </si>
+  <si>
+    <t>38,82</t>
   </si>
   <si>
     <t>63,33</t>
@@ -531,10 +537,10 @@
     <t>75</t>
   </si>
   <si>
-    <t>12,18</t>
-  </si>
-  <si>
-    <t>89,47</t>
+    <t>13,55</t>
+  </si>
+  <si>
+    <t>88,31</t>
   </si>
 </sst>
 </file>
@@ -1195,40 +1201,40 @@
         <v>2730939</v>
       </c>
       <c r="D6" s="6">
-        <v>2031308</v>
+        <v>2033929</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="6">
-        <v>365025</v>
+        <v>365798</v>
       </c>
       <c r="G6" s="6">
-        <v>51165</v>
+        <v>51177</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="6">
-        <v>1774</v>
+        <v>1767</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="6">
-        <v>626182</v>
+        <v>626419</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="6">
-        <v>5328</v>
+        <v>5355</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="6">
-        <v>2396333</v>
+        <v>2399727</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>41</v>
@@ -1251,7 +1257,7 @@
         <v>44</v>
       </c>
       <c r="F7" s="9">
-        <v>11179</v>
+        <v>11180</v>
       </c>
       <c r="G7" s="9">
         <v>971</v>
@@ -1278,7 +1284,7 @@
         <v>48</v>
       </c>
       <c r="O7" s="9">
-        <v>80226</v>
+        <v>80227</v>
       </c>
       <c r="P7" s="10" t="s">
         <v>49</v>
@@ -1295,16 +1301,16 @@
         <v>172957</v>
       </c>
       <c r="D8" s="9">
-        <v>137531</v>
+        <v>137582</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="9">
-        <v>30788</v>
+        <v>30822</v>
       </c>
       <c r="G8" s="9">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>53</v>
@@ -1316,19 +1322,19 @@
         <v>54</v>
       </c>
       <c r="K8" s="9">
-        <v>33066</v>
+        <v>33057</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>55</v>
       </c>
       <c r="M8" s="9">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="N8" s="10" t="s">
         <v>56</v>
       </c>
       <c r="O8" s="9">
-        <v>168319</v>
+        <v>168404</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>57</v>
@@ -1345,69 +1351,69 @@
         <v>342736</v>
       </c>
       <c r="D9" s="9">
-        <v>254520</v>
+        <v>255391</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>60</v>
       </c>
       <c r="F9" s="9">
-        <v>51356</v>
+        <v>51501</v>
       </c>
       <c r="G9" s="9">
-        <v>4507</v>
+        <v>4509</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>61</v>
       </c>
       <c r="I9" s="9">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>38</v>
       </c>
       <c r="K9" s="9">
-        <v>78589</v>
+        <v>78606</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="M9" s="9">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="O9" s="9">
-        <v>305876</v>
+        <v>306892</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" s="9">
         <v>362841</v>
       </c>
       <c r="D10" s="9">
-        <v>281312</v>
+        <v>281516</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" s="9">
-        <v>38184</v>
+        <v>38240</v>
       </c>
       <c r="G10" s="9">
-        <v>7196</v>
+        <v>7198</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I10" s="9">
         <v>215</v>
@@ -1416,89 +1422,89 @@
         <v>38</v>
       </c>
       <c r="K10" s="9">
-        <v>72588</v>
+        <v>72591</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M10" s="9">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O10" s="9">
-        <v>319496</v>
+        <v>319756</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" s="9">
         <v>449576</v>
       </c>
       <c r="D11" s="9">
-        <v>343049</v>
+        <v>343237</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11" s="9">
-        <v>46006</v>
+        <v>46036</v>
       </c>
       <c r="G11" s="9">
-        <v>12845</v>
+        <v>12844</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I11" s="9">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K11" s="9">
-        <v>90244</v>
+        <v>90263</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M11" s="9">
-        <v>1560</v>
+        <v>1571</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O11" s="9">
-        <v>389055</v>
+        <v>389273</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C12" s="9">
         <v>199396</v>
       </c>
       <c r="D12" s="9">
-        <v>141609</v>
+        <v>141611</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F12" s="9">
         <v>25388</v>
@@ -1507,7 +1513,7 @@
         <v>3930</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I12" s="9">
         <v>61</v>
@@ -1516,48 +1522,48 @@
         <v>46</v>
       </c>
       <c r="K12" s="9">
-        <v>53510</v>
+        <v>53507</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M12" s="9">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O12" s="9">
-        <v>166997</v>
+        <v>166999</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C13" s="9">
         <v>146092</v>
       </c>
       <c r="D13" s="9">
-        <v>113971</v>
+        <v>114027</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F13" s="9">
-        <v>20547</v>
+        <v>20560</v>
       </c>
       <c r="G13" s="9">
         <v>2595</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I13" s="9">
         <v>92</v>
@@ -1569,57 +1575,57 @@
         <v>28774</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M13" s="9">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="O13" s="9">
-        <v>134518</v>
+        <v>134587</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" s="9">
         <v>135256</v>
       </c>
       <c r="D14" s="9">
-        <v>95150</v>
+        <v>95277</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F14" s="9">
-        <v>19112</v>
+        <v>19149</v>
       </c>
       <c r="G14" s="9">
         <v>3131</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I14" s="9">
         <v>33</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K14" s="9">
-        <v>37343</v>
+        <v>37341</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M14" s="9">
         <v>71</v>
@@ -1628,136 +1634,136 @@
         <v>54</v>
       </c>
       <c r="O14" s="9">
-        <v>114262</v>
+        <v>114426</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="9">
         <v>152158</v>
       </c>
       <c r="D15" s="9">
-        <v>115177</v>
+        <v>115213</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F15" s="9">
-        <v>22765</v>
+        <v>22836</v>
       </c>
       <c r="G15" s="9">
-        <v>4662</v>
+        <v>4666</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I15" s="9">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="K15" s="9">
-        <v>32982</v>
+        <v>32960</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M15" s="9">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="O15" s="9">
-        <v>137942</v>
+        <v>138049</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C16" s="9">
         <v>135741</v>
       </c>
       <c r="D16" s="9">
-        <v>110293</v>
+        <v>110305</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F16" s="9">
-        <v>14593</v>
+        <v>14604</v>
       </c>
       <c r="G16" s="9">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I16" s="9">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K16" s="9">
-        <v>23580</v>
+        <v>23563</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M16" s="9">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O16" s="9">
-        <v>124886</v>
+        <v>124909</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C17" s="9">
         <v>75116</v>
       </c>
       <c r="D17" s="9">
-        <v>56160</v>
+        <v>56161</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F17" s="9">
-        <v>12645</v>
+        <v>12657</v>
       </c>
       <c r="G17" s="9">
         <v>1188</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I17" s="9">
         <v>144</v>
@@ -1766,10 +1772,10 @@
         <v>56</v>
       </c>
       <c r="K17" s="9">
-        <v>18449</v>
+        <v>18448</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M17" s="9">
         <v>35</v>
@@ -1778,36 +1784,36 @@
         <v>54</v>
       </c>
       <c r="O17" s="9">
-        <v>68805</v>
+        <v>68818</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C18" s="9">
         <v>99169</v>
       </c>
       <c r="D18" s="9">
-        <v>74119</v>
+        <v>74128</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F18" s="9">
-        <v>13036</v>
+        <v>13043</v>
       </c>
       <c r="G18" s="9">
-        <v>2399</v>
+        <v>2402</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I18" s="9">
         <v>53</v>
@@ -1816,30 +1822,30 @@
         <v>54</v>
       </c>
       <c r="K18" s="9">
-        <v>22783</v>
+        <v>22770</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="M18" s="9">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O18" s="9">
-        <v>87155</v>
+        <v>87171</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C19" s="9">
         <v>41772</v>
@@ -1848,16 +1854,16 @@
         <v>34635</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F19" s="9">
-        <v>7898</v>
+        <v>7906</v>
       </c>
       <c r="G19" s="9">
         <v>357</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I19" s="9">
         <v>27</v>
@@ -1869,166 +1875,166 @@
         <v>7126</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M19" s="9">
         <v>28</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="O19" s="9">
-        <v>42533</v>
+        <v>42541</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C20" s="9">
         <v>279478</v>
       </c>
       <c r="D20" s="9">
-        <v>165178</v>
+        <v>166177</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F20" s="9">
-        <v>45021</v>
+        <v>45347</v>
       </c>
       <c r="G20" s="9">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I20" s="9">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="K20" s="9">
-        <v>98684</v>
+        <v>98965</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M20" s="9">
-        <v>593</v>
+        <v>624</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="O20" s="9">
-        <v>210199</v>
+        <v>211524</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9">
         <v>53506</v>
       </c>
       <c r="D21" s="9">
-        <v>39557</v>
+        <v>39622</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F21" s="9">
-        <v>6507</v>
+        <v>6529</v>
       </c>
       <c r="G21" s="9">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I21" s="9">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>48</v>
       </c>
       <c r="K21" s="9">
-        <v>12915</v>
+        <v>12899</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M21" s="9">
         <v>24</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="O21" s="9">
-        <v>46064</v>
+        <v>46151</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C22" s="12">
         <v>2730939</v>
       </c>
       <c r="D22" s="12">
-        <v>2031308</v>
+        <v>2033929</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="12">
-        <v>365025</v>
+        <v>365798</v>
       </c>
       <c r="G22" s="12">
-        <v>51165</v>
+        <v>51177</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="12">
-        <v>1774</v>
+        <v>1767</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="12">
-        <v>626182</v>
+        <v>626419</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="12">
-        <v>5328</v>
+        <v>5355</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="O22" s="12">
-        <v>2396333</v>
+        <v>2399727</v>
       </c>
       <c r="P22" s="13" t="s">
         <v>41</v>
@@ -2057,7 +2063,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2089,25 +2095,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2147,25 +2153,25 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>7214680</v>
+        <v>7224601</v>
       </c>
       <c r="D6" s="6">
-        <v>117846</v>
+        <v>117902</v>
       </c>
       <c r="E6" s="6">
-        <v>76949</v>
+        <v>77017</v>
       </c>
       <c r="F6" s="6">
-        <v>382075</v>
+        <v>382404</v>
       </c>
       <c r="G6" s="6">
-        <v>62850</v>
+        <v>62889</v>
       </c>
       <c r="H6" s="6">
-        <v>9846</v>
+        <v>9845</v>
       </c>
       <c r="I6" s="6">
-        <v>7332526</v>
+        <v>7342503</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2176,7 +2182,7 @@
         <v>43</v>
       </c>
       <c r="C7" s="9">
-        <v>251660</v>
+        <v>251661</v>
       </c>
       <c r="D7" s="9">
         <v>2929</v>
@@ -2185,7 +2191,7 @@
         <v>2142</v>
       </c>
       <c r="F7" s="9">
-        <v>13367</v>
+        <v>13366</v>
       </c>
       <c r="G7" s="9">
         <v>310</v>
@@ -2194,7 +2200,7 @@
         <v>382</v>
       </c>
       <c r="I7" s="9">
-        <v>254589</v>
+        <v>254590</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2205,25 +2211,25 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>514556</v>
+        <v>514802</v>
       </c>
       <c r="D8" s="9">
-        <v>6552</v>
+        <v>6558</v>
       </c>
       <c r="E8" s="9">
-        <v>4998</v>
+        <v>5002</v>
       </c>
       <c r="F8" s="9">
-        <v>38724</v>
+        <v>38742</v>
       </c>
       <c r="G8" s="9">
-        <v>4553</v>
+        <v>4556</v>
       </c>
       <c r="H8" s="9">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I8" s="9">
-        <v>521108</v>
+        <v>521360</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2234,94 +2240,94 @@
         <v>59</v>
       </c>
       <c r="C9" s="9">
-        <v>936024</v>
+        <v>939052</v>
       </c>
       <c r="D9" s="9">
-        <v>15358</v>
+        <v>15387</v>
       </c>
       <c r="E9" s="9">
-        <v>10522</v>
+        <v>10548</v>
       </c>
       <c r="F9" s="9">
-        <v>44799</v>
+        <v>44917</v>
       </c>
       <c r="G9" s="9">
-        <v>5524</v>
+        <v>5530</v>
       </c>
       <c r="H9" s="9">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="I9" s="9">
-        <v>951382</v>
+        <v>954439</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" s="9">
-        <v>907129</v>
+        <v>907883</v>
       </c>
       <c r="D10" s="9">
-        <v>16662</v>
+        <v>16668</v>
       </c>
       <c r="E10" s="9">
-        <v>10657</v>
+        <v>10659</v>
       </c>
       <c r="F10" s="9">
-        <v>44064</v>
+        <v>44077</v>
       </c>
       <c r="G10" s="9">
-        <v>22650</v>
+        <v>22666</v>
       </c>
       <c r="H10" s="9">
         <v>1155</v>
       </c>
       <c r="I10" s="9">
-        <v>923791</v>
+        <v>924551</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" s="9">
-        <v>1139935</v>
+        <v>1140540</v>
       </c>
       <c r="D11" s="9">
         <v>21603</v>
       </c>
       <c r="E11" s="9">
-        <v>13421</v>
+        <v>13422</v>
       </c>
       <c r="F11" s="9">
-        <v>50447</v>
+        <v>50467</v>
       </c>
       <c r="G11" s="9">
-        <v>9064</v>
+        <v>9068</v>
       </c>
       <c r="H11" s="9">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="I11" s="9">
-        <v>1161538</v>
+        <v>1162143</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C12" s="9">
-        <v>518749</v>
+        <v>518754</v>
       </c>
       <c r="D12" s="9">
         <v>6353</v>
@@ -2339,27 +2345,27 @@
         <v>521</v>
       </c>
       <c r="I12" s="9">
-        <v>525102</v>
+        <v>525107</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C13" s="9">
-        <v>404030</v>
+        <v>404239</v>
       </c>
       <c r="D13" s="9">
-        <v>4795</v>
+        <v>4805</v>
       </c>
       <c r="E13" s="9">
-        <v>4515</v>
+        <v>4519</v>
       </c>
       <c r="F13" s="9">
-        <v>28951</v>
+        <v>28965</v>
       </c>
       <c r="G13" s="9">
         <v>1626</v>
@@ -2368,105 +2374,105 @@
         <v>487</v>
       </c>
       <c r="I13" s="9">
-        <v>408825</v>
+        <v>409044</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" s="9">
-        <v>339896</v>
+        <v>340356</v>
       </c>
       <c r="D14" s="9">
-        <v>9564</v>
+        <v>9576</v>
       </c>
       <c r="E14" s="9">
-        <v>3678</v>
+        <v>3685</v>
       </c>
       <c r="F14" s="9">
-        <v>22554</v>
+        <v>22585</v>
       </c>
       <c r="G14" s="9">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="H14" s="9">
         <v>391</v>
       </c>
       <c r="I14" s="9">
-        <v>349460</v>
+        <v>349932</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="9">
-        <v>416078</v>
+        <v>416323</v>
       </c>
       <c r="D15" s="9">
-        <v>7905</v>
+        <v>7900</v>
       </c>
       <c r="E15" s="9">
-        <v>6737</v>
+        <v>6742</v>
       </c>
       <c r="F15" s="9">
-        <v>28100</v>
+        <v>28113</v>
       </c>
       <c r="G15" s="9">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="H15" s="9">
         <v>518</v>
       </c>
       <c r="I15" s="9">
-        <v>423983</v>
+        <v>424223</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C16" s="9">
-        <v>369781</v>
+        <v>369851</v>
       </c>
       <c r="D16" s="9">
-        <v>5157</v>
+        <v>5158</v>
       </c>
       <c r="E16" s="9">
-        <v>3205</v>
+        <v>3207</v>
       </c>
       <c r="F16" s="9">
-        <v>21271</v>
+        <v>21276</v>
       </c>
       <c r="G16" s="9">
-        <v>4289</v>
+        <v>4291</v>
       </c>
       <c r="H16" s="9">
         <v>252</v>
       </c>
       <c r="I16" s="9">
-        <v>374938</v>
+        <v>375009</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C17" s="9">
-        <v>199356</v>
+        <v>199393</v>
       </c>
       <c r="D17" s="9">
         <v>4869</v>
@@ -2478,33 +2484,33 @@
         <v>10349</v>
       </c>
       <c r="G17" s="9">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H17" s="9">
         <v>398</v>
       </c>
       <c r="I17" s="9">
-        <v>204225</v>
+        <v>204262</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C18" s="9">
-        <v>251515</v>
+        <v>251550</v>
       </c>
       <c r="D18" s="9">
-        <v>5476</v>
+        <v>5477</v>
       </c>
       <c r="E18" s="9">
         <v>2674</v>
       </c>
       <c r="F18" s="9">
-        <v>14378</v>
+        <v>14381</v>
       </c>
       <c r="G18" s="9">
         <v>2406</v>
@@ -2513,18 +2519,18 @@
         <v>495</v>
       </c>
       <c r="I18" s="9">
-        <v>256991</v>
+        <v>257027</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C19" s="9">
-        <v>139875</v>
+        <v>139898</v>
       </c>
       <c r="D19" s="9">
         <v>1706</v>
@@ -2542,94 +2548,94 @@
         <v>233</v>
       </c>
       <c r="I19" s="9">
-        <v>141581</v>
+        <v>141604</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C20" s="9">
-        <v>687617</v>
+        <v>691567</v>
       </c>
       <c r="D20" s="9">
-        <v>7704</v>
+        <v>7702</v>
       </c>
       <c r="E20" s="9">
-        <v>4011</v>
+        <v>4029</v>
       </c>
       <c r="F20" s="9">
-        <v>19169</v>
+        <v>19264</v>
       </c>
       <c r="G20" s="9">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="H20" s="9">
         <v>710</v>
       </c>
       <c r="I20" s="9">
-        <v>695321</v>
+        <v>699269</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9">
-        <v>138479</v>
+        <v>138732</v>
       </c>
       <c r="D21" s="9">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="E21" s="9">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F21" s="9">
         <v>5956</v>
       </c>
       <c r="G21" s="9">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H21" s="9">
         <v>775</v>
       </c>
       <c r="I21" s="9">
-        <v>139692</v>
+        <v>139943</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C22" s="12">
-        <v>7214680</v>
+        <v>7224601</v>
       </c>
       <c r="D22" s="12">
-        <v>117846</v>
+        <v>117902</v>
       </c>
       <c r="E22" s="12">
-        <v>76949</v>
+        <v>77017</v>
       </c>
       <c r="F22" s="12">
-        <v>382075</v>
+        <v>382404</v>
       </c>
       <c r="G22" s="12">
-        <v>62850</v>
+        <v>62889</v>
       </c>
       <c r="H22" s="12">
-        <v>9846</v>
+        <v>9845</v>
       </c>
       <c r="I22" s="12">
-        <v>7332526</v>
+        <v>7342503</v>
       </c>
     </row>
   </sheetData>
@@ -2657,7 +2663,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2683,16 +2689,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2723,13 +2729,13 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>1450</v>
+        <v>1464</v>
       </c>
       <c r="D6" s="6">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F6" s="6">
         <v>4</v>
@@ -2749,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F7" s="9">
         <v>0</v>
@@ -2763,13 +2769,13 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D8" s="9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F8" s="9">
         <v>1</v>
@@ -2783,13 +2789,13 @@
         <v>59</v>
       </c>
       <c r="C9" s="9">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D9" s="9">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F9" s="9">
         <v>1</v>
@@ -2797,10 +2803,10 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" s="9">
         <v>160</v>
@@ -2809,7 +2815,7 @@
         <v>40</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -2817,19 +2823,19 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" s="9">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D11" s="9">
         <v>107</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
@@ -2837,19 +2843,19 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C12" s="9">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" s="9">
         <v>40</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F12" s="9">
         <v>1</v>
@@ -2857,19 +2863,19 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C13" s="9">
         <v>74</v>
       </c>
       <c r="D13" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
@@ -2877,10 +2883,10 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" s="9">
         <v>101</v>
@@ -2889,7 +2895,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -2897,19 +2903,19 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="9">
         <v>152</v>
       </c>
       <c r="D15" s="9">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F15" s="9">
         <v>0</v>
@@ -2917,19 +2923,19 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C16" s="9">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D16" s="9">
         <v>33</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
@@ -2937,10 +2943,10 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C17" s="9">
         <v>30</v>
@@ -2949,7 +2955,7 @@
         <v>19</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F17" s="9">
         <v>1</v>
@@ -2957,10 +2963,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C18" s="9">
         <v>63</v>
@@ -2969,7 +2975,7 @@
         <v>62</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
@@ -2977,10 +2983,10 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C19" s="9">
         <v>20</v>
@@ -2989,7 +2995,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F19" s="9">
         <v>0</v>
@@ -2997,19 +3003,19 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C20" s="9">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D20" s="9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -3017,19 +3023,19 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21" s="9">
         <v>68</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F21" s="9">
         <v>0</v>
@@ -3037,19 +3043,19 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C22" s="12">
-        <v>1450</v>
+        <v>1464</v>
       </c>
       <c r="D22" s="12">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F22" s="12">
         <v>4</v>

--- a/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="174">
   <si>
     <t>PROGRES PEMUTAKHIRAN KELUARGA - KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 8 Sep 2026, 06.16 | Dicetak: 8 Sep 2026, 07.17</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 9 Sep 2026, 06.16 | Dicetak: 9 Sep 2026, 08.15</t>
   </si>
   <si>
     <t>Kode</t>
@@ -123,22 +123,22 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>74,48</t>
-  </si>
-  <si>
-    <t>1,87</t>
+    <t>74,58</t>
+  </si>
+  <si>
+    <t>1,88</t>
   </si>
   <si>
     <t>0,06</t>
   </si>
   <si>
-    <t>22,94</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>87,87</t>
+    <t>22,95</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>88,02</t>
   </si>
   <si>
     <t>1801</t>
@@ -171,7 +171,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>79,55</t>
+    <t>79,57</t>
   </si>
   <si>
     <t>1,06</t>
@@ -180,13 +180,10 @@
     <t>0,05</t>
   </si>
   <si>
-    <t>19,11</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>97,37</t>
+    <t>19,1</t>
+  </si>
+  <si>
+    <t>97,4</t>
   </si>
   <si>
     <t>1803</t>
@@ -195,226 +192,226 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>74,52</t>
+    <t>74,71</t>
   </si>
   <si>
     <t>1,32</t>
   </si>
   <si>
+    <t>22,98</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>89,79</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>77,67</t>
+  </si>
+  <si>
+    <t>1,98</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>88,24</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>76,39</t>
+  </si>
+  <si>
+    <t>2,86</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>20,08</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>86,64</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>71,03</t>
+  </si>
+  <si>
+    <t>1,97</t>
+  </si>
+  <si>
+    <t>26,84</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>83,77</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>78,09</t>
+  </si>
+  <si>
+    <t>1,78</t>
+  </si>
+  <si>
+    <t>19,72</t>
+  </si>
+  <si>
+    <t>92,18</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>70,58</t>
+  </si>
+  <si>
+    <t>2,31</t>
+  </si>
+  <si>
+    <t>27,6</t>
+  </si>
+  <si>
+    <t>84,79</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>75,76</t>
+  </si>
+  <si>
+    <t>3,06</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>21,64</t>
+  </si>
+  <si>
+    <t>90,85</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>81,28</t>
+  </si>
+  <si>
+    <t>1,53</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>17,36</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>92,07</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>74,78</t>
+  </si>
+  <si>
+    <t>1,58</t>
+  </si>
+  <si>
+    <t>24,55</t>
+  </si>
+  <si>
+    <t>91,67</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>74,76</t>
+  </si>
+  <si>
+    <t>2,44</t>
+  </si>
+  <si>
     <t>22,93</t>
   </si>
   <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>89,54</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>77,59</t>
-  </si>
-  <si>
-    <t>1,98</t>
-  </si>
-  <si>
-    <t>20,01</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>88,13</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>76,35</t>
-  </si>
-  <si>
-    <t>2,86</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>20,08</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>86,59</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>71,02</t>
-  </si>
-  <si>
-    <t>1,97</t>
-  </si>
-  <si>
-    <t>26,83</t>
-  </si>
-  <si>
-    <t>83,75</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>78,05</t>
-  </si>
-  <si>
-    <t>1,78</t>
-  </si>
-  <si>
-    <t>19,7</t>
-  </si>
-  <si>
-    <t>92,12</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>70,44</t>
-  </si>
-  <si>
-    <t>2,31</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>27,61</t>
-  </si>
-  <si>
-    <t>84,6</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>75,72</t>
-  </si>
-  <si>
-    <t>3,07</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>21,66</t>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>87,92</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>82,91</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>17,06</t>
   </si>
   <si>
     <t>0,07</t>
   </si>
   <si>
-    <t>90,73</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>81,26</t>
-  </si>
-  <si>
-    <t>1,53</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>17,36</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>92,02</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>74,77</t>
-  </si>
-  <si>
-    <t>1,58</t>
-  </si>
-  <si>
-    <t>24,56</t>
-  </si>
-  <si>
-    <t>91,62</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>74,75</t>
-  </si>
-  <si>
-    <t>2,42</t>
-  </si>
-  <si>
-    <t>22,96</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>87,9</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>82,91</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>17,06</t>
-  </si>
-  <si>
-    <t>101,84</t>
+    <t>101,85</t>
   </si>
   <si>
     <t>1871</t>
@@ -423,19 +420,19 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>59,46</t>
-  </si>
-  <si>
-    <t>0,95</t>
-  </si>
-  <si>
-    <t>35,41</t>
+    <t>59,83</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>35,54</t>
   </si>
   <si>
     <t>0,22</t>
   </si>
   <si>
-    <t>75,69</t>
+    <t>76,25</t>
   </si>
   <si>
     <t>1872</t>
@@ -444,16 +441,13 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>74,05</t>
+    <t>74,24</t>
   </si>
   <si>
     <t>1,51</t>
   </si>
   <si>
-    <t>24,11</t>
-  </si>
-  <si>
-    <t>86,25</t>
+    <t>24,12</t>
   </si>
   <si>
     <t/>
@@ -495,37 +489,37 @@
     <t>Jumlah Bangunan Keluarga Khusus Berpindah-pindah Didata (K2)</t>
   </si>
   <si>
-    <t>45,22</t>
+    <t>48,74</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>15,38</t>
-  </si>
-  <si>
-    <t>46,74</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>55,98</t>
+  </si>
+  <si>
+    <t>34,38</t>
   </si>
   <si>
     <t>48,2</t>
   </si>
   <si>
-    <t>75,47</t>
-  </si>
-  <si>
-    <t>28,38</t>
-  </si>
-  <si>
-    <t>15,84</t>
+    <t>74,07</t>
+  </si>
+  <si>
+    <t>31,51</t>
+  </si>
+  <si>
+    <t>16,83</t>
   </si>
   <si>
     <t>80,26</t>
   </si>
   <si>
-    <t>38,82</t>
+    <t>55,95</t>
   </si>
   <si>
     <t>63,33</t>
@@ -537,10 +531,10 @@
     <t>75</t>
   </si>
   <si>
-    <t>13,55</t>
-  </si>
-  <si>
-    <t>88,31</t>
+    <t>14,1</t>
+  </si>
+  <si>
+    <t>91,03</t>
   </si>
 </sst>
 </file>
@@ -1201,40 +1195,40 @@
         <v>2730939</v>
       </c>
       <c r="D6" s="6">
-        <v>2033929</v>
+        <v>2036674</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="6">
-        <v>365798</v>
+        <v>367101</v>
       </c>
       <c r="G6" s="6">
-        <v>51177</v>
+        <v>51206</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="6">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="6">
-        <v>626419</v>
+        <v>626877</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="6">
-        <v>5355</v>
+        <v>5281</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="6">
-        <v>2399727</v>
+        <v>2403775</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>41</v>
@@ -1301,16 +1295,16 @@
         <v>172957</v>
       </c>
       <c r="D8" s="9">
-        <v>137582</v>
+        <v>137619</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="9">
-        <v>30822</v>
+        <v>30839</v>
       </c>
       <c r="G8" s="9">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>53</v>
@@ -1322,7 +1316,7 @@
         <v>54</v>
       </c>
       <c r="K8" s="9">
-        <v>33057</v>
+        <v>33034</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>55</v>
@@ -1331,39 +1325,39 @@
         <v>335</v>
       </c>
       <c r="N8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" s="9">
+        <v>168458</v>
+      </c>
+      <c r="P8" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="O8" s="9">
-        <v>168404</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="C9" s="9">
         <v>342736</v>
       </c>
       <c r="D9" s="9">
-        <v>255391</v>
+        <v>256072</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="9">
+        <v>51682</v>
+      </c>
+      <c r="G9" s="9">
+        <v>4513</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>60</v>
-      </c>
-      <c r="F9" s="9">
-        <v>51501</v>
-      </c>
-      <c r="G9" s="9">
-        <v>4509</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>61</v>
       </c>
       <c r="I9" s="9">
         <v>215</v>
@@ -1372,48 +1366,48 @@
         <v>38</v>
       </c>
       <c r="K9" s="9">
-        <v>78606</v>
+        <v>78767</v>
       </c>
       <c r="L9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="9">
+        <v>706</v>
+      </c>
+      <c r="N9" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="M9" s="9">
-        <v>705</v>
-      </c>
-      <c r="N9" s="10" t="s">
+      <c r="O9" s="9">
+        <v>307754</v>
+      </c>
+      <c r="P9" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="O9" s="9">
-        <v>306892</v>
-      </c>
-      <c r="P9" s="10" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="C10" s="9">
         <v>362841</v>
       </c>
       <c r="D10" s="9">
-        <v>281516</v>
+        <v>281801</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="9">
+        <v>38361</v>
+      </c>
+      <c r="G10" s="9">
+        <v>7199</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="F10" s="9">
-        <v>38240</v>
-      </c>
-      <c r="G10" s="9">
-        <v>7198</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>68</v>
       </c>
       <c r="I10" s="9">
         <v>215</v>
@@ -1422,98 +1416,98 @@
         <v>38</v>
       </c>
       <c r="K10" s="9">
-        <v>72591</v>
+        <v>72586</v>
       </c>
       <c r="L10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10" s="9">
+        <v>553</v>
+      </c>
+      <c r="N10" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="9">
-        <v>562</v>
-      </c>
-      <c r="N10" s="10" t="s">
+      <c r="O10" s="9">
+        <v>320162</v>
+      </c>
+      <c r="P10" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="O10" s="9">
-        <v>319756</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="C11" s="9">
         <v>449576</v>
       </c>
       <c r="D11" s="9">
-        <v>343237</v>
+        <v>343450</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="9">
+        <v>46078</v>
+      </c>
+      <c r="G11" s="9">
+        <v>12848</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="F11" s="9">
-        <v>46036</v>
-      </c>
-      <c r="G11" s="9">
-        <v>12844</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>75</v>
       </c>
       <c r="I11" s="9">
         <v>408</v>
       </c>
       <c r="J11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="9">
+        <v>90257</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="K11" s="9">
-        <v>90263</v>
-      </c>
-      <c r="L11" s="10" t="s">
+      <c r="M11" s="9">
+        <v>1586</v>
+      </c>
+      <c r="N11" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="M11" s="9">
-        <v>1571</v>
-      </c>
-      <c r="N11" s="10" t="s">
+      <c r="O11" s="9">
+        <v>389528</v>
+      </c>
+      <c r="P11" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="O11" s="9">
-        <v>389273</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="C12" s="9">
         <v>199396</v>
       </c>
       <c r="D12" s="9">
-        <v>141611</v>
+        <v>141640</v>
       </c>
       <c r="E12" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="9">
+        <v>25396</v>
+      </c>
+      <c r="G12" s="9">
+        <v>3932</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="F12" s="9">
-        <v>25388</v>
-      </c>
-      <c r="G12" s="9">
-        <v>3930</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="I12" s="9">
         <v>61</v>
@@ -1522,19 +1516,19 @@
         <v>46</v>
       </c>
       <c r="K12" s="9">
-        <v>53507</v>
+        <v>53521</v>
       </c>
       <c r="L12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M12" s="9">
+        <v>232</v>
+      </c>
+      <c r="N12" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="M12" s="9">
-        <v>300</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="O12" s="9">
-        <v>166999</v>
+        <v>167036</v>
       </c>
       <c r="P12" s="10" t="s">
         <v>85</v>
@@ -1551,13 +1545,13 @@
         <v>146092</v>
       </c>
       <c r="D13" s="9">
-        <v>114027</v>
+        <v>114088</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>88</v>
       </c>
       <c r="F13" s="9">
-        <v>20560</v>
+        <v>20576</v>
       </c>
       <c r="G13" s="9">
         <v>2595</v>
@@ -1572,19 +1566,19 @@
         <v>38</v>
       </c>
       <c r="K13" s="9">
-        <v>28774</v>
+        <v>28806</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>90</v>
       </c>
       <c r="M13" s="9">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="O13" s="9">
-        <v>134587</v>
+        <v>134664</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>91</v>
@@ -1601,13 +1595,13 @@
         <v>135256</v>
       </c>
       <c r="D14" s="9">
-        <v>95277</v>
+        <v>95470</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>94</v>
       </c>
       <c r="F14" s="9">
-        <v>19149</v>
+        <v>19216</v>
       </c>
       <c r="G14" s="9">
         <v>3131</v>
@@ -1616,236 +1610,236 @@
         <v>95</v>
       </c>
       <c r="I14" s="9">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="9">
+        <v>37329</v>
+      </c>
+      <c r="L14" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="K14" s="9">
-        <v>37341</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>97</v>
-      </c>
       <c r="M14" s="9">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N14" s="10" t="s">
         <v>54</v>
       </c>
       <c r="O14" s="9">
-        <v>114426</v>
+        <v>114686</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="C15" s="9">
         <v>152158</v>
       </c>
       <c r="D15" s="9">
-        <v>115213</v>
+        <v>115280</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="9">
+        <v>22949</v>
+      </c>
+      <c r="G15" s="9">
+        <v>4663</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F15" s="9">
-        <v>22836</v>
-      </c>
-      <c r="G15" s="9">
-        <v>4666</v>
-      </c>
-      <c r="H15" s="10" t="s">
+      <c r="I15" s="9">
+        <v>61</v>
+      </c>
+      <c r="J15" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="I15" s="9">
-        <v>64</v>
-      </c>
-      <c r="J15" s="10" t="s">
+      <c r="K15" s="9">
+        <v>32920</v>
+      </c>
+      <c r="L15" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="K15" s="9">
-        <v>32960</v>
-      </c>
-      <c r="L15" s="10" t="s">
+      <c r="M15" s="9">
+        <v>90</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="O15" s="9">
+        <v>138229</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="M15" s="9">
-        <v>99</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="O15" s="9">
-        <v>138049</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9">
         <v>135741</v>
       </c>
       <c r="D16" s="9">
-        <v>110305</v>
+        <v>110329</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F16" s="9">
-        <v>14604</v>
+        <v>14645</v>
       </c>
       <c r="G16" s="9">
         <v>2073</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I16" s="9">
         <v>109</v>
       </c>
       <c r="J16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" s="9">
+        <v>23561</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="M16" s="9">
+        <v>344</v>
+      </c>
+      <c r="N16" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K16" s="9">
-        <v>23563</v>
-      </c>
-      <c r="L16" s="10" t="s">
+      <c r="O16" s="9">
+        <v>124974</v>
+      </c>
+      <c r="P16" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="M16" s="9">
-        <v>331</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="O16" s="9">
-        <v>124909</v>
-      </c>
-      <c r="P16" s="10" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C17" s="9">
         <v>75116</v>
       </c>
       <c r="D17" s="9">
-        <v>56161</v>
+        <v>56172</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F17" s="9">
-        <v>12657</v>
+        <v>12687</v>
       </c>
       <c r="G17" s="9">
         <v>1188</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I17" s="9">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K17" s="9">
-        <v>18448</v>
+        <v>18439</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M17" s="9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N17" s="10" t="s">
         <v>54</v>
       </c>
       <c r="O17" s="9">
-        <v>68818</v>
+        <v>68859</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18" s="9">
         <v>99169</v>
       </c>
       <c r="D18" s="9">
-        <v>74128</v>
+        <v>74139</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F18" s="9">
-        <v>13043</v>
+        <v>13054</v>
       </c>
       <c r="G18" s="9">
-        <v>2402</v>
+        <v>2416</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I18" s="9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>54</v>
       </c>
       <c r="K18" s="9">
-        <v>22770</v>
+        <v>22737</v>
       </c>
       <c r="L18" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="M18" s="9">
+        <v>290</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="O18" s="9">
+        <v>87193</v>
+      </c>
+      <c r="P18" s="10" t="s">
         <v>125</v>
-      </c>
-      <c r="M18" s="9">
-        <v>282</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="O18" s="9">
-        <v>87171</v>
-      </c>
-      <c r="P18" s="10" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C19" s="9">
         <v>41772</v>
@@ -1854,16 +1848,16 @@
         <v>34635</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F19" s="9">
-        <v>7906</v>
+        <v>7908</v>
       </c>
       <c r="G19" s="9">
         <v>357</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I19" s="9">
         <v>27</v>
@@ -1875,95 +1869,95 @@
         <v>7126</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M19" s="9">
         <v>28</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="O19" s="9">
-        <v>42541</v>
+        <v>42543</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>135</v>
       </c>
       <c r="C20" s="9">
         <v>279478</v>
       </c>
       <c r="D20" s="9">
-        <v>166177</v>
+        <v>167211</v>
       </c>
       <c r="E20" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="9">
+        <v>45894</v>
+      </c>
+      <c r="G20" s="9">
+        <v>2675</v>
+      </c>
+      <c r="H20" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F20" s="9">
-        <v>45347</v>
-      </c>
-      <c r="G20" s="9">
-        <v>2669</v>
-      </c>
-      <c r="H20" s="10" t="s">
+      <c r="I20" s="9">
+        <v>184</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="K20" s="9">
+        <v>99339</v>
+      </c>
+      <c r="L20" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="I20" s="9">
-        <v>183</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="K20" s="9">
-        <v>98965</v>
-      </c>
-      <c r="L20" s="10" t="s">
+      <c r="M20" s="9">
+        <v>621</v>
+      </c>
+      <c r="N20" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="M20" s="9">
-        <v>624</v>
-      </c>
-      <c r="N20" s="10" t="s">
+      <c r="O20" s="9">
+        <v>213105</v>
+      </c>
+      <c r="P20" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="O20" s="9">
-        <v>211524</v>
-      </c>
-      <c r="P20" s="10" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>142</v>
       </c>
       <c r="C21" s="9">
         <v>53506</v>
       </c>
       <c r="D21" s="9">
-        <v>39622</v>
+        <v>39721</v>
       </c>
       <c r="E21" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="9">
+        <v>6636</v>
+      </c>
+      <c r="G21" s="9">
+        <v>807</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="F21" s="9">
-        <v>6529</v>
-      </c>
-      <c r="G21" s="9">
-        <v>808</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="I21" s="9">
         <v>51</v>
@@ -1972,69 +1966,69 @@
         <v>48</v>
       </c>
       <c r="K21" s="9">
-        <v>12899</v>
+        <v>12906</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M21" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="O21" s="9">
-        <v>46151</v>
+        <v>46357</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C22" s="12">
         <v>2730939</v>
       </c>
       <c r="D22" s="12">
-        <v>2033929</v>
+        <v>2036674</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="12">
-        <v>365798</v>
+        <v>367101</v>
       </c>
       <c r="G22" s="12">
-        <v>51177</v>
+        <v>51206</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="12">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="12">
-        <v>626419</v>
+        <v>626877</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="12">
-        <v>5355</v>
+        <v>5281</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="O22" s="12">
-        <v>2399727</v>
+        <v>2403775</v>
       </c>
       <c r="P22" s="13" t="s">
         <v>41</v>
@@ -2063,7 +2057,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2095,25 +2089,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2153,25 +2147,25 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>7224601</v>
+        <v>7236803</v>
       </c>
       <c r="D6" s="6">
-        <v>117902</v>
+        <v>117994</v>
       </c>
       <c r="E6" s="6">
-        <v>77017</v>
+        <v>77100</v>
       </c>
       <c r="F6" s="6">
-        <v>382404</v>
+        <v>382824</v>
       </c>
       <c r="G6" s="6">
-        <v>62889</v>
+        <v>62964</v>
       </c>
       <c r="H6" s="6">
-        <v>9845</v>
+        <v>9838</v>
       </c>
       <c r="I6" s="6">
-        <v>7342503</v>
+        <v>7354797</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2211,141 +2205,141 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>514802</v>
+        <v>514964</v>
       </c>
       <c r="D8" s="9">
-        <v>6558</v>
+        <v>6560</v>
       </c>
       <c r="E8" s="9">
-        <v>5002</v>
+        <v>5008</v>
       </c>
       <c r="F8" s="9">
-        <v>38742</v>
+        <v>38750</v>
       </c>
       <c r="G8" s="9">
-        <v>4556</v>
+        <v>4560</v>
       </c>
       <c r="H8" s="9">
         <v>524</v>
       </c>
       <c r="I8" s="9">
-        <v>521360</v>
+        <v>521524</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="C9" s="9">
-        <v>939052</v>
+        <v>941856</v>
       </c>
       <c r="D9" s="9">
-        <v>15387</v>
+        <v>15398</v>
       </c>
       <c r="E9" s="9">
-        <v>10548</v>
+        <v>10564</v>
       </c>
       <c r="F9" s="9">
-        <v>44917</v>
+        <v>44999</v>
       </c>
       <c r="G9" s="9">
-        <v>5530</v>
+        <v>5534</v>
       </c>
       <c r="H9" s="9">
-        <v>1134</v>
+        <v>1127</v>
       </c>
       <c r="I9" s="9">
-        <v>954439</v>
+        <v>957254</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>66</v>
-      </c>
       <c r="C10" s="9">
-        <v>907883</v>
+        <v>909074</v>
       </c>
       <c r="D10" s="9">
-        <v>16668</v>
+        <v>16680</v>
       </c>
       <c r="E10" s="9">
-        <v>10659</v>
+        <v>10669</v>
       </c>
       <c r="F10" s="9">
-        <v>44077</v>
+        <v>44135</v>
       </c>
       <c r="G10" s="9">
-        <v>22666</v>
+        <v>22696</v>
       </c>
       <c r="H10" s="9">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="I10" s="9">
-        <v>924551</v>
+        <v>925754</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>73</v>
-      </c>
       <c r="C11" s="9">
-        <v>1140540</v>
+        <v>1141264</v>
       </c>
       <c r="D11" s="9">
-        <v>21603</v>
+        <v>21615</v>
       </c>
       <c r="E11" s="9">
-        <v>13422</v>
+        <v>13430</v>
       </c>
       <c r="F11" s="9">
-        <v>50467</v>
+        <v>50507</v>
       </c>
       <c r="G11" s="9">
-        <v>9068</v>
+        <v>9072</v>
       </c>
       <c r="H11" s="9">
         <v>1870</v>
       </c>
       <c r="I11" s="9">
-        <v>1162143</v>
+        <v>1162879</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="C12" s="9">
-        <v>518754</v>
+        <v>518841</v>
       </c>
       <c r="D12" s="9">
-        <v>6353</v>
+        <v>6356</v>
       </c>
       <c r="E12" s="9">
-        <v>6168</v>
+        <v>6171</v>
       </c>
       <c r="F12" s="9">
-        <v>29370</v>
+        <v>29379</v>
       </c>
       <c r="G12" s="9">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="H12" s="9">
         <v>521</v>
       </c>
       <c r="I12" s="9">
-        <v>525107</v>
+        <v>525197</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2356,25 +2350,25 @@
         <v>87</v>
       </c>
       <c r="C13" s="9">
-        <v>404239</v>
+        <v>404452</v>
       </c>
       <c r="D13" s="9">
-        <v>4805</v>
+        <v>4808</v>
       </c>
       <c r="E13" s="9">
-        <v>4519</v>
+        <v>4518</v>
       </c>
       <c r="F13" s="9">
-        <v>28965</v>
+        <v>28987</v>
       </c>
       <c r="G13" s="9">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="H13" s="9">
         <v>487</v>
       </c>
       <c r="I13" s="9">
-        <v>409044</v>
+        <v>409260</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2385,103 +2379,103 @@
         <v>93</v>
       </c>
       <c r="C14" s="9">
-        <v>340356</v>
+        <v>341140</v>
       </c>
       <c r="D14" s="9">
-        <v>9576</v>
+        <v>9570</v>
       </c>
       <c r="E14" s="9">
-        <v>3685</v>
+        <v>3694</v>
       </c>
       <c r="F14" s="9">
-        <v>22585</v>
+        <v>22637</v>
       </c>
       <c r="G14" s="9">
-        <v>2235</v>
+        <v>2241</v>
       </c>
       <c r="H14" s="9">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I14" s="9">
-        <v>349932</v>
+        <v>350710</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="C15" s="9">
-        <v>416323</v>
+        <v>416822</v>
       </c>
       <c r="D15" s="9">
-        <v>7900</v>
+        <v>7906</v>
       </c>
       <c r="E15" s="9">
-        <v>6742</v>
+        <v>6746</v>
       </c>
       <c r="F15" s="9">
-        <v>28113</v>
+        <v>28136</v>
       </c>
       <c r="G15" s="9">
-        <v>4064</v>
+        <v>4071</v>
       </c>
       <c r="H15" s="9">
         <v>518</v>
       </c>
       <c r="I15" s="9">
-        <v>424223</v>
+        <v>424728</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9">
-        <v>369851</v>
+        <v>369952</v>
       </c>
       <c r="D16" s="9">
-        <v>5158</v>
+        <v>5159</v>
       </c>
       <c r="E16" s="9">
         <v>3207</v>
       </c>
       <c r="F16" s="9">
-        <v>21276</v>
+        <v>21278</v>
       </c>
       <c r="G16" s="9">
-        <v>4291</v>
+        <v>4295</v>
       </c>
       <c r="H16" s="9">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I16" s="9">
-        <v>375009</v>
+        <v>375111</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C17" s="9">
-        <v>199393</v>
+        <v>199517</v>
       </c>
       <c r="D17" s="9">
-        <v>4869</v>
+        <v>4871</v>
       </c>
       <c r="E17" s="9">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="F17" s="9">
-        <v>10349</v>
+        <v>10350</v>
       </c>
       <c r="G17" s="9">
         <v>1727</v>
@@ -2490,47 +2484,47 @@
         <v>398</v>
       </c>
       <c r="I17" s="9">
-        <v>204262</v>
+        <v>204388</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18" s="9">
-        <v>251550</v>
+        <v>251606</v>
       </c>
       <c r="D18" s="9">
-        <v>5477</v>
+        <v>5481</v>
       </c>
       <c r="E18" s="9">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="F18" s="9">
-        <v>14381</v>
+        <v>14384</v>
       </c>
       <c r="G18" s="9">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="H18" s="9">
         <v>495</v>
       </c>
       <c r="I18" s="9">
-        <v>257027</v>
+        <v>257087</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C19" s="9">
-        <v>139898</v>
+        <v>139900</v>
       </c>
       <c r="D19" s="9">
         <v>1706</v>
@@ -2539,7 +2533,7 @@
         <v>1062</v>
       </c>
       <c r="F19" s="9">
-        <v>10576</v>
+        <v>10578</v>
       </c>
       <c r="G19" s="9">
         <v>226</v>
@@ -2548,94 +2542,94 @@
         <v>233</v>
       </c>
       <c r="I19" s="9">
-        <v>141604</v>
+        <v>141606</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>135</v>
-      </c>
       <c r="C20" s="9">
-        <v>691567</v>
+        <v>696497</v>
       </c>
       <c r="D20" s="9">
-        <v>7702</v>
+        <v>7740</v>
       </c>
       <c r="E20" s="9">
-        <v>4029</v>
+        <v>4052</v>
       </c>
       <c r="F20" s="9">
-        <v>19264</v>
+        <v>19364</v>
       </c>
       <c r="G20" s="9">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="H20" s="9">
         <v>710</v>
       </c>
       <c r="I20" s="9">
-        <v>699269</v>
+        <v>704237</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>142</v>
-      </c>
       <c r="C21" s="9">
-        <v>138732</v>
+        <v>139257</v>
       </c>
       <c r="D21" s="9">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="E21" s="9">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="F21" s="9">
-        <v>5956</v>
+        <v>5974</v>
       </c>
       <c r="G21" s="9">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="H21" s="9">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="I21" s="9">
-        <v>139943</v>
+        <v>140472</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C22" s="12">
-        <v>7224601</v>
+        <v>7236803</v>
       </c>
       <c r="D22" s="12">
-        <v>117902</v>
+        <v>117994</v>
       </c>
       <c r="E22" s="12">
-        <v>77017</v>
+        <v>77100</v>
       </c>
       <c r="F22" s="12">
-        <v>382404</v>
+        <v>382824</v>
       </c>
       <c r="G22" s="12">
-        <v>62889</v>
+        <v>62964</v>
       </c>
       <c r="H22" s="12">
-        <v>9845</v>
+        <v>9838</v>
       </c>
       <c r="I22" s="12">
-        <v>7342503</v>
+        <v>7354797</v>
       </c>
     </row>
   </sheetData>
@@ -2663,7 +2657,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2689,16 +2683,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2729,13 +2723,13 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="D6" s="6">
-        <v>662</v>
+        <v>715</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F6" s="6">
         <v>4</v>
@@ -2755,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F7" s="9">
         <v>0</v>
@@ -2769,13 +2763,13 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" s="9">
         <v>12</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F8" s="9">
         <v>1</v>
@@ -2783,19 +2777,19 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="C9" s="9">
         <v>184</v>
       </c>
       <c r="D9" s="9">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F9" s="9">
         <v>1</v>
@@ -2803,19 +2797,19 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="C10" s="9">
         <v>160</v>
       </c>
       <c r="D10" s="9">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -2823,10 +2817,10 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="C11" s="9">
         <v>222</v>
@@ -2835,7 +2829,7 @@
         <v>107</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
@@ -2843,19 +2837,19 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="C12" s="9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="9">
         <v>40</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F12" s="9">
         <v>1</v>
@@ -2869,13 +2863,13 @@
         <v>87</v>
       </c>
       <c r="C13" s="9">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" s="9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
@@ -2892,10 +2886,10 @@
         <v>101</v>
       </c>
       <c r="D14" s="9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -2903,10 +2897,10 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="C15" s="9">
         <v>152</v>
@@ -2915,7 +2909,7 @@
         <v>122</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F15" s="9">
         <v>0</v>
@@ -2923,19 +2917,19 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D16" s="9">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
@@ -2943,10 +2937,10 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C17" s="9">
         <v>30</v>
@@ -2955,7 +2949,7 @@
         <v>19</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F17" s="9">
         <v>1</v>
@@ -2963,10 +2957,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18" s="9">
         <v>63</v>
@@ -2975,7 +2969,7 @@
         <v>62</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
@@ -2983,10 +2977,10 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C19" s="9">
         <v>20</v>
@@ -2995,7 +2989,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F19" s="9">
         <v>0</v>
@@ -3003,19 +2997,19 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>135</v>
-      </c>
       <c r="C20" s="9">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D20" s="9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -3023,19 +3017,19 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>142</v>
-      </c>
       <c r="C21" s="9">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D21" s="9">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F21" s="9">
         <v>0</v>
@@ -3043,19 +3037,19 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C22" s="12">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="D22" s="12">
-        <v>662</v>
+        <v>715</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F22" s="12">
         <v>4</v>

--- a/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="176">
   <si>
     <t>PROGRES PEMUTAKHIRAN KELUARGA - KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 9 Sep 2026, 06.16 | Dicetak: 9 Sep 2026, 08.15</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 10 Sep 2026, 06.16 | Dicetak: 10 Sep 2026, 08.07</t>
   </si>
   <si>
     <t>Kode</t>
@@ -123,7 +123,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>74,58</t>
+    <t>74,68</t>
   </si>
   <si>
     <t>1,88</t>
@@ -132,163 +132,166 @@
     <t>0,06</t>
   </si>
   <si>
-    <t>22,95</t>
+    <t>22,98</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>88,16</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>81,09</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>18,26</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>94,22</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>79,56</t>
+  </si>
+  <si>
+    <t>1,06</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>19,09</t>
+  </si>
+  <si>
+    <t>97,41</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>74,89</t>
+  </si>
+  <si>
+    <t>1,32</t>
+  </si>
+  <si>
+    <t>23,02</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>77,7</t>
+  </si>
+  <si>
+    <t>1,99</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>88,3</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>76,43</t>
+  </si>
+  <si>
+    <t>2,85</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>20,08</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>86,69</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>71,04</t>
+  </si>
+  <si>
+    <t>1,97</t>
+  </si>
+  <si>
+    <t>26,85</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>83,78</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>78,17</t>
+  </si>
+  <si>
+    <t>1,78</t>
+  </si>
+  <si>
+    <t>19,73</t>
   </si>
   <si>
     <t>0,19</t>
   </si>
   <si>
-    <t>88,02</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>81,09</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>18,26</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>94,22</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>79,57</t>
-  </si>
-  <si>
-    <t>1,06</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>19,1</t>
-  </si>
-  <si>
-    <t>97,4</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>74,71</t>
-  </si>
-  <si>
-    <t>1,32</t>
-  </si>
-  <si>
-    <t>22,98</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>89,79</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>77,67</t>
-  </si>
-  <si>
-    <t>1,98</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>88,24</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>76,39</t>
-  </si>
-  <si>
-    <t>2,86</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>20,08</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>86,64</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>71,03</t>
-  </si>
-  <si>
-    <t>1,97</t>
-  </si>
-  <si>
-    <t>26,84</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>83,77</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>78,09</t>
-  </si>
-  <si>
-    <t>1,78</t>
-  </si>
-  <si>
-    <t>19,72</t>
-  </si>
-  <si>
-    <t>92,18</t>
+    <t>92,26</t>
   </si>
   <si>
     <t>1808</t>
@@ -297,16 +300,16 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>70,58</t>
-  </si>
-  <si>
-    <t>2,31</t>
-  </si>
-  <si>
-    <t>27,6</t>
-  </si>
-  <si>
-    <t>84,79</t>
+    <t>70,71</t>
+  </si>
+  <si>
+    <t>2,32</t>
+  </si>
+  <si>
+    <t>27,63</t>
+  </si>
+  <si>
+    <t>84,96</t>
   </si>
   <si>
     <t>1809</t>
@@ -315,7 +318,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>75,76</t>
+    <t>75,78</t>
   </si>
   <si>
     <t>3,06</t>
@@ -327,7 +330,7 @@
     <t>21,64</t>
   </si>
   <si>
-    <t>90,85</t>
+    <t>90,87</t>
   </si>
   <si>
     <t>1810</t>
@@ -348,91 +351,91 @@
     <t>17,36</t>
   </si>
   <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>92,16</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>74,8</t>
+  </si>
+  <si>
+    <t>1,58</t>
+  </si>
+  <si>
+    <t>24,54</t>
+  </si>
+  <si>
+    <t>91,75</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>74,77</t>
+  </si>
+  <si>
+    <t>2,44</t>
+  </si>
+  <si>
+    <t>22,92</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>87,94</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>82,91</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>17,06</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>101,85</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>60,33</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>35,71</t>
+  </si>
+  <si>
     <t>0,25</t>
   </si>
   <si>
-    <t>92,07</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>74,78</t>
-  </si>
-  <si>
-    <t>1,58</t>
-  </si>
-  <si>
-    <t>24,55</t>
-  </si>
-  <si>
-    <t>91,67</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>74,76</t>
-  </si>
-  <si>
-    <t>2,44</t>
-  </si>
-  <si>
-    <t>22,93</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>87,92</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>82,91</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>17,06</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>101,85</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>59,83</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>35,54</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>76,25</t>
+    <t>76,95</t>
   </si>
   <si>
     <t>1872</t>
@@ -441,13 +444,16 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>74,24</t>
+    <t>74,35</t>
   </si>
   <si>
     <t>1,51</t>
   </si>
   <si>
-    <t>24,12</t>
+    <t>24,07</t>
+  </si>
+  <si>
+    <t>86,89</t>
   </si>
   <si>
     <t/>
@@ -489,40 +495,40 @@
     <t>Jumlah Bangunan Keluarga Khusus Berpindah-pindah Didata (K2)</t>
   </si>
   <si>
-    <t>48,74</t>
+    <t>49,15</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>55,98</t>
-  </si>
-  <si>
-    <t>34,38</t>
-  </si>
-  <si>
-    <t>48,2</t>
+    <t>14,12</t>
+  </si>
+  <si>
+    <t>55,68</t>
+  </si>
+  <si>
+    <t>36,65</t>
+  </si>
+  <si>
+    <t>47,98</t>
   </si>
   <si>
     <t>74,07</t>
   </si>
   <si>
-    <t>31,51</t>
-  </si>
-  <si>
-    <t>16,83</t>
+    <t>31,08</t>
+  </si>
+  <si>
+    <t>17,82</t>
   </si>
   <si>
     <t>80,26</t>
   </si>
   <si>
-    <t>55,95</t>
-  </si>
-  <si>
-    <t>63,33</t>
+    <t>59,76</t>
+  </si>
+  <si>
+    <t>73,33</t>
   </si>
   <si>
     <t>98,41</t>
@@ -531,7 +537,7 @@
     <t>75</t>
   </si>
   <si>
-    <t>14,1</t>
+    <t>14,01</t>
   </si>
   <si>
     <t>91,03</t>
@@ -1195,40 +1201,40 @@
         <v>2730939</v>
       </c>
       <c r="D6" s="6">
-        <v>2036674</v>
+        <v>2039374</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="6">
-        <v>367101</v>
+        <v>368269</v>
       </c>
       <c r="G6" s="6">
-        <v>51206</v>
+        <v>51207</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="6">
-        <v>1768</v>
+        <v>1760</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="6">
-        <v>626877</v>
+        <v>627485</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="6">
-        <v>5281</v>
+        <v>5374</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="6">
-        <v>2403775</v>
+        <v>2407643</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>41</v>
@@ -1295,13 +1301,13 @@
         <v>172957</v>
       </c>
       <c r="D8" s="9">
-        <v>137619</v>
+        <v>137613</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="9">
-        <v>30839</v>
+        <v>30861</v>
       </c>
       <c r="G8" s="9">
         <v>1838</v>
@@ -1316,19 +1322,19 @@
         <v>54</v>
       </c>
       <c r="K8" s="9">
-        <v>33034</v>
+        <v>33016</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>55</v>
       </c>
       <c r="M8" s="9">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="N8" s="10" t="s">
         <v>40</v>
       </c>
       <c r="O8" s="9">
-        <v>168458</v>
+        <v>168474</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>56</v>
@@ -1345,16 +1351,16 @@
         <v>342736</v>
       </c>
       <c r="D9" s="9">
-        <v>256072</v>
+        <v>256665</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F9" s="9">
-        <v>51682</v>
+        <v>51784</v>
       </c>
       <c r="G9" s="9">
-        <v>4513</v>
+        <v>4516</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>60</v>
@@ -1366,19 +1372,19 @@
         <v>38</v>
       </c>
       <c r="K9" s="9">
-        <v>78767</v>
+        <v>78885</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>61</v>
       </c>
       <c r="M9" s="9">
-        <v>706</v>
+        <v>724</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>62</v>
       </c>
       <c r="O9" s="9">
-        <v>307754</v>
+        <v>308449</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>63</v>
@@ -1395,40 +1401,40 @@
         <v>362841</v>
       </c>
       <c r="D10" s="9">
-        <v>281801</v>
+        <v>281940</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>66</v>
       </c>
       <c r="F10" s="9">
-        <v>38361</v>
+        <v>38453</v>
       </c>
       <c r="G10" s="9">
-        <v>7199</v>
+        <v>7203</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>67</v>
       </c>
       <c r="I10" s="9">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>38</v>
       </c>
       <c r="K10" s="9">
-        <v>72586</v>
+        <v>72576</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>68</v>
       </c>
       <c r="M10" s="9">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="N10" s="10" t="s">
         <v>69</v>
       </c>
       <c r="O10" s="9">
-        <v>320162</v>
+        <v>320393</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>70</v>
@@ -1445,40 +1451,40 @@
         <v>449576</v>
       </c>
       <c r="D11" s="9">
-        <v>343450</v>
+        <v>343629</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>73</v>
       </c>
       <c r="F11" s="9">
-        <v>46078</v>
+        <v>46124</v>
       </c>
       <c r="G11" s="9">
-        <v>12848</v>
+        <v>12831</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>74</v>
       </c>
       <c r="I11" s="9">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>75</v>
       </c>
       <c r="K11" s="9">
-        <v>90257</v>
+        <v>90265</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>76</v>
       </c>
       <c r="M11" s="9">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>77</v>
       </c>
       <c r="O11" s="9">
-        <v>389528</v>
+        <v>389753</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>78</v>
@@ -1495,13 +1501,13 @@
         <v>199396</v>
       </c>
       <c r="D12" s="9">
-        <v>141640</v>
+        <v>141644</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>81</v>
       </c>
       <c r="F12" s="9">
-        <v>25396</v>
+        <v>25403</v>
       </c>
       <c r="G12" s="9">
         <v>3932</v>
@@ -1516,7 +1522,7 @@
         <v>46</v>
       </c>
       <c r="K12" s="9">
-        <v>53521</v>
+        <v>53528</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>83</v>
@@ -1528,7 +1534,7 @@
         <v>84</v>
       </c>
       <c r="O12" s="9">
-        <v>167036</v>
+        <v>167047</v>
       </c>
       <c r="P12" s="10" t="s">
         <v>85</v>
@@ -1545,16 +1551,16 @@
         <v>146092</v>
       </c>
       <c r="D13" s="9">
-        <v>114088</v>
+        <v>114196</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>88</v>
       </c>
       <c r="F13" s="9">
-        <v>20576</v>
+        <v>20595</v>
       </c>
       <c r="G13" s="9">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>89</v>
@@ -1566,7 +1572,7 @@
         <v>38</v>
       </c>
       <c r="K13" s="9">
-        <v>28806</v>
+        <v>28829</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>90</v>
@@ -1575,39 +1581,39 @@
         <v>279</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="O13" s="9">
-        <v>134664</v>
+        <v>134791</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="9">
         <v>135256</v>
       </c>
       <c r="D14" s="9">
-        <v>95470</v>
+        <v>95640</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F14" s="9">
-        <v>19216</v>
+        <v>19277</v>
       </c>
       <c r="G14" s="9">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I14" s="9">
         <v>36</v>
@@ -1616,160 +1622,160 @@
         <v>46</v>
       </c>
       <c r="K14" s="9">
-        <v>37329</v>
+        <v>37371</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M14" s="9">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="O14" s="9">
-        <v>114686</v>
+        <v>114917</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="9">
         <v>152158</v>
       </c>
       <c r="D15" s="9">
-        <v>115280</v>
+        <v>115301</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F15" s="9">
-        <v>22949</v>
+        <v>22969</v>
       </c>
       <c r="G15" s="9">
         <v>4663</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I15" s="9">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K15" s="9">
-        <v>32920</v>
+        <v>32930</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M15" s="9">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="O15" s="9">
-        <v>138229</v>
+        <v>138270</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="9">
         <v>135741</v>
       </c>
       <c r="D16" s="9">
-        <v>110329</v>
+        <v>110332</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F16" s="9">
-        <v>14645</v>
+        <v>14766</v>
       </c>
       <c r="G16" s="9">
         <v>2073</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I16" s="9">
         <v>109</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K16" s="9">
-        <v>23561</v>
+        <v>23558</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M16" s="9">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O16" s="9">
-        <v>124974</v>
+        <v>125098</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" s="9">
         <v>75116</v>
       </c>
       <c r="D17" s="9">
-        <v>56172</v>
+        <v>56188</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F17" s="9">
-        <v>12687</v>
+        <v>12729</v>
       </c>
       <c r="G17" s="9">
         <v>1188</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I17" s="9">
         <v>143</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="K17" s="9">
-        <v>18439</v>
+        <v>18430</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M17" s="9">
         <v>34</v>
@@ -1778,36 +1784,36 @@
         <v>54</v>
       </c>
       <c r="O17" s="9">
-        <v>68859</v>
+        <v>68917</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="9">
         <v>99169</v>
       </c>
       <c r="D18" s="9">
-        <v>74139</v>
+        <v>74145</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F18" s="9">
-        <v>13054</v>
+        <v>13060</v>
       </c>
       <c r="G18" s="9">
-        <v>2416</v>
+        <v>2420</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I18" s="9">
         <v>54</v>
@@ -1816,30 +1822,30 @@
         <v>54</v>
       </c>
       <c r="K18" s="9">
-        <v>22737</v>
+        <v>22726</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M18" s="9">
         <v>290</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O18" s="9">
-        <v>87193</v>
+        <v>87205</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" s="9">
         <v>41772</v>
@@ -1848,16 +1854,16 @@
         <v>34635</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F19" s="9">
-        <v>7908</v>
+        <v>7909</v>
       </c>
       <c r="G19" s="9">
         <v>357</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I19" s="9">
         <v>27</v>
@@ -1869,166 +1875,166 @@
         <v>7126</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M19" s="9">
         <v>28</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O19" s="9">
-        <v>42543</v>
+        <v>42544</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="9">
         <v>279478</v>
       </c>
       <c r="D20" s="9">
-        <v>167211</v>
+        <v>168615</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F20" s="9">
-        <v>45894</v>
+        <v>46452</v>
       </c>
       <c r="G20" s="9">
-        <v>2675</v>
+        <v>2681</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I20" s="9">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K20" s="9">
-        <v>99339</v>
+        <v>99815</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M20" s="9">
-        <v>621</v>
+        <v>686</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O20" s="9">
-        <v>213105</v>
+        <v>215067</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9">
         <v>53506</v>
       </c>
       <c r="D21" s="9">
-        <v>39721</v>
+        <v>39784</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F21" s="9">
-        <v>6636</v>
+        <v>6707</v>
       </c>
       <c r="G21" s="9">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I21" s="9">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="K21" s="9">
-        <v>12906</v>
+        <v>12881</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M21" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>54</v>
       </c>
       <c r="O21" s="9">
-        <v>46357</v>
+        <v>46491</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C22" s="12">
         <v>2730939</v>
       </c>
       <c r="D22" s="12">
-        <v>2036674</v>
+        <v>2039374</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="12">
-        <v>367101</v>
+        <v>368269</v>
       </c>
       <c r="G22" s="12">
-        <v>51206</v>
+        <v>51207</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="12">
-        <v>1768</v>
+        <v>1760</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="12">
-        <v>626877</v>
+        <v>627485</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="12">
-        <v>5281</v>
+        <v>5374</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="O22" s="12">
-        <v>2403775</v>
+        <v>2407643</v>
       </c>
       <c r="P22" s="13" t="s">
         <v>41</v>
@@ -2057,7 +2063,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2089,25 +2095,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2147,25 +2153,25 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>7236803</v>
+        <v>7248282</v>
       </c>
       <c r="D6" s="6">
-        <v>117994</v>
+        <v>118103</v>
       </c>
       <c r="E6" s="6">
-        <v>77100</v>
+        <v>77165</v>
       </c>
       <c r="F6" s="6">
-        <v>382824</v>
+        <v>383196</v>
       </c>
       <c r="G6" s="6">
-        <v>62964</v>
+        <v>63020</v>
       </c>
       <c r="H6" s="6">
-        <v>9838</v>
+        <v>9851</v>
       </c>
       <c r="I6" s="6">
-        <v>7354797</v>
+        <v>7366385</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2205,25 +2211,25 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>514964</v>
+        <v>515009</v>
       </c>
       <c r="D8" s="9">
-        <v>6560</v>
+        <v>6557</v>
       </c>
       <c r="E8" s="9">
-        <v>5008</v>
+        <v>5011</v>
       </c>
       <c r="F8" s="9">
-        <v>38750</v>
+        <v>38743</v>
       </c>
       <c r="G8" s="9">
-        <v>4560</v>
+        <v>4563</v>
       </c>
       <c r="H8" s="9">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I8" s="9">
-        <v>521524</v>
+        <v>521566</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2234,25 +2240,25 @@
         <v>58</v>
       </c>
       <c r="C9" s="9">
-        <v>941856</v>
+        <v>944088</v>
       </c>
       <c r="D9" s="9">
-        <v>15398</v>
+        <v>15422</v>
       </c>
       <c r="E9" s="9">
-        <v>10564</v>
+        <v>10572</v>
       </c>
       <c r="F9" s="9">
-        <v>44999</v>
+        <v>45053</v>
       </c>
       <c r="G9" s="9">
-        <v>5534</v>
+        <v>5543</v>
       </c>
       <c r="H9" s="9">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="I9" s="9">
-        <v>957254</v>
+        <v>959510</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2263,25 +2269,25 @@
         <v>65</v>
       </c>
       <c r="C10" s="9">
-        <v>909074</v>
+        <v>909726</v>
       </c>
       <c r="D10" s="9">
-        <v>16680</v>
+        <v>16690</v>
       </c>
       <c r="E10" s="9">
-        <v>10669</v>
+        <v>10673</v>
       </c>
       <c r="F10" s="9">
-        <v>44135</v>
+        <v>44162</v>
       </c>
       <c r="G10" s="9">
-        <v>22696</v>
+        <v>22715</v>
       </c>
       <c r="H10" s="9">
         <v>1156</v>
       </c>
       <c r="I10" s="9">
-        <v>925754</v>
+        <v>926416</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2292,25 +2298,25 @@
         <v>72</v>
       </c>
       <c r="C11" s="9">
-        <v>1141264</v>
+        <v>1141886</v>
       </c>
       <c r="D11" s="9">
-        <v>21615</v>
+        <v>21630</v>
       </c>
       <c r="E11" s="9">
-        <v>13430</v>
+        <v>13440</v>
       </c>
       <c r="F11" s="9">
-        <v>50507</v>
+        <v>50538</v>
       </c>
       <c r="G11" s="9">
-        <v>9072</v>
+        <v>9076</v>
       </c>
       <c r="H11" s="9">
-        <v>1870</v>
+        <v>1873</v>
       </c>
       <c r="I11" s="9">
-        <v>1162879</v>
+        <v>1163516</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2321,16 +2327,16 @@
         <v>80</v>
       </c>
       <c r="C12" s="9">
-        <v>518841</v>
+        <v>518875</v>
       </c>
       <c r="D12" s="9">
-        <v>6356</v>
+        <v>6359</v>
       </c>
       <c r="E12" s="9">
-        <v>6171</v>
+        <v>6173</v>
       </c>
       <c r="F12" s="9">
-        <v>29379</v>
+        <v>29381</v>
       </c>
       <c r="G12" s="9">
         <v>2074</v>
@@ -2339,7 +2345,7 @@
         <v>521</v>
       </c>
       <c r="I12" s="9">
-        <v>525197</v>
+        <v>525234</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2350,123 +2356,123 @@
         <v>87</v>
       </c>
       <c r="C13" s="9">
-        <v>404452</v>
+        <v>404928</v>
       </c>
       <c r="D13" s="9">
-        <v>4808</v>
+        <v>4811</v>
       </c>
       <c r="E13" s="9">
-        <v>4518</v>
+        <v>4524</v>
       </c>
       <c r="F13" s="9">
-        <v>28987</v>
+        <v>29035</v>
       </c>
       <c r="G13" s="9">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="H13" s="9">
         <v>487</v>
       </c>
       <c r="I13" s="9">
-        <v>409260</v>
+        <v>409739</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="9">
-        <v>341140</v>
+        <v>341846</v>
       </c>
       <c r="D14" s="9">
-        <v>9570</v>
+        <v>9595</v>
       </c>
       <c r="E14" s="9">
-        <v>3694</v>
+        <v>3700</v>
       </c>
       <c r="F14" s="9">
-        <v>22637</v>
+        <v>22673</v>
       </c>
       <c r="G14" s="9">
-        <v>2241</v>
+        <v>2246</v>
       </c>
       <c r="H14" s="9">
         <v>393</v>
       </c>
       <c r="I14" s="9">
-        <v>350710</v>
+        <v>351441</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="9">
-        <v>416822</v>
+        <v>416940</v>
       </c>
       <c r="D15" s="9">
-        <v>7906</v>
+        <v>7905</v>
       </c>
       <c r="E15" s="9">
-        <v>6746</v>
+        <v>6747</v>
       </c>
       <c r="F15" s="9">
-        <v>28136</v>
+        <v>28145</v>
       </c>
       <c r="G15" s="9">
-        <v>4071</v>
+        <v>4074</v>
       </c>
       <c r="H15" s="9">
         <v>518</v>
       </c>
       <c r="I15" s="9">
-        <v>424728</v>
+        <v>424845</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="9">
-        <v>369952</v>
+        <v>370100</v>
       </c>
       <c r="D16" s="9">
-        <v>5159</v>
+        <v>5161</v>
       </c>
       <c r="E16" s="9">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="F16" s="9">
-        <v>21278</v>
+        <v>21285</v>
       </c>
       <c r="G16" s="9">
-        <v>4295</v>
+        <v>4297</v>
       </c>
       <c r="H16" s="9">
         <v>250</v>
       </c>
       <c r="I16" s="9">
-        <v>375111</v>
+        <v>375261</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" s="9">
-        <v>199517</v>
+        <v>199619</v>
       </c>
       <c r="D17" s="9">
         <v>4871</v>
@@ -2475,7 +2481,7 @@
         <v>2194</v>
       </c>
       <c r="F17" s="9">
-        <v>10350</v>
+        <v>10356</v>
       </c>
       <c r="G17" s="9">
         <v>1727</v>
@@ -2484,21 +2490,21 @@
         <v>398</v>
       </c>
       <c r="I17" s="9">
-        <v>204388</v>
+        <v>204490</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="9">
-        <v>251606</v>
+        <v>251638</v>
       </c>
       <c r="D18" s="9">
-        <v>5481</v>
+        <v>5484</v>
       </c>
       <c r="E18" s="9">
         <v>2675</v>
@@ -2507,24 +2513,24 @@
         <v>14384</v>
       </c>
       <c r="G18" s="9">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="H18" s="9">
         <v>495</v>
       </c>
       <c r="I18" s="9">
-        <v>257087</v>
+        <v>257122</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" s="9">
-        <v>139900</v>
+        <v>139903</v>
       </c>
       <c r="D19" s="9">
         <v>1706</v>
@@ -2542,94 +2548,94 @@
         <v>233</v>
       </c>
       <c r="I19" s="9">
-        <v>141606</v>
+        <v>141609</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="9">
-        <v>696497</v>
+        <v>702459</v>
       </c>
       <c r="D20" s="9">
-        <v>7740</v>
+        <v>7767</v>
       </c>
       <c r="E20" s="9">
-        <v>4052</v>
+        <v>4077</v>
       </c>
       <c r="F20" s="9">
-        <v>19364</v>
+        <v>19515</v>
       </c>
       <c r="G20" s="9">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="H20" s="9">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="I20" s="9">
-        <v>704237</v>
+        <v>710226</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9">
-        <v>139257</v>
+        <v>139604</v>
       </c>
       <c r="D21" s="9">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="E21" s="9">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F21" s="9">
-        <v>5974</v>
+        <v>5982</v>
       </c>
       <c r="G21" s="9">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="H21" s="9">
         <v>774</v>
       </c>
       <c r="I21" s="9">
-        <v>140472</v>
+        <v>140820</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C22" s="12">
-        <v>7236803</v>
+        <v>7248282</v>
       </c>
       <c r="D22" s="12">
-        <v>117994</v>
+        <v>118103</v>
       </c>
       <c r="E22" s="12">
-        <v>77100</v>
+        <v>77165</v>
       </c>
       <c r="F22" s="12">
-        <v>382824</v>
+        <v>383196</v>
       </c>
       <c r="G22" s="12">
-        <v>62964</v>
+        <v>63020</v>
       </c>
       <c r="H22" s="12">
-        <v>9838</v>
+        <v>9851</v>
       </c>
       <c r="I22" s="12">
-        <v>7354797</v>
+        <v>7366385</v>
       </c>
     </row>
   </sheetData>
@@ -2657,7 +2663,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2683,16 +2689,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2723,13 +2729,13 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>1467</v>
+        <v>1475</v>
       </c>
       <c r="D6" s="6">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F6" s="6">
         <v>4</v>
@@ -2749,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F7" s="9">
         <v>0</v>
@@ -2763,13 +2769,13 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D8" s="9">
         <v>12</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F8" s="9">
         <v>1</v>
@@ -2783,13 +2789,13 @@
         <v>58</v>
       </c>
       <c r="C9" s="9">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D9" s="9">
         <v>103</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F9" s="9">
         <v>1</v>
@@ -2803,13 +2809,13 @@
         <v>65</v>
       </c>
       <c r="C10" s="9">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D10" s="9">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -2823,13 +2829,13 @@
         <v>72</v>
       </c>
       <c r="C11" s="9">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D11" s="9">
         <v>107</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
@@ -2849,7 +2855,7 @@
         <v>40</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F12" s="9">
         <v>1</v>
@@ -2863,13 +2869,13 @@
         <v>87</v>
       </c>
       <c r="C13" s="9">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" s="9">
         <v>23</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
@@ -2877,19 +2883,19 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="9">
         <v>101</v>
       </c>
       <c r="D14" s="9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -2897,10 +2903,10 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="9">
         <v>152</v>
@@ -2909,7 +2915,7 @@
         <v>122</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F15" s="9">
         <v>0</v>
@@ -2917,19 +2923,19 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="9">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D16" s="9">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
@@ -2937,19 +2943,19 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" s="9">
         <v>30</v>
       </c>
       <c r="D17" s="9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F17" s="9">
         <v>1</v>
@@ -2957,10 +2963,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="9">
         <v>63</v>
@@ -2969,7 +2975,7 @@
         <v>62</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
@@ -2977,10 +2983,10 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" s="9">
         <v>20</v>
@@ -2989,7 +2995,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F19" s="9">
         <v>0</v>
@@ -2997,19 +3003,19 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="9">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D20" s="9">
         <v>22</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -3017,10 +3023,10 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9">
         <v>78</v>
@@ -3029,7 +3035,7 @@
         <v>71</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F21" s="9">
         <v>0</v>
@@ -3037,19 +3043,19 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C22" s="12">
-        <v>1467</v>
+        <v>1475</v>
       </c>
       <c r="D22" s="12">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F22" s="12">
         <v>4</v>

--- a/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
@@ -18,7 +18,7 @@
     <t>PROGRES PEMUTAKHIRAN KELUARGA - KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 10 Sep 2026, 06.16 | Dicetak: 10 Sep 2026, 08.07</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 11 Sep 2026, 06.16 | Dicetak: 11 Sep 2026, 07.29</t>
   </si>
   <si>
     <t>Kode</t>
@@ -123,7 +123,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>74,68</t>
+    <t>74,77</t>
   </si>
   <si>
     <t>1,88</t>
@@ -138,7 +138,7 @@
     <t>0,2</t>
   </si>
   <si>
-    <t>88,16</t>
+    <t>88,3</t>
   </si>
   <si>
     <t>1801</t>
@@ -171,7 +171,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>79,56</t>
+    <t>79,61</t>
   </si>
   <si>
     <t>1,06</t>
@@ -180,10 +180,10 @@
     <t>0,05</t>
   </si>
   <si>
-    <t>19,09</t>
-  </si>
-  <si>
-    <t>97,41</t>
+    <t>19,06</t>
+  </si>
+  <si>
+    <t>97,47</t>
   </si>
   <si>
     <t>1803</t>
@@ -192,19 +192,19 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>74,89</t>
+    <t>75,04</t>
   </si>
   <si>
     <t>1,32</t>
   </si>
   <si>
-    <t>23,02</t>
+    <t>23,04</t>
   </si>
   <si>
     <t>0,21</t>
   </si>
   <si>
-    <t>90</t>
+    <t>90,18</t>
   </si>
   <si>
     <t>1804</t>
@@ -213,7 +213,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>77,7</t>
+    <t>77,74</t>
   </si>
   <si>
     <t>1,99</t>
@@ -225,7 +225,7 @@
     <t>0,16</t>
   </si>
   <si>
-    <t>88,3</t>
+    <t>88,36</t>
   </si>
   <si>
     <t>1805</t>
@@ -234,7 +234,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>76,43</t>
+    <t>76,48</t>
   </si>
   <si>
     <t>2,85</t>
@@ -243,13 +243,13 @@
     <t>0,09</t>
   </si>
   <si>
-    <t>20,08</t>
+    <t>20,09</t>
   </si>
   <si>
     <t>0,35</t>
   </si>
   <si>
-    <t>86,69</t>
+    <t>86,75</t>
   </si>
   <si>
     <t>1806</t>
@@ -258,19 +258,19 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>71,04</t>
+    <t>71,05</t>
   </si>
   <si>
     <t>1,97</t>
   </si>
   <si>
-    <t>26,85</t>
+    <t>26,84</t>
   </si>
   <si>
     <t>0,12</t>
   </si>
   <si>
-    <t>83,78</t>
+    <t>83,8</t>
   </si>
   <si>
     <t>1807</t>
@@ -279,19 +279,19 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>78,17</t>
+    <t>78,23</t>
   </si>
   <si>
     <t>1,78</t>
   </si>
   <si>
-    <t>19,73</t>
+    <t>19,74</t>
   </si>
   <si>
     <t>0,19</t>
   </si>
   <si>
-    <t>92,26</t>
+    <t>92,34</t>
   </si>
   <si>
     <t>1808</t>
@@ -300,16 +300,16 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>70,71</t>
+    <t>70,81</t>
   </si>
   <si>
     <t>2,32</t>
   </si>
   <si>
-    <t>27,63</t>
-  </si>
-  <si>
-    <t>84,96</t>
+    <t>27,59</t>
+  </si>
+  <si>
+    <t>85,1</t>
   </si>
   <si>
     <t>1809</t>
@@ -318,7 +318,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>75,78</t>
+    <t>75,79</t>
   </si>
   <si>
     <t>3,06</t>
@@ -327,10 +327,10 @@
     <t>0,04</t>
   </si>
   <si>
-    <t>21,64</t>
-  </si>
-  <si>
-    <t>90,87</t>
+    <t>21,63</t>
+  </si>
+  <si>
+    <t>90,9</t>
   </si>
   <si>
     <t>1810</t>
@@ -339,7 +339,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>81,28</t>
+    <t>81,29</t>
   </si>
   <si>
     <t>1,53</t>
@@ -348,13 +348,13 @@
     <t>0,08</t>
   </si>
   <si>
-    <t>17,36</t>
+    <t>17,35</t>
   </si>
   <si>
     <t>0,26</t>
   </si>
   <si>
-    <t>92,16</t>
+    <t>92,17</t>
   </si>
   <si>
     <t>1811</t>
@@ -363,16 +363,19 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>74,8</t>
+    <t>74,81</t>
   </si>
   <si>
     <t>1,58</t>
   </si>
   <si>
-    <t>24,54</t>
-  </si>
-  <si>
-    <t>91,75</t>
+    <t>24,57</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>91,76</t>
   </si>
   <si>
     <t>1812</t>
@@ -381,19 +384,19 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>74,77</t>
+    <t>74,78</t>
   </si>
   <si>
     <t>2,44</t>
   </si>
   <si>
-    <t>22,92</t>
+    <t>22,9</t>
   </si>
   <si>
     <t>0,29</t>
   </si>
   <si>
-    <t>87,94</t>
+    <t>87,95</t>
   </si>
   <si>
     <t>1813</t>
@@ -414,7 +417,7 @@
     <t>0,07</t>
   </si>
   <si>
-    <t>101,85</t>
+    <t>101,87</t>
   </si>
   <si>
     <t>1871</t>
@@ -423,19 +426,19 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>60,33</t>
+    <t>60,78</t>
   </si>
   <si>
     <t>0,96</t>
   </si>
   <si>
-    <t>35,71</t>
+    <t>35,8</t>
   </si>
   <si>
     <t>0,25</t>
   </si>
   <si>
-    <t>76,95</t>
+    <t>77,63</t>
   </si>
   <si>
     <t>1872</t>
@@ -444,16 +447,16 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>74,35</t>
-  </si>
-  <si>
-    <t>1,51</t>
-  </si>
-  <si>
-    <t>24,07</t>
-  </si>
-  <si>
-    <t>86,89</t>
+    <t>74,66</t>
+  </si>
+  <si>
+    <t>1,49</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>87,37</t>
   </si>
   <si>
     <t/>
@@ -495,52 +498,49 @@
     <t>Jumlah Bangunan Keluarga Khusus Berpindah-pindah Didata (K2)</t>
   </si>
   <si>
-    <t>49,15</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>14,12</t>
-  </si>
-  <si>
-    <t>55,68</t>
-  </si>
-  <si>
-    <t>36,65</t>
+    <t>51,31</t>
+  </si>
+  <si>
+    <t>20,93</t>
+  </si>
+  <si>
+    <t>57,51</t>
+  </si>
+  <si>
+    <t>36,42</t>
   </si>
   <si>
     <t>47,98</t>
   </si>
   <si>
-    <t>74,07</t>
-  </si>
-  <si>
-    <t>31,08</t>
-  </si>
-  <si>
-    <t>17,82</t>
-  </si>
-  <si>
-    <t>80,26</t>
-  </si>
-  <si>
-    <t>59,76</t>
-  </si>
-  <si>
-    <t>73,33</t>
+    <t>75</t>
+  </si>
+  <si>
+    <t>35,14</t>
+  </si>
+  <si>
+    <t>20,79</t>
+  </si>
+  <si>
+    <t>81,58</t>
+  </si>
+  <si>
+    <t>72,84</t>
+  </si>
+  <si>
+    <t>80</t>
   </si>
   <si>
     <t>98,41</t>
   </si>
   <si>
-    <t>75</t>
+    <t>76,19</t>
   </si>
   <si>
     <t>14,01</t>
   </si>
   <si>
-    <t>91,03</t>
+    <t>93,42</t>
   </si>
 </sst>
 </file>
@@ -1201,13 +1201,13 @@
         <v>2730939</v>
       </c>
       <c r="D6" s="6">
-        <v>2039374</v>
+        <v>2042019</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="6">
-        <v>368269</v>
+        <v>369405</v>
       </c>
       <c r="G6" s="6">
         <v>51207</v>
@@ -1216,25 +1216,25 @@
         <v>37</v>
       </c>
       <c r="I6" s="6">
-        <v>1760</v>
+        <v>1768</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="6">
-        <v>627485</v>
+        <v>627674</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="6">
-        <v>5374</v>
+        <v>5354</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="6">
-        <v>2407643</v>
+        <v>2411424</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>41</v>
@@ -1301,28 +1301,28 @@
         <v>172957</v>
       </c>
       <c r="D8" s="9">
-        <v>137613</v>
+        <v>137690</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="9">
-        <v>30861</v>
+        <v>30893</v>
       </c>
       <c r="G8" s="9">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>53</v>
       </c>
       <c r="I8" s="9">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>54</v>
       </c>
       <c r="K8" s="9">
-        <v>33016</v>
+        <v>32958</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>55</v>
@@ -1334,7 +1334,7 @@
         <v>40</v>
       </c>
       <c r="O8" s="9">
-        <v>168474</v>
+        <v>168583</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>56</v>
@@ -1351,16 +1351,16 @@
         <v>342736</v>
       </c>
       <c r="D9" s="9">
-        <v>256665</v>
+        <v>257187</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F9" s="9">
-        <v>51784</v>
+        <v>51893</v>
       </c>
       <c r="G9" s="9">
-        <v>4516</v>
+        <v>4517</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>60</v>
@@ -1372,19 +1372,19 @@
         <v>38</v>
       </c>
       <c r="K9" s="9">
-        <v>78885</v>
+        <v>78979</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>61</v>
       </c>
       <c r="M9" s="9">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>62</v>
       </c>
       <c r="O9" s="9">
-        <v>308449</v>
+        <v>309080</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>63</v>
@@ -1401,40 +1401,40 @@
         <v>362841</v>
       </c>
       <c r="D10" s="9">
-        <v>281940</v>
+        <v>282074</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>66</v>
       </c>
       <c r="F10" s="9">
-        <v>38453</v>
+        <v>38550</v>
       </c>
       <c r="G10" s="9">
-        <v>7203</v>
+        <v>7206</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>67</v>
       </c>
       <c r="I10" s="9">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>38</v>
       </c>
       <c r="K10" s="9">
-        <v>72576</v>
+        <v>72553</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>68</v>
       </c>
       <c r="M10" s="9">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="N10" s="10" t="s">
         <v>69</v>
       </c>
       <c r="O10" s="9">
-        <v>320393</v>
+        <v>320624</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>70</v>
@@ -1451,40 +1451,40 @@
         <v>449576</v>
       </c>
       <c r="D11" s="9">
-        <v>343629</v>
+        <v>343840</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>73</v>
       </c>
       <c r="F11" s="9">
-        <v>46124</v>
+        <v>46148</v>
       </c>
       <c r="G11" s="9">
-        <v>12831</v>
+        <v>12824</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>74</v>
       </c>
       <c r="I11" s="9">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>75</v>
       </c>
       <c r="K11" s="9">
-        <v>90265</v>
+        <v>90323</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>76</v>
       </c>
       <c r="M11" s="9">
-        <v>1579</v>
+        <v>1555</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>77</v>
       </c>
       <c r="O11" s="9">
-        <v>389753</v>
+        <v>389988</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>78</v>
@@ -1501,13 +1501,13 @@
         <v>199396</v>
       </c>
       <c r="D12" s="9">
-        <v>141644</v>
+        <v>141668</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>81</v>
       </c>
       <c r="F12" s="9">
-        <v>25403</v>
+        <v>25419</v>
       </c>
       <c r="G12" s="9">
         <v>3932</v>
@@ -1522,19 +1522,19 @@
         <v>46</v>
       </c>
       <c r="K12" s="9">
-        <v>53528</v>
+        <v>53509</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>83</v>
       </c>
       <c r="M12" s="9">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N12" s="10" t="s">
         <v>84</v>
       </c>
       <c r="O12" s="9">
-        <v>167047</v>
+        <v>167087</v>
       </c>
       <c r="P12" s="10" t="s">
         <v>85</v>
@@ -1551,16 +1551,16 @@
         <v>146092</v>
       </c>
       <c r="D13" s="9">
-        <v>114196</v>
+        <v>114287</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>88</v>
       </c>
       <c r="F13" s="9">
-        <v>20595</v>
+        <v>20620</v>
       </c>
       <c r="G13" s="9">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>89</v>
@@ -1572,19 +1572,19 @@
         <v>38</v>
       </c>
       <c r="K13" s="9">
-        <v>28829</v>
+        <v>28832</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>90</v>
       </c>
       <c r="M13" s="9">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N13" s="10" t="s">
         <v>91</v>
       </c>
       <c r="O13" s="9">
-        <v>134791</v>
+        <v>134907</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>92</v>
@@ -1601,16 +1601,16 @@
         <v>135256</v>
       </c>
       <c r="D14" s="9">
-        <v>95640</v>
+        <v>95779</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>95</v>
       </c>
       <c r="F14" s="9">
-        <v>19277</v>
+        <v>19321</v>
       </c>
       <c r="G14" s="9">
-        <v>3132</v>
+        <v>3134</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>96</v>
@@ -1622,19 +1622,19 @@
         <v>46</v>
       </c>
       <c r="K14" s="9">
-        <v>37371</v>
+        <v>37314</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>97</v>
       </c>
       <c r="M14" s="9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N14" s="10" t="s">
         <v>38</v>
       </c>
       <c r="O14" s="9">
-        <v>114917</v>
+        <v>115100</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>98</v>
@@ -1651,40 +1651,40 @@
         <v>152158</v>
       </c>
       <c r="D15" s="9">
-        <v>115301</v>
+        <v>115318</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>101</v>
       </c>
       <c r="F15" s="9">
-        <v>22969</v>
+        <v>22987</v>
       </c>
       <c r="G15" s="9">
-        <v>4663</v>
+        <v>4662</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>102</v>
       </c>
       <c r="I15" s="9">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>103</v>
       </c>
       <c r="K15" s="9">
-        <v>32930</v>
+        <v>32913</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>104</v>
       </c>
       <c r="M15" s="9">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N15" s="10" t="s">
         <v>54</v>
       </c>
       <c r="O15" s="9">
-        <v>138270</v>
+        <v>138305</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>105</v>
@@ -1701,13 +1701,13 @@
         <v>135741</v>
       </c>
       <c r="D16" s="9">
-        <v>110332</v>
+        <v>110340</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>108</v>
       </c>
       <c r="F16" s="9">
-        <v>14766</v>
+        <v>14769</v>
       </c>
       <c r="G16" s="9">
         <v>2073</v>
@@ -1722,7 +1722,7 @@
         <v>110</v>
       </c>
       <c r="K16" s="9">
-        <v>23558</v>
+        <v>23546</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>111</v>
@@ -1734,7 +1734,7 @@
         <v>112</v>
       </c>
       <c r="O16" s="9">
-        <v>125098</v>
+        <v>125109</v>
       </c>
       <c r="P16" s="10" t="s">
         <v>113</v>
@@ -1751,16 +1751,16 @@
         <v>75116</v>
       </c>
       <c r="D17" s="9">
-        <v>56188</v>
+        <v>56194</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>116</v>
       </c>
       <c r="F17" s="9">
-        <v>12729</v>
+        <v>12735</v>
       </c>
       <c r="G17" s="9">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>117</v>
@@ -1772,48 +1772,48 @@
         <v>91</v>
       </c>
       <c r="K17" s="9">
-        <v>18430</v>
+        <v>18459</v>
       </c>
       <c r="L17" s="10" t="s">
         <v>118</v>
       </c>
       <c r="M17" s="9">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="O17" s="9">
-        <v>68917</v>
+        <v>68929</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" s="9">
         <v>99169</v>
       </c>
       <c r="D18" s="9">
-        <v>74145</v>
+        <v>74158</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F18" s="9">
-        <v>13060</v>
+        <v>13066</v>
       </c>
       <c r="G18" s="9">
         <v>2420</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I18" s="9">
         <v>54</v>
@@ -1822,30 +1822,30 @@
         <v>54</v>
       </c>
       <c r="K18" s="9">
-        <v>22726</v>
+        <v>22705</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M18" s="9">
         <v>290</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O18" s="9">
-        <v>87205</v>
+        <v>87224</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" s="9">
         <v>41772</v>
@@ -1854,16 +1854,16 @@
         <v>34635</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F19" s="9">
-        <v>7909</v>
+        <v>7917</v>
       </c>
       <c r="G19" s="9">
         <v>357</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I19" s="9">
         <v>27</v>
@@ -1875,107 +1875,107 @@
         <v>7126</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M19" s="9">
         <v>28</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O19" s="9">
-        <v>42544</v>
+        <v>42552</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="9">
         <v>279478</v>
       </c>
       <c r="D20" s="9">
-        <v>168615</v>
+        <v>169855</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F20" s="9">
-        <v>46452</v>
+        <v>47105</v>
       </c>
       <c r="G20" s="9">
-        <v>2681</v>
+        <v>2686</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I20" s="9">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K20" s="9">
-        <v>99815</v>
+        <v>100066</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M20" s="9">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O20" s="9">
-        <v>215067</v>
+        <v>216960</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="9">
         <v>53506</v>
       </c>
       <c r="D21" s="9">
-        <v>39784</v>
+        <v>39947</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F21" s="9">
-        <v>6707</v>
+        <v>6802</v>
       </c>
       <c r="G21" s="9">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I21" s="9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="K21" s="9">
-        <v>12881</v>
+        <v>12842</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M21" s="9">
         <v>26</v>
@@ -1984,30 +1984,30 @@
         <v>54</v>
       </c>
       <c r="O21" s="9">
-        <v>46491</v>
+        <v>46749</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="12">
         <v>2730939</v>
       </c>
       <c r="D22" s="12">
-        <v>2039374</v>
+        <v>2042019</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="12">
-        <v>368269</v>
+        <v>369405</v>
       </c>
       <c r="G22" s="12">
         <v>51207</v>
@@ -2016,25 +2016,25 @@
         <v>37</v>
       </c>
       <c r="I22" s="12">
-        <v>1760</v>
+        <v>1768</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="12">
-        <v>627485</v>
+        <v>627674</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="12">
-        <v>5374</v>
+        <v>5354</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="O22" s="12">
-        <v>2407643</v>
+        <v>2411424</v>
       </c>
       <c r="P22" s="13" t="s">
         <v>41</v>
@@ -2063,7 +2063,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2095,25 +2095,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2153,25 +2153,25 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>7248282</v>
+        <v>7259602</v>
       </c>
       <c r="D6" s="6">
-        <v>118103</v>
+        <v>118187</v>
       </c>
       <c r="E6" s="6">
-        <v>77165</v>
+        <v>77233</v>
       </c>
       <c r="F6" s="6">
-        <v>383196</v>
+        <v>383633</v>
       </c>
       <c r="G6" s="6">
-        <v>63020</v>
+        <v>63080</v>
       </c>
       <c r="H6" s="6">
-        <v>9851</v>
+        <v>9848</v>
       </c>
       <c r="I6" s="6">
-        <v>7366385</v>
+        <v>7377789</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2211,25 +2211,25 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>515009</v>
+        <v>515325</v>
       </c>
       <c r="D8" s="9">
-        <v>6557</v>
+        <v>6561</v>
       </c>
       <c r="E8" s="9">
-        <v>5011</v>
+        <v>5013</v>
       </c>
       <c r="F8" s="9">
-        <v>38743</v>
+        <v>38775</v>
       </c>
       <c r="G8" s="9">
-        <v>4563</v>
+        <v>4567</v>
       </c>
       <c r="H8" s="9">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="I8" s="9">
-        <v>521566</v>
+        <v>521886</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2240,25 +2240,25 @@
         <v>58</v>
       </c>
       <c r="C9" s="9">
-        <v>944088</v>
+        <v>946172</v>
       </c>
       <c r="D9" s="9">
-        <v>15422</v>
+        <v>15433</v>
       </c>
       <c r="E9" s="9">
-        <v>10572</v>
+        <v>10589</v>
       </c>
       <c r="F9" s="9">
-        <v>45053</v>
+        <v>45127</v>
       </c>
       <c r="G9" s="9">
-        <v>5543</v>
+        <v>5549</v>
       </c>
       <c r="H9" s="9">
         <v>1134</v>
       </c>
       <c r="I9" s="9">
-        <v>959510</v>
+        <v>961605</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2269,25 +2269,25 @@
         <v>65</v>
       </c>
       <c r="C10" s="9">
-        <v>909726</v>
+        <v>910373</v>
       </c>
       <c r="D10" s="9">
-        <v>16690</v>
+        <v>16699</v>
       </c>
       <c r="E10" s="9">
-        <v>10673</v>
+        <v>10674</v>
       </c>
       <c r="F10" s="9">
-        <v>44162</v>
+        <v>44198</v>
       </c>
       <c r="G10" s="9">
-        <v>22715</v>
+        <v>22743</v>
       </c>
       <c r="H10" s="9">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="I10" s="9">
-        <v>926416</v>
+        <v>927072</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2298,25 +2298,25 @@
         <v>72</v>
       </c>
       <c r="C11" s="9">
-        <v>1141886</v>
+        <v>1142650</v>
       </c>
       <c r="D11" s="9">
-        <v>21630</v>
+        <v>21636</v>
       </c>
       <c r="E11" s="9">
-        <v>13440</v>
+        <v>13447</v>
       </c>
       <c r="F11" s="9">
-        <v>50538</v>
+        <v>50570</v>
       </c>
       <c r="G11" s="9">
-        <v>9076</v>
+        <v>9080</v>
       </c>
       <c r="H11" s="9">
         <v>1873</v>
       </c>
       <c r="I11" s="9">
-        <v>1163516</v>
+        <v>1164286</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2327,16 +2327,16 @@
         <v>80</v>
       </c>
       <c r="C12" s="9">
-        <v>518875</v>
+        <v>518992</v>
       </c>
       <c r="D12" s="9">
-        <v>6359</v>
+        <v>6360</v>
       </c>
       <c r="E12" s="9">
-        <v>6173</v>
+        <v>6175</v>
       </c>
       <c r="F12" s="9">
-        <v>29381</v>
+        <v>29403</v>
       </c>
       <c r="G12" s="9">
         <v>2074</v>
@@ -2345,7 +2345,7 @@
         <v>521</v>
       </c>
       <c r="I12" s="9">
-        <v>525234</v>
+        <v>525352</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2356,25 +2356,25 @@
         <v>87</v>
       </c>
       <c r="C13" s="9">
-        <v>404928</v>
+        <v>405247</v>
       </c>
       <c r="D13" s="9">
-        <v>4811</v>
+        <v>4816</v>
       </c>
       <c r="E13" s="9">
-        <v>4524</v>
+        <v>4530</v>
       </c>
       <c r="F13" s="9">
-        <v>29035</v>
+        <v>29064</v>
       </c>
       <c r="G13" s="9">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="H13" s="9">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I13" s="9">
-        <v>409739</v>
+        <v>410063</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2385,25 +2385,25 @@
         <v>94</v>
       </c>
       <c r="C14" s="9">
-        <v>341846</v>
+        <v>342393</v>
       </c>
       <c r="D14" s="9">
-        <v>9595</v>
+        <v>9610</v>
       </c>
       <c r="E14" s="9">
-        <v>3700</v>
+        <v>3707</v>
       </c>
       <c r="F14" s="9">
-        <v>22673</v>
+        <v>22714</v>
       </c>
       <c r="G14" s="9">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="H14" s="9">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I14" s="9">
-        <v>351441</v>
+        <v>352003</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2414,16 +2414,16 @@
         <v>100</v>
       </c>
       <c r="C15" s="9">
-        <v>416940</v>
+        <v>417028</v>
       </c>
       <c r="D15" s="9">
-        <v>7905</v>
+        <v>7899</v>
       </c>
       <c r="E15" s="9">
-        <v>6747</v>
+        <v>6746</v>
       </c>
       <c r="F15" s="9">
-        <v>28145</v>
+        <v>28154</v>
       </c>
       <c r="G15" s="9">
         <v>4074</v>
@@ -2432,7 +2432,7 @@
         <v>518</v>
       </c>
       <c r="I15" s="9">
-        <v>424845</v>
+        <v>424927</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2443,25 +2443,25 @@
         <v>107</v>
       </c>
       <c r="C16" s="9">
-        <v>370100</v>
+        <v>370121</v>
       </c>
       <c r="D16" s="9">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="E16" s="9">
         <v>3206</v>
       </c>
       <c r="F16" s="9">
-        <v>21285</v>
+        <v>21286</v>
       </c>
       <c r="G16" s="9">
-        <v>4297</v>
+        <v>4298</v>
       </c>
       <c r="H16" s="9">
         <v>250</v>
       </c>
       <c r="I16" s="9">
-        <v>375261</v>
+        <v>375283</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2472,65 +2472,65 @@
         <v>115</v>
       </c>
       <c r="C17" s="9">
-        <v>199619</v>
+        <v>199652</v>
       </c>
       <c r="D17" s="9">
         <v>4871</v>
       </c>
       <c r="E17" s="9">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="F17" s="9">
-        <v>10356</v>
+        <v>10359</v>
       </c>
       <c r="G17" s="9">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H17" s="9">
         <v>398</v>
       </c>
       <c r="I17" s="9">
-        <v>204490</v>
+        <v>204523</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" s="9">
-        <v>251638</v>
+        <v>251694</v>
       </c>
       <c r="D18" s="9">
-        <v>5484</v>
+        <v>5488</v>
       </c>
       <c r="E18" s="9">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="F18" s="9">
-        <v>14384</v>
+        <v>14387</v>
       </c>
       <c r="G18" s="9">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="H18" s="9">
         <v>495</v>
       </c>
       <c r="I18" s="9">
-        <v>257122</v>
+        <v>257182</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" s="9">
-        <v>139903</v>
+        <v>139931</v>
       </c>
       <c r="D19" s="9">
         <v>1706</v>
@@ -2539,7 +2539,7 @@
         <v>1062</v>
       </c>
       <c r="F19" s="9">
-        <v>10578</v>
+        <v>10576</v>
       </c>
       <c r="G19" s="9">
         <v>226</v>
@@ -2548,94 +2548,94 @@
         <v>233</v>
       </c>
       <c r="I19" s="9">
-        <v>141609</v>
+        <v>141637</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="9">
-        <v>702459</v>
+        <v>708079</v>
       </c>
       <c r="D20" s="9">
-        <v>7767</v>
+        <v>7798</v>
       </c>
       <c r="E20" s="9">
-        <v>4077</v>
+        <v>4100</v>
       </c>
       <c r="F20" s="9">
-        <v>19515</v>
+        <v>19661</v>
       </c>
       <c r="G20" s="9">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="H20" s="9">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="I20" s="9">
-        <v>710226</v>
+        <v>715877</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="9">
-        <v>139604</v>
+        <v>140284</v>
       </c>
       <c r="D21" s="9">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="E21" s="9">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="F21" s="9">
-        <v>5982</v>
+        <v>5993</v>
       </c>
       <c r="G21" s="9">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="H21" s="9">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="I21" s="9">
-        <v>140820</v>
+        <v>141503</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="12">
-        <v>7248282</v>
+        <v>7259602</v>
       </c>
       <c r="D22" s="12">
-        <v>118103</v>
+        <v>118187</v>
       </c>
       <c r="E22" s="12">
-        <v>77165</v>
+        <v>77233</v>
       </c>
       <c r="F22" s="12">
-        <v>383196</v>
+        <v>383633</v>
       </c>
       <c r="G22" s="12">
-        <v>63020</v>
+        <v>63080</v>
       </c>
       <c r="H22" s="12">
-        <v>9851</v>
+        <v>9848</v>
       </c>
       <c r="I22" s="12">
-        <v>7366385</v>
+        <v>7377789</v>
       </c>
     </row>
   </sheetData>
@@ -2663,7 +2663,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2689,16 +2689,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2729,13 +2729,13 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>1475</v>
+        <v>1485</v>
       </c>
       <c r="D6" s="6">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F6" s="6">
         <v>4</v>
@@ -2755,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="F7" s="9">
         <v>0</v>
@@ -2769,10 +2769,10 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>162</v>
@@ -2789,10 +2789,10 @@
         <v>58</v>
       </c>
       <c r="C9" s="9">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D9" s="9">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>163</v>
@@ -2809,7 +2809,7 @@
         <v>65</v>
       </c>
       <c r="C10" s="9">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D10" s="9">
         <v>59</v>
@@ -2849,10 +2849,10 @@
         <v>80</v>
       </c>
       <c r="C12" s="9">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D12" s="9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>166</v>
@@ -2872,7 +2872,7 @@
         <v>74</v>
       </c>
       <c r="D13" s="9">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>167</v>
@@ -2892,7 +2892,7 @@
         <v>101</v>
       </c>
       <c r="D14" s="9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>168</v>
@@ -2912,7 +2912,7 @@
         <v>152</v>
       </c>
       <c r="D15" s="9">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>169</v>
@@ -2929,10 +2929,10 @@
         <v>107</v>
       </c>
       <c r="C16" s="9">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" s="9">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>170</v>
@@ -2952,7 +2952,7 @@
         <v>30</v>
       </c>
       <c r="D17" s="9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>171</v>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" s="9">
         <v>63</v>
@@ -2983,16 +2983,16 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>173</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="9">
         <v>157</v>
@@ -3023,13 +3023,13 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="9">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D21" s="9">
         <v>71</v>
@@ -3043,19 +3043,19 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="12">
-        <v>1475</v>
+        <v>1485</v>
       </c>
       <c r="D22" s="12">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F22" s="12">
         <v>4</v>

--- a/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="177">
   <si>
     <t>PROGRES PEMUTAKHIRAN KELUARGA - KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 11 Sep 2026, 06.16 | Dicetak: 11 Sep 2026, 07.29</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 13 Sep 2026, 12.16 | Dicetak: 13 Sep 2026, 14.35</t>
   </si>
   <si>
     <t>Kode</t>
@@ -123,7 +123,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>74,77</t>
+    <t>74,92</t>
   </si>
   <si>
     <t>1,88</t>
@@ -132,13 +132,13 @@
     <t>0,06</t>
   </si>
   <si>
-    <t>22,98</t>
+    <t>23</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>88,3</t>
+    <t>88,51</t>
   </si>
   <si>
     <t>1801</t>
@@ -171,7 +171,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>79,61</t>
+    <t>79,67</t>
   </si>
   <si>
     <t>1,06</t>
@@ -180,10 +180,13 @@
     <t>0,05</t>
   </si>
   <si>
-    <t>19,06</t>
-  </si>
-  <si>
-    <t>97,47</t>
+    <t>19,01</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>97,57</t>
   </si>
   <si>
     <t>1803</t>
@@ -192,19 +195,19 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>75,04</t>
+    <t>75,2</t>
   </si>
   <si>
     <t>1,32</t>
   </si>
   <si>
-    <t>23,04</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>90,18</t>
+    <t>23,07</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>90,39</t>
   </si>
   <si>
     <t>1804</t>
@@ -213,19 +216,19 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>77,74</t>
+    <t>77,77</t>
   </si>
   <si>
     <t>1,99</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>0,16</t>
-  </si>
-  <si>
-    <t>88,36</t>
+    <t>19,99</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>88,41</t>
   </si>
   <si>
     <t>1805</t>
@@ -234,7 +237,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>76,48</t>
+    <t>76,54</t>
   </si>
   <si>
     <t>2,85</t>
@@ -249,7 +252,7 @@
     <t>0,35</t>
   </si>
   <si>
-    <t>86,75</t>
+    <t>86,82</t>
   </si>
   <si>
     <t>1806</t>
@@ -258,19 +261,19 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>71,05</t>
+    <t>71,06</t>
   </si>
   <si>
     <t>1,97</t>
   </si>
   <si>
-    <t>26,84</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>83,8</t>
+    <t>26,83</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>83,82</t>
   </si>
   <si>
     <t>1807</t>
@@ -279,19 +282,19 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>78,23</t>
+    <t>78,24</t>
   </si>
   <si>
     <t>1,78</t>
   </si>
   <si>
-    <t>19,74</t>
+    <t>19,73</t>
   </si>
   <si>
     <t>0,19</t>
   </si>
   <si>
-    <t>92,34</t>
+    <t>92,37</t>
   </si>
   <si>
     <t>1808</t>
@@ -300,16 +303,16 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>70,81</t>
+    <t>70,92</t>
   </si>
   <si>
     <t>2,32</t>
   </si>
   <si>
-    <t>27,59</t>
-  </si>
-  <si>
-    <t>85,1</t>
+    <t>27,54</t>
+  </si>
+  <si>
+    <t>85,25</t>
   </si>
   <si>
     <t>1809</t>
@@ -327,10 +330,10 @@
     <t>0,04</t>
   </si>
   <si>
-    <t>21,63</t>
-  </si>
-  <si>
-    <t>90,9</t>
+    <t>21,62</t>
+  </si>
+  <si>
+    <t>90,92</t>
   </si>
   <si>
     <t>1810</t>
@@ -339,7 +342,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>81,29</t>
+    <t>81,32</t>
   </si>
   <si>
     <t>1,53</t>
@@ -348,13 +351,13 @@
     <t>0,08</t>
   </si>
   <si>
-    <t>17,35</t>
+    <t>17,33</t>
   </si>
   <si>
     <t>0,26</t>
   </si>
   <si>
-    <t>92,17</t>
+    <t>92,2</t>
   </si>
   <si>
     <t>1811</t>
@@ -363,7 +366,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>74,81</t>
+    <t>74,82</t>
   </si>
   <si>
     <t>1,58</t>
@@ -375,7 +378,7 @@
     <t>0</t>
   </si>
   <si>
-    <t>91,76</t>
+    <t>91,82</t>
   </si>
   <si>
     <t>1812</t>
@@ -384,19 +387,19 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>74,78</t>
+    <t>74,8</t>
   </si>
   <si>
     <t>2,44</t>
   </si>
   <si>
-    <t>22,9</t>
+    <t>22,88</t>
   </si>
   <si>
     <t>0,29</t>
   </si>
   <si>
-    <t>87,95</t>
+    <t>87,98</t>
   </si>
   <si>
     <t>1813</t>
@@ -405,7 +408,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>82,91</t>
+    <t>82,92</t>
   </si>
   <si>
     <t>0,85</t>
@@ -426,19 +429,19 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>60,78</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>35,8</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>77,63</t>
+    <t>61,65</t>
+  </si>
+  <si>
+    <t>0,97</t>
+  </si>
+  <si>
+    <t>36,04</t>
+  </si>
+  <si>
+    <t>0,31</t>
+  </si>
+  <si>
+    <t>78,85</t>
   </si>
   <si>
     <t>1872</t>
@@ -447,16 +450,16 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>74,66</t>
-  </si>
-  <si>
-    <t>1,49</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>87,37</t>
+    <t>75,29</t>
+  </si>
+  <si>
+    <t>1,48</t>
+  </si>
+  <si>
+    <t>23,76</t>
+  </si>
+  <si>
+    <t>88,53</t>
   </si>
   <si>
     <t/>
@@ -498,49 +501,49 @@
     <t>Jumlah Bangunan Keluarga Khusus Berpindah-pindah Didata (K2)</t>
   </si>
   <si>
-    <t>51,31</t>
-  </si>
-  <si>
-    <t>20,93</t>
-  </si>
-  <si>
-    <t>57,51</t>
-  </si>
-  <si>
-    <t>36,42</t>
+    <t>53,23</t>
+  </si>
+  <si>
+    <t>23,86</t>
+  </si>
+  <si>
+    <t>58,33</t>
+  </si>
+  <si>
+    <t>44,1</t>
   </si>
   <si>
     <t>47,98</t>
   </si>
   <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>35,14</t>
-  </si>
-  <si>
-    <t>20,79</t>
+    <t>57,33</t>
+  </si>
+  <si>
+    <t>43,84</t>
+  </si>
+  <si>
+    <t>21,78</t>
   </si>
   <si>
     <t>81,58</t>
   </si>
   <si>
-    <t>72,84</t>
+    <t>82,72</t>
   </si>
   <si>
     <t>80</t>
   </si>
   <si>
-    <t>98,41</t>
+    <t>100</t>
   </si>
   <si>
     <t>76,19</t>
   </si>
   <si>
-    <t>14,01</t>
-  </si>
-  <si>
-    <t>93,42</t>
+    <t>16,98</t>
+  </si>
+  <si>
+    <t>96</t>
   </si>
 </sst>
 </file>
@@ -1201,40 +1204,40 @@
         <v>2730939</v>
       </c>
       <c r="D6" s="6">
-        <v>2042019</v>
+        <v>2046078</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="6">
-        <v>369405</v>
+        <v>371200</v>
       </c>
       <c r="G6" s="6">
-        <v>51207</v>
+        <v>51217</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="6">
-        <v>1768</v>
+        <v>1756</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="6">
-        <v>627674</v>
+        <v>628070</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="6">
-        <v>5354</v>
+        <v>5579</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="6">
-        <v>2411424</v>
+        <v>2417278</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>41</v>
@@ -1301,69 +1304,69 @@
         <v>172957</v>
       </c>
       <c r="D8" s="9">
-        <v>137690</v>
+        <v>137794</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="9">
-        <v>30893</v>
+        <v>30965</v>
       </c>
       <c r="G8" s="9">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>53</v>
       </c>
       <c r="I8" s="9">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>54</v>
       </c>
       <c r="K8" s="9">
-        <v>32958</v>
+        <v>32880</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>55</v>
       </c>
       <c r="M8" s="9">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="O8" s="9">
-        <v>168583</v>
+        <v>168759</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="9">
         <v>342736</v>
       </c>
       <c r="D9" s="9">
-        <v>257187</v>
+        <v>257735</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" s="9">
-        <v>51893</v>
+        <v>52073</v>
       </c>
       <c r="G9" s="9">
-        <v>4517</v>
+        <v>4520</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I9" s="9">
         <v>215</v>
@@ -1372,148 +1375,148 @@
         <v>38</v>
       </c>
       <c r="K9" s="9">
-        <v>78979</v>
+        <v>79085</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M9" s="9">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O9" s="9">
-        <v>309080</v>
+        <v>309808</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="9">
         <v>362841</v>
       </c>
       <c r="D10" s="9">
-        <v>282074</v>
+        <v>282174</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F10" s="9">
-        <v>38550</v>
+        <v>38622</v>
       </c>
       <c r="G10" s="9">
-        <v>7206</v>
+        <v>7208</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" s="9">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>38</v>
       </c>
       <c r="K10" s="9">
-        <v>72553</v>
+        <v>72539</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M10" s="9">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O10" s="9">
-        <v>320624</v>
+        <v>320796</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="9">
         <v>449576</v>
       </c>
       <c r="D11" s="9">
-        <v>343840</v>
+        <v>344101</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" s="9">
-        <v>46148</v>
+        <v>46203</v>
       </c>
       <c r="G11" s="9">
-        <v>12824</v>
+        <v>12825</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I11" s="9">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K11" s="9">
-        <v>90323</v>
+        <v>90310</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M11" s="9">
-        <v>1555</v>
+        <v>1574</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O11" s="9">
-        <v>389988</v>
+        <v>390304</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" s="9">
         <v>199396</v>
       </c>
       <c r="D12" s="9">
-        <v>141668</v>
+        <v>141688</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F12" s="9">
-        <v>25419</v>
+        <v>25450</v>
       </c>
       <c r="G12" s="9">
         <v>3932</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I12" s="9">
         <v>61</v>
@@ -1522,48 +1525,48 @@
         <v>46</v>
       </c>
       <c r="K12" s="9">
-        <v>53509</v>
+        <v>53497</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M12" s="9">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O12" s="9">
-        <v>167087</v>
+        <v>167138</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" s="9">
         <v>146092</v>
       </c>
       <c r="D13" s="9">
-        <v>114287</v>
+        <v>114309</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F13" s="9">
-        <v>20620</v>
+        <v>20632</v>
       </c>
       <c r="G13" s="9">
         <v>2597</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I13" s="9">
         <v>92</v>
@@ -1572,48 +1575,48 @@
         <v>38</v>
       </c>
       <c r="K13" s="9">
-        <v>28832</v>
+        <v>28829</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M13" s="9">
         <v>280</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O13" s="9">
-        <v>134907</v>
+        <v>134941</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" s="9">
         <v>135256</v>
       </c>
       <c r="D14" s="9">
-        <v>95779</v>
+        <v>95927</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" s="9">
-        <v>19321</v>
+        <v>19382</v>
       </c>
       <c r="G14" s="9">
-        <v>3134</v>
+        <v>3136</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I14" s="9">
         <v>36</v>
@@ -1622,198 +1625,198 @@
         <v>46</v>
       </c>
       <c r="K14" s="9">
-        <v>37314</v>
+        <v>37243</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M14" s="9">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N14" s="10" t="s">
         <v>38</v>
       </c>
       <c r="O14" s="9">
-        <v>115100</v>
+        <v>115309</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="9">
         <v>152158</v>
       </c>
       <c r="D15" s="9">
-        <v>115318</v>
+        <v>115320</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F15" s="9">
-        <v>22987</v>
+        <v>23020</v>
       </c>
       <c r="G15" s="9">
-        <v>4662</v>
+        <v>4661</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I15" s="9">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K15" s="9">
-        <v>32913</v>
+        <v>32903</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M15" s="9">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N15" s="10" t="s">
         <v>54</v>
       </c>
       <c r="O15" s="9">
-        <v>138305</v>
+        <v>138340</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16" s="9">
         <v>135741</v>
       </c>
       <c r="D16" s="9">
-        <v>110340</v>
+        <v>110381</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F16" s="9">
-        <v>14769</v>
+        <v>14772</v>
       </c>
       <c r="G16" s="9">
         <v>2073</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I16" s="9">
         <v>109</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K16" s="9">
-        <v>23546</v>
+        <v>23518</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M16" s="9">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O16" s="9">
-        <v>125109</v>
+        <v>125153</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="9">
         <v>75116</v>
       </c>
       <c r="D17" s="9">
-        <v>56194</v>
+        <v>56201</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F17" s="9">
-        <v>12735</v>
+        <v>12770</v>
       </c>
       <c r="G17" s="9">
         <v>1189</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I17" s="9">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K17" s="9">
-        <v>18459</v>
+        <v>18453</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M17" s="9">
         <v>1</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O17" s="9">
-        <v>68929</v>
+        <v>68971</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="9">
         <v>99169</v>
       </c>
       <c r="D18" s="9">
-        <v>74158</v>
+        <v>74177</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F18" s="9">
-        <v>13066</v>
+        <v>13075</v>
       </c>
       <c r="G18" s="9">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I18" s="9">
         <v>54</v>
@@ -1822,48 +1825,48 @@
         <v>54</v>
       </c>
       <c r="K18" s="9">
-        <v>22705</v>
+        <v>22694</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M18" s="9">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O18" s="9">
-        <v>87224</v>
+        <v>87252</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C19" s="9">
         <v>41772</v>
       </c>
       <c r="D19" s="9">
-        <v>34635</v>
+        <v>34636</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F19" s="9">
-        <v>7917</v>
+        <v>7919</v>
       </c>
       <c r="G19" s="9">
         <v>357</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I19" s="9">
         <v>27</v>
@@ -1872,98 +1875,98 @@
         <v>38</v>
       </c>
       <c r="K19" s="9">
-        <v>7126</v>
+        <v>7125</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M19" s="9">
         <v>28</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O19" s="9">
-        <v>42552</v>
+        <v>42555</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="9">
         <v>279478</v>
       </c>
       <c r="D20" s="9">
-        <v>169855</v>
+        <v>172302</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F20" s="9">
-        <v>47105</v>
+        <v>48056</v>
       </c>
       <c r="G20" s="9">
-        <v>2686</v>
+        <v>2698</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I20" s="9">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K20" s="9">
-        <v>100066</v>
+        <v>100730</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M20" s="9">
-        <v>703</v>
+        <v>855</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O20" s="9">
-        <v>216960</v>
+        <v>220358</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="9">
         <v>53506</v>
       </c>
       <c r="D21" s="9">
-        <v>39947</v>
+        <v>40286</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F21" s="9">
-        <v>6802</v>
+        <v>7081</v>
       </c>
       <c r="G21" s="9">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I21" s="9">
         <v>51</v>
@@ -1972,69 +1975,69 @@
         <v>48</v>
       </c>
       <c r="K21" s="9">
-        <v>12842</v>
+        <v>12715</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M21" s="9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="O21" s="9">
-        <v>46749</v>
+        <v>47367</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="12">
         <v>2730939</v>
       </c>
       <c r="D22" s="12">
-        <v>2042019</v>
+        <v>2046078</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="12">
-        <v>369405</v>
+        <v>371200</v>
       </c>
       <c r="G22" s="12">
-        <v>51207</v>
+        <v>51217</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="12">
-        <v>1768</v>
+        <v>1756</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="12">
-        <v>627674</v>
+        <v>628070</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="12">
-        <v>5354</v>
+        <v>5579</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="O22" s="12">
-        <v>2411424</v>
+        <v>2417278</v>
       </c>
       <c r="P22" s="13" t="s">
         <v>41</v>
@@ -2063,7 +2066,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2095,25 +2098,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2153,25 +2156,25 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>7259602</v>
+        <v>7276833</v>
       </c>
       <c r="D6" s="6">
-        <v>118187</v>
+        <v>118288</v>
       </c>
       <c r="E6" s="6">
-        <v>77233</v>
+        <v>77365</v>
       </c>
       <c r="F6" s="6">
-        <v>383633</v>
+        <v>384155</v>
       </c>
       <c r="G6" s="6">
-        <v>63080</v>
+        <v>63161</v>
       </c>
       <c r="H6" s="6">
-        <v>9848</v>
+        <v>9851</v>
       </c>
       <c r="I6" s="6">
-        <v>7377789</v>
+        <v>7395121</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2211,132 +2214,132 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>515325</v>
+        <v>515815</v>
       </c>
       <c r="D8" s="9">
-        <v>6561</v>
+        <v>6563</v>
       </c>
       <c r="E8" s="9">
-        <v>5013</v>
+        <v>5024</v>
       </c>
       <c r="F8" s="9">
-        <v>38775</v>
+        <v>38836</v>
       </c>
       <c r="G8" s="9">
-        <v>4567</v>
+        <v>4576</v>
       </c>
       <c r="H8" s="9">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="I8" s="9">
-        <v>521886</v>
+        <v>522378</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="9">
-        <v>946172</v>
+        <v>948500</v>
       </c>
       <c r="D9" s="9">
-        <v>15433</v>
+        <v>15453</v>
       </c>
       <c r="E9" s="9">
-        <v>10589</v>
+        <v>10610</v>
       </c>
       <c r="F9" s="9">
-        <v>45127</v>
+        <v>45231</v>
       </c>
       <c r="G9" s="9">
-        <v>5549</v>
+        <v>5561</v>
       </c>
       <c r="H9" s="9">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="I9" s="9">
-        <v>961605</v>
+        <v>963953</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="9">
-        <v>910373</v>
+        <v>910875</v>
       </c>
       <c r="D10" s="9">
-        <v>16699</v>
+        <v>16709</v>
       </c>
       <c r="E10" s="9">
-        <v>10674</v>
+        <v>10681</v>
       </c>
       <c r="F10" s="9">
-        <v>44198</v>
+        <v>44212</v>
       </c>
       <c r="G10" s="9">
-        <v>22743</v>
+        <v>22764</v>
       </c>
       <c r="H10" s="9">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="I10" s="9">
-        <v>927072</v>
+        <v>927584</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="9">
-        <v>1142650</v>
+        <v>1143603</v>
       </c>
       <c r="D11" s="9">
-        <v>21636</v>
+        <v>21638</v>
       </c>
       <c r="E11" s="9">
-        <v>13447</v>
+        <v>13458</v>
       </c>
       <c r="F11" s="9">
-        <v>50570</v>
+        <v>50614</v>
       </c>
       <c r="G11" s="9">
-        <v>9080</v>
+        <v>9086</v>
       </c>
       <c r="H11" s="9">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="I11" s="9">
-        <v>1164286</v>
+        <v>1165241</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" s="9">
-        <v>518992</v>
+        <v>519132</v>
       </c>
       <c r="D12" s="9">
-        <v>6360</v>
+        <v>6361</v>
       </c>
       <c r="E12" s="9">
         <v>6175</v>
       </c>
       <c r="F12" s="9">
-        <v>29403</v>
+        <v>29409</v>
       </c>
       <c r="G12" s="9">
         <v>2074</v>
@@ -2345,134 +2348,134 @@
         <v>521</v>
       </c>
       <c r="I12" s="9">
-        <v>525352</v>
+        <v>525493</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" s="9">
-        <v>405247</v>
+        <v>405332</v>
       </c>
       <c r="D13" s="9">
-        <v>4816</v>
+        <v>4823</v>
       </c>
       <c r="E13" s="9">
-        <v>4530</v>
+        <v>4534</v>
       </c>
       <c r="F13" s="9">
-        <v>29064</v>
+        <v>29075</v>
       </c>
       <c r="G13" s="9">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="H13" s="9">
         <v>488</v>
       </c>
       <c r="I13" s="9">
-        <v>410063</v>
+        <v>410155</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" s="9">
-        <v>342393</v>
+        <v>343013</v>
       </c>
       <c r="D14" s="9">
-        <v>9610</v>
+        <v>9586</v>
       </c>
       <c r="E14" s="9">
-        <v>3707</v>
+        <v>3718</v>
       </c>
       <c r="F14" s="9">
-        <v>22714</v>
+        <v>22746</v>
       </c>
       <c r="G14" s="9">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="H14" s="9">
         <v>392</v>
       </c>
       <c r="I14" s="9">
-        <v>352003</v>
+        <v>352599</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="9">
-        <v>417028</v>
+        <v>417113</v>
       </c>
       <c r="D15" s="9">
         <v>7899</v>
       </c>
       <c r="E15" s="9">
-        <v>6746</v>
+        <v>6745</v>
       </c>
       <c r="F15" s="9">
-        <v>28154</v>
+        <v>28159</v>
       </c>
       <c r="G15" s="9">
-        <v>4074</v>
+        <v>4077</v>
       </c>
       <c r="H15" s="9">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I15" s="9">
-        <v>424927</v>
+        <v>425012</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16" s="9">
-        <v>370121</v>
+        <v>370239</v>
       </c>
       <c r="D16" s="9">
-        <v>5162</v>
+        <v>5164</v>
       </c>
       <c r="E16" s="9">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="F16" s="9">
-        <v>21286</v>
+        <v>21294</v>
       </c>
       <c r="G16" s="9">
         <v>4298</v>
       </c>
       <c r="H16" s="9">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I16" s="9">
-        <v>375283</v>
+        <v>375403</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="9">
-        <v>199652</v>
+        <v>199768</v>
       </c>
       <c r="D17" s="9">
         <v>4871</v>
@@ -2481,7 +2484,7 @@
         <v>2195</v>
       </c>
       <c r="F17" s="9">
-        <v>10359</v>
+        <v>10360</v>
       </c>
       <c r="G17" s="9">
         <v>1728</v>
@@ -2490,18 +2493,18 @@
         <v>398</v>
       </c>
       <c r="I17" s="9">
-        <v>204523</v>
+        <v>204639</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="9">
-        <v>251694</v>
+        <v>251753</v>
       </c>
       <c r="D18" s="9">
         <v>5488</v>
@@ -2510,27 +2513,27 @@
         <v>2676</v>
       </c>
       <c r="F18" s="9">
-        <v>14387</v>
+        <v>14388</v>
       </c>
       <c r="G18" s="9">
-        <v>2411</v>
+        <v>2417</v>
       </c>
       <c r="H18" s="9">
         <v>495</v>
       </c>
       <c r="I18" s="9">
-        <v>257182</v>
+        <v>257241</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C19" s="9">
-        <v>139931</v>
+        <v>139937</v>
       </c>
       <c r="D19" s="9">
         <v>1706</v>
@@ -2539,7 +2542,7 @@
         <v>1062</v>
       </c>
       <c r="F19" s="9">
-        <v>10576</v>
+        <v>10579</v>
       </c>
       <c r="G19" s="9">
         <v>226</v>
@@ -2548,94 +2551,94 @@
         <v>233</v>
       </c>
       <c r="I19" s="9">
-        <v>141637</v>
+        <v>141643</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="9">
-        <v>708079</v>
+        <v>718218</v>
       </c>
       <c r="D20" s="9">
-        <v>7798</v>
+        <v>7877</v>
       </c>
       <c r="E20" s="9">
-        <v>4100</v>
+        <v>4162</v>
       </c>
       <c r="F20" s="9">
-        <v>19661</v>
+        <v>19892</v>
       </c>
       <c r="G20" s="9">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="H20" s="9">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I20" s="9">
-        <v>715877</v>
+        <v>726095</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="9">
-        <v>140284</v>
+        <v>141874</v>
       </c>
       <c r="D21" s="9">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="E21" s="9">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="F21" s="9">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="G21" s="9">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="H21" s="9">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I21" s="9">
-        <v>141503</v>
+        <v>143095</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="12">
-        <v>7259602</v>
+        <v>7276833</v>
       </c>
       <c r="D22" s="12">
-        <v>118187</v>
+        <v>118288</v>
       </c>
       <c r="E22" s="12">
-        <v>77233</v>
+        <v>77365</v>
       </c>
       <c r="F22" s="12">
-        <v>383633</v>
+        <v>384155</v>
       </c>
       <c r="G22" s="12">
-        <v>63080</v>
+        <v>63161</v>
       </c>
       <c r="H22" s="12">
-        <v>9848</v>
+        <v>9851</v>
       </c>
       <c r="I22" s="12">
-        <v>7377789</v>
+        <v>7395121</v>
       </c>
     </row>
   </sheetData>
@@ -2663,7 +2666,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2689,16 +2692,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2729,13 +2732,13 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>1485</v>
+        <v>1503</v>
       </c>
       <c r="D6" s="6">
-        <v>762</v>
+        <v>800</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F6" s="6">
         <v>4</v>
@@ -2755,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F7" s="9">
         <v>0</v>
@@ -2769,13 +2772,13 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D8" s="9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F8" s="9">
         <v>1</v>
@@ -2783,19 +2786,19 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="9">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D9" s="9">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F9" s="9">
         <v>1</v>
@@ -2803,19 +2806,19 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="9">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D10" s="9">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -2823,10 +2826,10 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="9">
         <v>223</v>
@@ -2835,7 +2838,7 @@
         <v>107</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
@@ -2843,19 +2846,19 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" s="9">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D12" s="9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F12" s="9">
         <v>1</v>
@@ -2863,19 +2866,19 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" s="9">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" s="9">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
@@ -2883,19 +2886,19 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" s="9">
         <v>101</v>
       </c>
       <c r="D14" s="9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -2903,10 +2906,10 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="9">
         <v>152</v>
@@ -2915,7 +2918,7 @@
         <v>124</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F15" s="9">
         <v>0</v>
@@ -2923,19 +2926,19 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16" s="9">
         <v>81</v>
       </c>
       <c r="D16" s="9">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
@@ -2943,10 +2946,10 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="9">
         <v>30</v>
@@ -2955,7 +2958,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F17" s="9">
         <v>1</v>
@@ -2963,19 +2966,19 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="9">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" s="9">
         <v>62</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
@@ -2983,10 +2986,10 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C19" s="9">
         <v>21</v>
@@ -2995,7 +2998,7 @@
         <v>16</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F19" s="9">
         <v>0</v>
@@ -3003,19 +3006,19 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="9">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D20" s="9">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -3023,19 +3026,19 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="9">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" s="9">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F21" s="9">
         <v>0</v>
@@ -3043,19 +3046,19 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="12">
-        <v>1485</v>
+        <v>1503</v>
       </c>
       <c r="D22" s="12">
-        <v>762</v>
+        <v>800</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F22" s="12">
         <v>4</v>

--- a/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
@@ -18,7 +18,7 @@
     <t>PROGRES PEMUTAKHIRAN KELUARGA - KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 13 Sep 2026, 12.16 | Dicetak: 13 Sep 2026, 14.35</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 15 Sep 2026, 06.16 | Dicetak: 15 Sep 2026, 06.35</t>
   </si>
   <si>
     <t>Kode</t>
@@ -123,7 +123,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>74,92</t>
+    <t>75,01</t>
   </si>
   <si>
     <t>1,88</t>
@@ -132,13 +132,13 @@
     <t>0,06</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>88,51</t>
+    <t>23,03</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>88,63</t>
   </si>
   <si>
     <t>1801</t>
@@ -156,310 +156,307 @@
     <t>0,03</t>
   </si>
   <si>
-    <t>18,26</t>
+    <t>18,35</t>
+  </si>
+  <si>
+    <t>0,01</t>
+  </si>
+  <si>
+    <t>94,22</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>79,69</t>
+  </si>
+  <si>
+    <t>1,06</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>18,99</t>
+  </si>
+  <si>
+    <t>97,61</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>75,34</t>
+  </si>
+  <si>
+    <t>1,32</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>23,09</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>90,55</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>77,8</t>
+  </si>
+  <si>
+    <t>1,99</t>
+  </si>
+  <si>
+    <t>20,02</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>88,48</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>76,59</t>
+  </si>
+  <si>
+    <t>2,85</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>20,09</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>86,88</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>71,06</t>
+  </si>
+  <si>
+    <t>1,97</t>
+  </si>
+  <si>
+    <t>26,83</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>83,83</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>78,24</t>
+  </si>
+  <si>
+    <t>1,78</t>
+  </si>
+  <si>
+    <t>19,73</t>
+  </si>
+  <si>
+    <t>92,37</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>70,95</t>
+  </si>
+  <si>
+    <t>2,32</t>
+  </si>
+  <si>
+    <t>27,54</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>85,29</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>75,84</t>
+  </si>
+  <si>
+    <t>3,06</t>
+  </si>
+  <si>
+    <t>21,63</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>81,32</t>
+  </si>
+  <si>
+    <t>1,53</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>17,33</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>92,2</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>74,82</t>
+  </si>
+  <si>
+    <t>1,58</t>
+  </si>
+  <si>
+    <t>24,57</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>91,88</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>2,45</t>
+  </si>
+  <si>
+    <t>22,85</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>88,01</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>82,93</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>17,1</t>
+  </si>
+  <si>
+    <t>101,88</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>62,09</t>
+  </si>
+  <si>
+    <t>0,97</t>
+  </si>
+  <si>
+    <t>36,29</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>79,47</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>75,45</t>
+  </si>
+  <si>
+    <t>1,46</t>
   </si>
   <si>
     <t>0,1</t>
   </si>
   <si>
-    <t>94,22</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>79,67</t>
-  </si>
-  <si>
-    <t>1,06</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>19,01</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>97,57</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>75,2</t>
-  </si>
-  <si>
-    <t>1,32</t>
-  </si>
-  <si>
-    <t>23,07</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>90,39</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>77,77</t>
-  </si>
-  <si>
-    <t>1,99</t>
-  </si>
-  <si>
-    <t>19,99</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>88,41</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>76,54</t>
-  </si>
-  <si>
-    <t>2,85</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>20,09</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>86,82</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>71,06</t>
-  </si>
-  <si>
-    <t>1,97</t>
-  </si>
-  <si>
-    <t>26,83</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>83,82</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>78,24</t>
-  </si>
-  <si>
-    <t>1,78</t>
-  </si>
-  <si>
-    <t>19,73</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>92,37</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>70,92</t>
-  </si>
-  <si>
-    <t>2,32</t>
-  </si>
-  <si>
-    <t>27,54</t>
-  </si>
-  <si>
-    <t>85,25</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>75,79</t>
-  </si>
-  <si>
-    <t>3,06</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>21,62</t>
-  </si>
-  <si>
-    <t>90,92</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>81,32</t>
-  </si>
-  <si>
-    <t>1,53</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>17,33</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>92,2</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>74,82</t>
-  </si>
-  <si>
-    <t>1,58</t>
-  </si>
-  <si>
-    <t>24,57</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>91,82</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>74,8</t>
-  </si>
-  <si>
-    <t>2,44</t>
-  </si>
-  <si>
-    <t>22,88</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>87,98</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>82,92</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>17,06</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>101,87</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>61,65</t>
-  </si>
-  <si>
-    <t>0,97</t>
-  </si>
-  <si>
-    <t>36,04</t>
-  </si>
-  <si>
-    <t>0,31</t>
-  </si>
-  <si>
-    <t>78,85</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>75,29</t>
-  </si>
-  <si>
-    <t>1,48</t>
-  </si>
-  <si>
-    <t>23,76</t>
-  </si>
-  <si>
-    <t>88,53</t>
+    <t>23,83</t>
+  </si>
+  <si>
+    <t>88,75</t>
   </si>
   <si>
     <t/>
@@ -501,34 +498,37 @@
     <t>Jumlah Bangunan Keluarga Khusus Berpindah-pindah Didata (K2)</t>
   </si>
   <si>
-    <t>53,23</t>
-  </si>
-  <si>
-    <t>23,86</t>
-  </si>
-  <si>
-    <t>58,33</t>
-  </si>
-  <si>
-    <t>44,1</t>
-  </si>
-  <si>
-    <t>47,98</t>
-  </si>
-  <si>
-    <t>57,33</t>
-  </si>
-  <si>
-    <t>43,84</t>
-  </si>
-  <si>
-    <t>21,78</t>
-  </si>
-  <si>
-    <t>81,58</t>
-  </si>
-  <si>
-    <t>82,72</t>
+    <t>58,83</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>21,57</t>
+  </si>
+  <si>
+    <t>60,62</t>
+  </si>
+  <si>
+    <t>46,58</t>
+  </si>
+  <si>
+    <t>62,01</t>
+  </si>
+  <si>
+    <t>78,67</t>
+  </si>
+  <si>
+    <t>64,47</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>88,89</t>
   </si>
   <si>
     <t>80</t>
@@ -537,10 +537,10 @@
     <t>100</t>
   </si>
   <si>
-    <t>76,19</t>
-  </si>
-  <si>
-    <t>16,98</t>
+    <t>80,95</t>
+  </si>
+  <si>
+    <t>15,88</t>
   </si>
   <si>
     <t>96</t>
@@ -1204,40 +1204,40 @@
         <v>2730939</v>
       </c>
       <c r="D6" s="6">
-        <v>2046078</v>
+        <v>2048409</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="6">
-        <v>371200</v>
+        <v>372141</v>
       </c>
       <c r="G6" s="6">
-        <v>51217</v>
+        <v>51223</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="6">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="6">
-        <v>628070</v>
+        <v>628998</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="6">
-        <v>5579</v>
+        <v>5601</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="6">
-        <v>2417278</v>
+        <v>2420550</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>41</v>
@@ -1275,13 +1275,13 @@
         <v>46</v>
       </c>
       <c r="K7" s="9">
-        <v>15549</v>
+        <v>15625</v>
       </c>
       <c r="L7" s="10" t="s">
         <v>47</v>
       </c>
       <c r="M7" s="9">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="N7" s="10" t="s">
         <v>48</v>
@@ -1304,90 +1304,90 @@
         <v>172957</v>
       </c>
       <c r="D8" s="9">
-        <v>137794</v>
+        <v>137831</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="9">
-        <v>30965</v>
+        <v>30996</v>
       </c>
       <c r="G8" s="9">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>53</v>
       </c>
       <c r="I8" s="9">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>54</v>
       </c>
       <c r="K8" s="9">
-        <v>32880</v>
+        <v>32850</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>55</v>
       </c>
       <c r="M8" s="9">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="N8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" s="9">
+        <v>168827</v>
+      </c>
+      <c r="P8" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="O8" s="9">
-        <v>168759</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="C9" s="9">
         <v>342736</v>
       </c>
       <c r="D9" s="9">
-        <v>257735</v>
+        <v>258220</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="9">
+        <v>52128</v>
+      </c>
+      <c r="G9" s="9">
+        <v>4522</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="9">
-        <v>52073</v>
-      </c>
-      <c r="G9" s="9">
-        <v>4520</v>
-      </c>
-      <c r="H9" s="10" t="s">
+      <c r="I9" s="9">
+        <v>226</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="9">
-        <v>215</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>38</v>
-      </c>
       <c r="K9" s="9">
-        <v>79085</v>
+        <v>79127</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>62</v>
       </c>
       <c r="M9" s="9">
-        <v>742</v>
+        <v>649</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>63</v>
       </c>
       <c r="O9" s="9">
-        <v>309808</v>
+        <v>310348</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>64</v>
@@ -1404,13 +1404,13 @@
         <v>362841</v>
       </c>
       <c r="D10" s="9">
-        <v>282174</v>
+        <v>282304</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>67</v>
       </c>
       <c r="F10" s="9">
-        <v>38622</v>
+        <v>38738</v>
       </c>
       <c r="G10" s="9">
         <v>7208</v>
@@ -1419,25 +1419,25 @@
         <v>68</v>
       </c>
       <c r="I10" s="9">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>38</v>
       </c>
       <c r="K10" s="9">
-        <v>72539</v>
+        <v>72634</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>69</v>
       </c>
       <c r="M10" s="9">
-        <v>609</v>
+        <v>473</v>
       </c>
       <c r="N10" s="10" t="s">
         <v>70</v>
       </c>
       <c r="O10" s="9">
-        <v>320796</v>
+        <v>321042</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>71</v>
@@ -1454,40 +1454,40 @@
         <v>449576</v>
       </c>
       <c r="D11" s="9">
-        <v>344101</v>
+        <v>344323</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F11" s="9">
-        <v>46203</v>
+        <v>46247</v>
       </c>
       <c r="G11" s="9">
-        <v>12825</v>
+        <v>12826</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>75</v>
       </c>
       <c r="I11" s="9">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>76</v>
       </c>
       <c r="K11" s="9">
-        <v>90310</v>
+        <v>90307</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>77</v>
       </c>
       <c r="M11" s="9">
-        <v>1574</v>
+        <v>1557</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>78</v>
       </c>
       <c r="O11" s="9">
-        <v>390304</v>
+        <v>390570</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>79</v>
@@ -1504,13 +1504,13 @@
         <v>199396</v>
       </c>
       <c r="D12" s="9">
-        <v>141688</v>
+        <v>141690</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>82</v>
       </c>
       <c r="F12" s="9">
-        <v>25450</v>
+        <v>25455</v>
       </c>
       <c r="G12" s="9">
         <v>3932</v>
@@ -1525,19 +1525,19 @@
         <v>46</v>
       </c>
       <c r="K12" s="9">
-        <v>53497</v>
+        <v>53495</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>84</v>
       </c>
       <c r="M12" s="9">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N12" s="10" t="s">
         <v>85</v>
       </c>
       <c r="O12" s="9">
-        <v>167138</v>
+        <v>167145</v>
       </c>
       <c r="P12" s="10" t="s">
         <v>86</v>
@@ -1560,7 +1560,7 @@
         <v>89</v>
       </c>
       <c r="F13" s="9">
-        <v>20632</v>
+        <v>20640</v>
       </c>
       <c r="G13" s="9">
         <v>2597</v>
@@ -1575,48 +1575,48 @@
         <v>38</v>
       </c>
       <c r="K13" s="9">
-        <v>28829</v>
+        <v>28830</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>91</v>
       </c>
       <c r="M13" s="9">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N13" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O13" s="9">
+        <v>134949</v>
+      </c>
+      <c r="P13" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="O13" s="9">
-        <v>134941</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>95</v>
       </c>
       <c r="C14" s="9">
         <v>135256</v>
       </c>
       <c r="D14" s="9">
-        <v>95927</v>
+        <v>95962</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" s="9">
-        <v>19382</v>
+        <v>19403</v>
       </c>
       <c r="G14" s="9">
         <v>3136</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I14" s="9">
         <v>36</v>
@@ -1625,19 +1625,19 @@
         <v>46</v>
       </c>
       <c r="K14" s="9">
-        <v>37243</v>
+        <v>37249</v>
       </c>
       <c r="L14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="M14" s="9">
+        <v>55</v>
+      </c>
+      <c r="N14" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="M14" s="9">
-        <v>80</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>38</v>
-      </c>
       <c r="O14" s="9">
-        <v>115309</v>
+        <v>115365</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>99</v>
@@ -1654,13 +1654,13 @@
         <v>152158</v>
       </c>
       <c r="D15" s="9">
-        <v>115320</v>
+        <v>115398</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>102</v>
       </c>
       <c r="F15" s="9">
-        <v>23020</v>
+        <v>23069</v>
       </c>
       <c r="G15" s="9">
         <v>4661</v>
@@ -1669,25 +1669,25 @@
         <v>103</v>
       </c>
       <c r="I15" s="9">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J15" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" s="9">
+        <v>32919</v>
+      </c>
+      <c r="L15" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="K15" s="9">
-        <v>32903</v>
-      </c>
-      <c r="L15" s="10" t="s">
+      <c r="M15" s="9">
+        <v>25</v>
+      </c>
+      <c r="N15" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="M15" s="9">
-        <v>73</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="O15" s="9">
-        <v>138340</v>
+        <v>138467</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>106</v>
@@ -1704,13 +1704,13 @@
         <v>135741</v>
       </c>
       <c r="D16" s="9">
-        <v>110381</v>
+        <v>110380</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>109</v>
       </c>
       <c r="F16" s="9">
-        <v>14772</v>
+        <v>14774</v>
       </c>
       <c r="G16" s="9">
         <v>2073</v>
@@ -1725,7 +1725,7 @@
         <v>111</v>
       </c>
       <c r="K16" s="9">
-        <v>23518</v>
+        <v>23519</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>112</v>
@@ -1737,7 +1737,7 @@
         <v>113</v>
       </c>
       <c r="O16" s="9">
-        <v>125153</v>
+        <v>125154</v>
       </c>
       <c r="P16" s="10" t="s">
         <v>114</v>
@@ -1754,13 +1754,13 @@
         <v>75116</v>
       </c>
       <c r="D17" s="9">
-        <v>56201</v>
+        <v>56202</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>117</v>
       </c>
       <c r="F17" s="9">
-        <v>12770</v>
+        <v>12818</v>
       </c>
       <c r="G17" s="9">
         <v>1189</v>
@@ -1772,7 +1772,7 @@
         <v>144</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="K17" s="9">
         <v>18453</v>
@@ -1781,13 +1781,13 @@
         <v>119</v>
       </c>
       <c r="M17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="10" t="s">
         <v>120</v>
       </c>
       <c r="O17" s="9">
-        <v>68971</v>
+        <v>69020</v>
       </c>
       <c r="P17" s="10" t="s">
         <v>121</v>
@@ -1804,19 +1804,19 @@
         <v>99169</v>
       </c>
       <c r="D18" s="9">
-        <v>74177</v>
+        <v>74201</v>
       </c>
       <c r="E18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="9">
+        <v>13081</v>
+      </c>
+      <c r="G18" s="9">
+        <v>2425</v>
+      </c>
+      <c r="H18" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="F18" s="9">
-        <v>13075</v>
-      </c>
-      <c r="G18" s="9">
-        <v>2421</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I18" s="9">
         <v>54</v>
@@ -1825,39 +1825,39 @@
         <v>54</v>
       </c>
       <c r="K18" s="9">
-        <v>22694</v>
+        <v>22663</v>
       </c>
       <c r="L18" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="M18" s="9">
+        <v>299</v>
+      </c>
+      <c r="N18" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="M18" s="9">
-        <v>289</v>
-      </c>
-      <c r="N18" s="10" t="s">
+      <c r="O18" s="9">
+        <v>87282</v>
+      </c>
+      <c r="P18" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="O18" s="9">
-        <v>87252</v>
-      </c>
-      <c r="P18" s="10" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>129</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>130</v>
       </c>
       <c r="C19" s="9">
         <v>41772</v>
       </c>
       <c r="D19" s="9">
-        <v>34636</v>
+        <v>34640</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F19" s="9">
         <v>7919</v>
@@ -1866,7 +1866,7 @@
         <v>357</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I19" s="9">
         <v>27</v>
@@ -1875,169 +1875,169 @@
         <v>38</v>
       </c>
       <c r="K19" s="9">
-        <v>7125</v>
+        <v>7141</v>
       </c>
       <c r="L19" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="M19" s="9">
+        <v>8</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="O19" s="9">
+        <v>42559</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="M19" s="9">
-        <v>28</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="O19" s="9">
-        <v>42555</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C20" s="9">
         <v>279478</v>
       </c>
       <c r="D20" s="9">
-        <v>172302</v>
+        <v>173531</v>
       </c>
       <c r="E20" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" s="9">
+        <v>48579</v>
+      </c>
+      <c r="G20" s="9">
+        <v>2703</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="I20" s="9">
+        <v>185</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K20" s="9">
+        <v>101435</v>
+      </c>
+      <c r="L20" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="9">
-        <v>48056</v>
-      </c>
-      <c r="G20" s="9">
-        <v>2698</v>
-      </c>
-      <c r="H20" s="10" t="s">
+      <c r="M20" s="9">
+        <v>1274</v>
+      </c>
+      <c r="N20" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="I20" s="9">
-        <v>191</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="K20" s="9">
-        <v>100730</v>
-      </c>
-      <c r="L20" s="10" t="s">
+      <c r="O20" s="9">
+        <v>222110</v>
+      </c>
+      <c r="P20" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="M20" s="9">
-        <v>855</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="O20" s="9">
-        <v>220358</v>
-      </c>
-      <c r="P20" s="10" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9">
         <v>53506</v>
       </c>
       <c r="D21" s="9">
-        <v>40286</v>
+        <v>40371</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F21" s="9">
-        <v>7081</v>
+        <v>7114</v>
       </c>
       <c r="G21" s="9">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I21" s="9">
         <v>51</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
       <c r="K21" s="9">
-        <v>12715</v>
+        <v>12751</v>
       </c>
       <c r="L21" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="M21" s="9">
+        <v>22</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="O21" s="9">
+        <v>47485</v>
+      </c>
+      <c r="P21" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="M21" s="9">
-        <v>24</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="O21" s="9">
-        <v>47367</v>
-      </c>
-      <c r="P21" s="10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="C22" s="12">
         <v>2730939</v>
       </c>
       <c r="D22" s="12">
-        <v>2046078</v>
+        <v>2048409</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="12">
-        <v>371200</v>
+        <v>372141</v>
       </c>
       <c r="G22" s="12">
-        <v>51217</v>
+        <v>51223</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="12">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="12">
-        <v>628070</v>
+        <v>628998</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="12">
-        <v>5579</v>
+        <v>5601</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="O22" s="12">
-        <v>2417278</v>
+        <v>2420550</v>
       </c>
       <c r="P22" s="13" t="s">
         <v>41</v>
@@ -2066,7 +2066,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2098,25 +2098,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2156,25 +2156,25 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>7276833</v>
+        <v>7286572</v>
       </c>
       <c r="D6" s="6">
-        <v>118288</v>
+        <v>118351</v>
       </c>
       <c r="E6" s="6">
-        <v>77365</v>
+        <v>77446</v>
       </c>
       <c r="F6" s="6">
-        <v>384155</v>
+        <v>384459</v>
       </c>
       <c r="G6" s="6">
-        <v>63161</v>
+        <v>63214</v>
       </c>
       <c r="H6" s="6">
-        <v>9851</v>
+        <v>9853</v>
       </c>
       <c r="I6" s="6">
-        <v>7395121</v>
+        <v>7404923</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2214,54 +2214,54 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>515815</v>
+        <v>516000</v>
       </c>
       <c r="D8" s="9">
-        <v>6563</v>
+        <v>6566</v>
       </c>
       <c r="E8" s="9">
-        <v>5024</v>
+        <v>5027</v>
       </c>
       <c r="F8" s="9">
-        <v>38836</v>
+        <v>38858</v>
       </c>
       <c r="G8" s="9">
-        <v>4576</v>
+        <v>4577</v>
       </c>
       <c r="H8" s="9">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I8" s="9">
-        <v>522378</v>
+        <v>522566</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="C9" s="9">
-        <v>948500</v>
+        <v>950207</v>
       </c>
       <c r="D9" s="9">
-        <v>15453</v>
+        <v>15463</v>
       </c>
       <c r="E9" s="9">
-        <v>10610</v>
+        <v>10628</v>
       </c>
       <c r="F9" s="9">
-        <v>45231</v>
+        <v>45289</v>
       </c>
       <c r="G9" s="9">
-        <v>5561</v>
+        <v>5567</v>
       </c>
       <c r="H9" s="9">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="I9" s="9">
-        <v>963953</v>
+        <v>965670</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2272,25 +2272,25 @@
         <v>66</v>
       </c>
       <c r="C10" s="9">
-        <v>910875</v>
+        <v>911553</v>
       </c>
       <c r="D10" s="9">
-        <v>16709</v>
+        <v>16727</v>
       </c>
       <c r="E10" s="9">
-        <v>10681</v>
+        <v>10690</v>
       </c>
       <c r="F10" s="9">
-        <v>44212</v>
+        <v>44227</v>
       </c>
       <c r="G10" s="9">
-        <v>22764</v>
+        <v>22787</v>
       </c>
       <c r="H10" s="9">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="I10" s="9">
-        <v>927584</v>
+        <v>928280</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2301,25 +2301,25 @@
         <v>73</v>
       </c>
       <c r="C11" s="9">
-        <v>1143603</v>
+        <v>1144429</v>
       </c>
       <c r="D11" s="9">
-        <v>21638</v>
+        <v>21640</v>
       </c>
       <c r="E11" s="9">
-        <v>13458</v>
+        <v>13469</v>
       </c>
       <c r="F11" s="9">
-        <v>50614</v>
+        <v>50682</v>
       </c>
       <c r="G11" s="9">
-        <v>9086</v>
+        <v>9091</v>
       </c>
       <c r="H11" s="9">
         <v>1874</v>
       </c>
       <c r="I11" s="9">
-        <v>1165241</v>
+        <v>1166069</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2330,16 +2330,16 @@
         <v>81</v>
       </c>
       <c r="C12" s="9">
-        <v>519132</v>
+        <v>519157</v>
       </c>
       <c r="D12" s="9">
-        <v>6361</v>
+        <v>6362</v>
       </c>
       <c r="E12" s="9">
         <v>6175</v>
       </c>
       <c r="F12" s="9">
-        <v>29409</v>
+        <v>29415</v>
       </c>
       <c r="G12" s="9">
         <v>2074</v>
@@ -2348,7 +2348,7 @@
         <v>521</v>
       </c>
       <c r="I12" s="9">
-        <v>525493</v>
+        <v>525519</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2359,7 +2359,7 @@
         <v>88</v>
       </c>
       <c r="C13" s="9">
-        <v>405332</v>
+        <v>405349</v>
       </c>
       <c r="D13" s="9">
         <v>4823</v>
@@ -2368,7 +2368,7 @@
         <v>4534</v>
       </c>
       <c r="F13" s="9">
-        <v>29075</v>
+        <v>29077</v>
       </c>
       <c r="G13" s="9">
         <v>1635</v>
@@ -2377,36 +2377,36 @@
         <v>488</v>
       </c>
       <c r="I13" s="9">
-        <v>410155</v>
+        <v>410172</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>95</v>
-      </c>
       <c r="C14" s="9">
-        <v>343013</v>
+        <v>343202</v>
       </c>
       <c r="D14" s="9">
-        <v>9586</v>
+        <v>9585</v>
       </c>
       <c r="E14" s="9">
-        <v>3718</v>
+        <v>3719</v>
       </c>
       <c r="F14" s="9">
-        <v>22746</v>
+        <v>22763</v>
       </c>
       <c r="G14" s="9">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="H14" s="9">
         <v>392</v>
       </c>
       <c r="I14" s="9">
-        <v>352599</v>
+        <v>352787</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2417,25 +2417,25 @@
         <v>101</v>
       </c>
       <c r="C15" s="9">
-        <v>417113</v>
+        <v>417508</v>
       </c>
       <c r="D15" s="9">
-        <v>7899</v>
+        <v>7901</v>
       </c>
       <c r="E15" s="9">
-        <v>6745</v>
+        <v>6753</v>
       </c>
       <c r="F15" s="9">
-        <v>28159</v>
+        <v>28172</v>
       </c>
       <c r="G15" s="9">
-        <v>4077</v>
+        <v>4080</v>
       </c>
       <c r="H15" s="9">
         <v>517</v>
       </c>
       <c r="I15" s="9">
-        <v>425012</v>
+        <v>425409</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2446,7 +2446,7 @@
         <v>108</v>
       </c>
       <c r="C16" s="9">
-        <v>370239</v>
+        <v>370250</v>
       </c>
       <c r="D16" s="9">
         <v>5164</v>
@@ -2455,7 +2455,7 @@
         <v>3205</v>
       </c>
       <c r="F16" s="9">
-        <v>21294</v>
+        <v>21295</v>
       </c>
       <c r="G16" s="9">
         <v>4298</v>
@@ -2464,7 +2464,7 @@
         <v>249</v>
       </c>
       <c r="I16" s="9">
-        <v>375403</v>
+        <v>375414</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2475,7 +2475,7 @@
         <v>116</v>
       </c>
       <c r="C17" s="9">
-        <v>199768</v>
+        <v>199922</v>
       </c>
       <c r="D17" s="9">
         <v>4871</v>
@@ -2484,7 +2484,7 @@
         <v>2195</v>
       </c>
       <c r="F17" s="9">
-        <v>10360</v>
+        <v>10362</v>
       </c>
       <c r="G17" s="9">
         <v>1728</v>
@@ -2493,7 +2493,7 @@
         <v>398</v>
       </c>
       <c r="I17" s="9">
-        <v>204639</v>
+        <v>204793</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2504,36 +2504,36 @@
         <v>123</v>
       </c>
       <c r="C18" s="9">
-        <v>251753</v>
+        <v>251821</v>
       </c>
       <c r="D18" s="9">
-        <v>5488</v>
+        <v>5494</v>
       </c>
       <c r="E18" s="9">
         <v>2676</v>
       </c>
       <c r="F18" s="9">
-        <v>14388</v>
+        <v>14397</v>
       </c>
       <c r="G18" s="9">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="H18" s="9">
         <v>495</v>
       </c>
       <c r="I18" s="9">
-        <v>257241</v>
+        <v>257315</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>130</v>
-      </c>
       <c r="C19" s="9">
-        <v>139937</v>
+        <v>139948</v>
       </c>
       <c r="D19" s="9">
         <v>1706</v>
@@ -2542,7 +2542,7 @@
         <v>1062</v>
       </c>
       <c r="F19" s="9">
-        <v>10579</v>
+        <v>10581</v>
       </c>
       <c r="G19" s="9">
         <v>226</v>
@@ -2551,94 +2551,94 @@
         <v>233</v>
       </c>
       <c r="I19" s="9">
-        <v>141643</v>
+        <v>141654</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C20" s="9">
-        <v>718218</v>
+        <v>723335</v>
       </c>
       <c r="D20" s="9">
-        <v>7877</v>
+        <v>7904</v>
       </c>
       <c r="E20" s="9">
-        <v>4162</v>
+        <v>4193</v>
       </c>
       <c r="F20" s="9">
-        <v>19892</v>
+        <v>19975</v>
       </c>
       <c r="G20" s="9">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="H20" s="9">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="I20" s="9">
-        <v>726095</v>
+        <v>731239</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9">
-        <v>141874</v>
+        <v>142230</v>
       </c>
       <c r="D21" s="9">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="E21" s="9">
         <v>978</v>
       </c>
       <c r="F21" s="9">
-        <v>5994</v>
+        <v>6000</v>
       </c>
       <c r="G21" s="9">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="H21" s="9">
         <v>773</v>
       </c>
       <c r="I21" s="9">
-        <v>143095</v>
+        <v>143446</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>150</v>
-      </c>
       <c r="C22" s="12">
-        <v>7276833</v>
+        <v>7286572</v>
       </c>
       <c r="D22" s="12">
-        <v>118288</v>
+        <v>118351</v>
       </c>
       <c r="E22" s="12">
-        <v>77365</v>
+        <v>77446</v>
       </c>
       <c r="F22" s="12">
-        <v>384155</v>
+        <v>384459</v>
       </c>
       <c r="G22" s="12">
-        <v>63161</v>
+        <v>63214</v>
       </c>
       <c r="H22" s="12">
-        <v>9851</v>
+        <v>9853</v>
       </c>
       <c r="I22" s="12">
-        <v>7395121</v>
+        <v>7404923</v>
       </c>
     </row>
   </sheetData>
@@ -2666,7 +2666,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2692,16 +2692,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2732,16 +2732,16 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>1503</v>
+        <v>1535</v>
       </c>
       <c r="D6" s="6">
-        <v>800</v>
+        <v>903</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F6" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2755,10 +2755,10 @@
         <v>10</v>
       </c>
       <c r="D7" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="F7" s="9">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D8" s="9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>163</v>
@@ -2786,16 +2786,16 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="C9" s="9">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D9" s="9">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>164</v>
@@ -2815,7 +2815,7 @@
         <v>161</v>
       </c>
       <c r="D10" s="9">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>165</v>
@@ -2832,10 +2832,10 @@
         <v>73</v>
       </c>
       <c r="C11" s="9">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D11" s="9">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>166</v>
@@ -2855,7 +2855,7 @@
         <v>75</v>
       </c>
       <c r="D12" s="9">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>167</v>
@@ -2872,10 +2872,10 @@
         <v>88</v>
       </c>
       <c r="C13" s="9">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" s="9">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>168</v>
@@ -2886,16 +2886,16 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>95</v>
-      </c>
       <c r="C14" s="9">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" s="9">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>169</v>
@@ -2912,16 +2912,16 @@
         <v>101</v>
       </c>
       <c r="C15" s="9">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D15" s="9">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>170</v>
       </c>
       <c r="F15" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2935,7 +2935,7 @@
         <v>81</v>
       </c>
       <c r="D16" s="9">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>171</v>
@@ -2986,33 +2986,33 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>129</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>130</v>
       </c>
       <c r="C19" s="9">
         <v>21</v>
       </c>
       <c r="D19" s="9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>174</v>
       </c>
       <c r="F19" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C20" s="9">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D20" s="9">
         <v>27</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C21" s="9">
         <v>75</v>
@@ -3046,22 +3046,22 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>150</v>
-      </c>
       <c r="C22" s="12">
-        <v>1503</v>
+        <v>1535</v>
       </c>
       <c r="D22" s="12">
-        <v>800</v>
+        <v>903</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F22" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
+++ b/data/Export_Progres_Pemutakhiran_Keluarga_Kabupaten_Kota.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="179">
   <si>
     <t>PROGRES PEMUTAKHIRAN KELUARGA - KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 15 Sep 2026, 06.16 | Dicetak: 15 Sep 2026, 06.35</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 16 Sep 2026, 06.16 | Dicetak: 16 Sep 2026, 08.56</t>
   </si>
   <si>
     <t>Kode</t>
@@ -123,7 +123,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>75,01</t>
+    <t>75,02</t>
   </si>
   <si>
     <t>1,88</t>
@@ -135,55 +135,58 @@
     <t>23,03</t>
   </si>
   <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>88,65</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>81,09</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>18,35</t>
+  </si>
+  <si>
+    <t>0,01</t>
+  </si>
+  <si>
+    <t>94,23</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>79,69</t>
+  </si>
+  <si>
+    <t>1,06</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>18,99</t>
+  </si>
+  <si>
     <t>0,21</t>
   </si>
   <si>
-    <t>88,63</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>81,09</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>18,35</t>
-  </si>
-  <si>
-    <t>0,01</t>
-  </si>
-  <si>
-    <t>94,22</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>79,69</t>
-  </si>
-  <si>
-    <t>1,06</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>18,99</t>
-  </si>
-  <si>
-    <t>97,61</t>
+    <t>97,62</t>
   </si>
   <si>
     <t>1803</t>
@@ -192,7 +195,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>75,34</t>
+    <t>75,38</t>
   </si>
   <si>
     <t>1,32</t>
@@ -201,13 +204,13 @@
     <t>0,07</t>
   </si>
   <si>
-    <t>23,09</t>
+    <t>23,1</t>
   </si>
   <si>
     <t>0,19</t>
   </si>
   <si>
-    <t>90,55</t>
+    <t>90,59</t>
   </si>
   <si>
     <t>1804</t>
@@ -216,7 +219,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>77,8</t>
+    <t>77,81</t>
   </si>
   <si>
     <t>1,99</t>
@@ -225,10 +228,10 @@
     <t>20,02</t>
   </si>
   <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>88,48</t>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>88,49</t>
   </si>
   <si>
     <t>1805</t>
@@ -237,7 +240,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>76,59</t>
+    <t>76,6</t>
   </si>
   <si>
     <t>2,85</t>
@@ -249,7 +252,7 @@
     <t>20,09</t>
   </si>
   <si>
-    <t>0,35</t>
+    <t>0,34</t>
   </si>
   <si>
     <t>86,88</t>
@@ -270,7 +273,7 @@
     <t>26,83</t>
   </si>
   <si>
-    <t>0,12</t>
+    <t>0,11</t>
   </si>
   <si>
     <t>83,83</t>
@@ -282,7 +285,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>78,24</t>
+    <t>78,25</t>
   </si>
   <si>
     <t>1,78</t>
@@ -300,19 +303,19 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>70,95</t>
+    <t>70,91</t>
   </si>
   <si>
     <t>2,32</t>
   </si>
   <si>
-    <t>27,54</t>
+    <t>27,59</t>
   </si>
   <si>
     <t>0,04</t>
   </si>
   <si>
-    <t>85,29</t>
+    <t>85,28</t>
   </si>
   <si>
     <t>1809</t>
@@ -333,7 +336,7 @@
     <t>0,02</t>
   </si>
   <si>
-    <t>91</t>
+    <t>91,01</t>
   </si>
   <si>
     <t>1810</t>
@@ -354,7 +357,7 @@
     <t>17,33</t>
   </si>
   <si>
-    <t>0,26</t>
+    <t>0,27</t>
   </si>
   <si>
     <t>92,2</t>
@@ -366,19 +369,19 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>74,82</t>
-  </si>
-  <si>
-    <t>1,58</t>
-  </si>
-  <si>
-    <t>24,57</t>
+    <t>74,91</t>
+  </si>
+  <si>
+    <t>1,59</t>
+  </si>
+  <si>
+    <t>24,47</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>91,88</t>
+    <t>91,94</t>
   </si>
   <si>
     <t>1812</t>
@@ -387,16 +390,19 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
+    <t>74,83</t>
+  </si>
+  <si>
     <t>2,45</t>
   </si>
   <si>
-    <t>22,85</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>88,01</t>
+    <t>22,84</t>
+  </si>
+  <si>
+    <t>0,31</t>
+  </si>
+  <si>
+    <t>88,02</t>
   </si>
   <si>
     <t>1813</t>
@@ -414,7 +420,7 @@
     <t>17,1</t>
   </si>
   <si>
-    <t>101,88</t>
+    <t>101,89</t>
   </si>
   <si>
     <t>1871</t>
@@ -423,7 +429,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>62,09</t>
+    <t>62,13</t>
   </si>
   <si>
     <t>0,97</t>
@@ -432,10 +438,10 @@
     <t>36,29</t>
   </si>
   <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>79,47</t>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>79,56</t>
   </si>
   <si>
     <t>1872</t>
@@ -453,10 +459,10 @@
     <t>0,1</t>
   </si>
   <si>
-    <t>23,83</t>
-  </si>
-  <si>
-    <t>88,75</t>
+    <t>23,85</t>
+  </si>
+  <si>
+    <t>88,74</t>
   </si>
   <si>
     <t/>
@@ -498,37 +504,37 @@
     <t>Jumlah Bangunan Keluarga Khusus Berpindah-pindah Didata (K2)</t>
   </si>
   <si>
-    <t>58,83</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>21,57</t>
-  </si>
-  <si>
-    <t>60,62</t>
-  </si>
-  <si>
-    <t>46,58</t>
-  </si>
-  <si>
-    <t>62,01</t>
-  </si>
-  <si>
-    <t>78,67</t>
-  </si>
-  <si>
-    <t>64,47</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>88,89</t>
+    <t>66,43</t>
+  </si>
+  <si>
+    <t>44,44</t>
+  </si>
+  <si>
+    <t>35,77</t>
+  </si>
+  <si>
+    <t>65,28</t>
+  </si>
+  <si>
+    <t>50,93</t>
+  </si>
+  <si>
+    <t>91,48</t>
+  </si>
+  <si>
+    <t>81,33</t>
+  </si>
+  <si>
+    <t>68,83</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>91,36</t>
   </si>
   <si>
     <t>80</t>
@@ -537,13 +543,13 @@
     <t>100</t>
   </si>
   <si>
-    <t>80,95</t>
-  </si>
-  <si>
-    <t>15,88</t>
-  </si>
-  <si>
-    <t>96</t>
+    <t>85,71</t>
+  </si>
+  <si>
+    <t>15,7</t>
+  </si>
+  <si>
+    <t>97,33</t>
   </si>
 </sst>
 </file>
@@ -1204,13 +1210,13 @@
         <v>2730939</v>
       </c>
       <c r="D6" s="6">
-        <v>2048409</v>
+        <v>2048724</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="6">
-        <v>372141</v>
+        <v>372347</v>
       </c>
       <c r="G6" s="6">
         <v>51223</v>
@@ -1219,25 +1225,25 @@
         <v>37</v>
       </c>
       <c r="I6" s="6">
-        <v>1761</v>
+        <v>1758</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="6">
-        <v>628998</v>
+        <v>629028</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="M6" s="6">
-        <v>5601</v>
+        <v>5956</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="6">
-        <v>2420550</v>
+        <v>2421071</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>41</v>
@@ -1260,7 +1266,7 @@
         <v>44</v>
       </c>
       <c r="F7" s="9">
-        <v>11180</v>
+        <v>11182</v>
       </c>
       <c r="G7" s="9">
         <v>971</v>
@@ -1287,7 +1293,7 @@
         <v>48</v>
       </c>
       <c r="O7" s="9">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="P7" s="10" t="s">
         <v>49</v>
@@ -1310,7 +1316,7 @@
         <v>52</v>
       </c>
       <c r="F8" s="9">
-        <v>30996</v>
+        <v>31004</v>
       </c>
       <c r="G8" s="9">
         <v>1840</v>
@@ -1331,92 +1337,92 @@
         <v>55</v>
       </c>
       <c r="M8" s="9">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="O8" s="9">
-        <v>168827</v>
+        <v>168835</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="9">
         <v>342736</v>
       </c>
       <c r="D9" s="9">
-        <v>258220</v>
+        <v>258346</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" s="9">
-        <v>52128</v>
+        <v>52131</v>
       </c>
       <c r="G9" s="9">
-        <v>4522</v>
+        <v>4523</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I9" s="9">
         <v>226</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" s="9">
-        <v>79127</v>
+        <v>79157</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M9" s="9">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O9" s="9">
-        <v>310348</v>
+        <v>310477</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="9">
         <v>362841</v>
       </c>
       <c r="D10" s="9">
-        <v>282304</v>
+        <v>282312</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" s="9">
-        <v>38738</v>
+        <v>38771</v>
       </c>
       <c r="G10" s="9">
         <v>7208</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I10" s="9">
         <v>215</v>
@@ -1425,139 +1431,139 @@
         <v>38</v>
       </c>
       <c r="K10" s="9">
-        <v>72634</v>
+        <v>72637</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M10" s="9">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O10" s="9">
-        <v>321042</v>
+        <v>321083</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" s="9">
         <v>449576</v>
       </c>
       <c r="D11" s="9">
-        <v>344323</v>
+        <v>344356</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" s="9">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="G11" s="9">
         <v>12826</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I11" s="9">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K11" s="9">
-        <v>90307</v>
+        <v>90308</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M11" s="9">
-        <v>1557</v>
+        <v>1548</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O11" s="9">
-        <v>390570</v>
+        <v>390607</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="9">
         <v>199396</v>
       </c>
       <c r="D12" s="9">
-        <v>141690</v>
+        <v>141699</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F12" s="9">
-        <v>25455</v>
+        <v>25457</v>
       </c>
       <c r="G12" s="9">
         <v>3932</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I12" s="9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>46</v>
       </c>
       <c r="K12" s="9">
-        <v>53495</v>
+        <v>53500</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M12" s="9">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O12" s="9">
-        <v>167145</v>
+        <v>167156</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" s="9">
         <v>146092</v>
       </c>
       <c r="D13" s="9">
-        <v>114309</v>
+        <v>114310</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F13" s="9">
         <v>20640</v>
@@ -1566,7 +1572,7 @@
         <v>2597</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I13" s="9">
         <v>92</v>
@@ -1575,48 +1581,48 @@
         <v>38</v>
       </c>
       <c r="K13" s="9">
-        <v>28830</v>
+        <v>28829</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M13" s="9">
         <v>279</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O13" s="9">
-        <v>134949</v>
+        <v>134950</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" s="9">
-        <v>135256</v>
+        <v>135357</v>
       </c>
       <c r="D14" s="9">
-        <v>95962</v>
+        <v>95978</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" s="9">
-        <v>19403</v>
+        <v>19454</v>
       </c>
       <c r="G14" s="9">
         <v>3136</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I14" s="9">
         <v>36</v>
@@ -1625,89 +1631,89 @@
         <v>46</v>
       </c>
       <c r="K14" s="9">
-        <v>37249</v>
+        <v>37346</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M14" s="9">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O14" s="9">
-        <v>115365</v>
+        <v>115432</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" s="9">
         <v>152158</v>
       </c>
       <c r="D15" s="9">
-        <v>115398</v>
+        <v>115401</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F15" s="9">
-        <v>23069</v>
+        <v>23079</v>
       </c>
       <c r="G15" s="9">
         <v>4661</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I15" s="9">
         <v>55</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K15" s="9">
-        <v>32919</v>
+        <v>32918</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M15" s="9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O15" s="9">
-        <v>138467</v>
+        <v>138480</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" s="9">
         <v>135741</v>
       </c>
       <c r="D16" s="9">
-        <v>110380</v>
+        <v>110383</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F16" s="9">
         <v>14774</v>
@@ -1716,98 +1722,98 @@
         <v>2073</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I16" s="9">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K16" s="9">
-        <v>23519</v>
+        <v>23529</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M16" s="9">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O16" s="9">
-        <v>125154</v>
+        <v>125157</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="9">
-        <v>75116</v>
+        <v>75015</v>
       </c>
       <c r="D17" s="9">
-        <v>56202</v>
+        <v>56195</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F17" s="9">
-        <v>12818</v>
+        <v>12771</v>
       </c>
       <c r="G17" s="9">
         <v>1189</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I17" s="9">
         <v>144</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K17" s="9">
-        <v>18453</v>
+        <v>18353</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M17" s="9">
         <v>0</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O17" s="9">
-        <v>69020</v>
+        <v>68966</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C18" s="9">
         <v>99169</v>
       </c>
       <c r="D18" s="9">
-        <v>74201</v>
+        <v>74210</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F18" s="9">
         <v>13081</v>
@@ -1816,7 +1822,7 @@
         <v>2425</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I18" s="9">
         <v>54</v>
@@ -1825,48 +1831,48 @@
         <v>54</v>
       </c>
       <c r="K18" s="9">
-        <v>22663</v>
+        <v>22646</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M18" s="9">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O18" s="9">
-        <v>87282</v>
+        <v>87291</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" s="9">
         <v>41772</v>
       </c>
       <c r="D19" s="9">
-        <v>34640</v>
+        <v>34643</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F19" s="9">
-        <v>7919</v>
+        <v>7920</v>
       </c>
       <c r="G19" s="9">
         <v>357</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I19" s="9">
         <v>27</v>
@@ -1875,89 +1881,89 @@
         <v>38</v>
       </c>
       <c r="K19" s="9">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M19" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O19" s="9">
-        <v>42559</v>
+        <v>42563</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20" s="9">
         <v>279478</v>
       </c>
       <c r="D20" s="9">
-        <v>173531</v>
+        <v>173645</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F20" s="9">
-        <v>48579</v>
+        <v>48718</v>
       </c>
       <c r="G20" s="9">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I20" s="9">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="K20" s="9">
-        <v>101435</v>
+        <v>101426</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M20" s="9">
-        <v>1274</v>
+        <v>1629</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O20" s="9">
-        <v>222110</v>
+        <v>222363</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C21" s="9">
         <v>53506</v>
       </c>
       <c r="D21" s="9">
-        <v>40371</v>
+        <v>40368</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F21" s="9">
         <v>7114</v>
@@ -1966,51 +1972,51 @@
         <v>783</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I21" s="9">
         <v>51</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K21" s="9">
-        <v>12751</v>
+        <v>12762</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M21" s="9">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="O21" s="9">
-        <v>47485</v>
+        <v>47482</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="12">
         <v>2730939</v>
       </c>
       <c r="D22" s="12">
-        <v>2048409</v>
+        <v>2048724</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F22" s="12">
-        <v>372141</v>
+        <v>372347</v>
       </c>
       <c r="G22" s="12">
         <v>51223</v>
@@ -2019,25 +2025,25 @@
         <v>37</v>
       </c>
       <c r="I22" s="12">
-        <v>1761</v>
+        <v>1758</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="12">
-        <v>628998</v>
+        <v>629028</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>39</v>
       </c>
       <c r="M22" s="12">
-        <v>5601</v>
+        <v>5956</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="O22" s="12">
-        <v>2420550</v>
+        <v>2421071</v>
       </c>
       <c r="P22" s="13" t="s">
         <v>41</v>
@@ -2066,7 +2072,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2098,25 +2104,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2156,25 +2162,25 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>7286572</v>
+        <v>7287827</v>
       </c>
       <c r="D6" s="6">
-        <v>118351</v>
+        <v>118363</v>
       </c>
       <c r="E6" s="6">
-        <v>77446</v>
+        <v>77459</v>
       </c>
       <c r="F6" s="6">
-        <v>384459</v>
+        <v>384493</v>
       </c>
       <c r="G6" s="6">
-        <v>63214</v>
+        <v>63215</v>
       </c>
       <c r="H6" s="6">
-        <v>9853</v>
+        <v>9854</v>
       </c>
       <c r="I6" s="6">
-        <v>7404923</v>
+        <v>7406190</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2185,7 +2191,7 @@
         <v>43</v>
       </c>
       <c r="C7" s="9">
-        <v>251661</v>
+        <v>251668</v>
       </c>
       <c r="D7" s="9">
         <v>2929</v>
@@ -2203,7 +2209,7 @@
         <v>382</v>
       </c>
       <c r="I7" s="9">
-        <v>254590</v>
+        <v>254597</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2214,7 +2220,7 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>516000</v>
+        <v>516022</v>
       </c>
       <c r="D8" s="9">
         <v>6566</v>
@@ -2232,18 +2238,18 @@
         <v>516</v>
       </c>
       <c r="I8" s="9">
-        <v>522566</v>
+        <v>522588</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="9">
-        <v>950207</v>
+        <v>950453</v>
       </c>
       <c r="D9" s="9">
         <v>15463</v>
@@ -2252,7 +2258,7 @@
         <v>10628</v>
       </c>
       <c r="F9" s="9">
-        <v>45289</v>
+        <v>45293</v>
       </c>
       <c r="G9" s="9">
         <v>5567</v>
@@ -2261,27 +2267,27 @@
         <v>1138</v>
       </c>
       <c r="I9" s="9">
-        <v>965670</v>
+        <v>965916</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="9">
-        <v>911553</v>
+        <v>911660</v>
       </c>
       <c r="D10" s="9">
-        <v>16727</v>
+        <v>16728</v>
       </c>
       <c r="E10" s="9">
-        <v>10690</v>
+        <v>10691</v>
       </c>
       <c r="F10" s="9">
-        <v>44227</v>
+        <v>44228</v>
       </c>
       <c r="G10" s="9">
         <v>22787</v>
@@ -2290,27 +2296,27 @@
         <v>1161</v>
       </c>
       <c r="I10" s="9">
-        <v>928280</v>
+        <v>928388</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" s="9">
-        <v>1144429</v>
+        <v>1144575</v>
       </c>
       <c r="D11" s="9">
-        <v>21640</v>
+        <v>21641</v>
       </c>
       <c r="E11" s="9">
-        <v>13469</v>
+        <v>13474</v>
       </c>
       <c r="F11" s="9">
-        <v>50682</v>
+        <v>50688</v>
       </c>
       <c r="G11" s="9">
         <v>9091</v>
@@ -2319,18 +2325,18 @@
         <v>1874</v>
       </c>
       <c r="I11" s="9">
-        <v>1166069</v>
+        <v>1166216</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="9">
-        <v>519157</v>
+        <v>519179</v>
       </c>
       <c r="D12" s="9">
         <v>6362</v>
@@ -2339,7 +2345,7 @@
         <v>6175</v>
       </c>
       <c r="F12" s="9">
-        <v>29415</v>
+        <v>29418</v>
       </c>
       <c r="G12" s="9">
         <v>2074</v>
@@ -2348,18 +2354,18 @@
         <v>521</v>
       </c>
       <c r="I12" s="9">
-        <v>525519</v>
+        <v>525541</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" s="9">
-        <v>405349</v>
+        <v>405350</v>
       </c>
       <c r="D13" s="9">
         <v>4823</v>
@@ -2368,7 +2374,7 @@
         <v>4534</v>
       </c>
       <c r="F13" s="9">
-        <v>29077</v>
+        <v>29079</v>
       </c>
       <c r="G13" s="9">
         <v>1635</v>
@@ -2377,27 +2383,27 @@
         <v>488</v>
       </c>
       <c r="I13" s="9">
-        <v>410172</v>
+        <v>410173</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" s="9">
-        <v>343202</v>
+        <v>343394</v>
       </c>
       <c r="D14" s="9">
-        <v>9585</v>
+        <v>9590</v>
       </c>
       <c r="E14" s="9">
         <v>3719</v>
       </c>
       <c r="F14" s="9">
-        <v>22763</v>
+        <v>22772</v>
       </c>
       <c r="G14" s="9">
         <v>2252</v>
@@ -2406,47 +2412,47 @@
         <v>392</v>
       </c>
       <c r="I14" s="9">
-        <v>352787</v>
+        <v>352984</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" s="9">
-        <v>417508</v>
+        <v>417530</v>
       </c>
       <c r="D15" s="9">
-        <v>7901</v>
+        <v>7902</v>
       </c>
       <c r="E15" s="9">
-        <v>6753</v>
+        <v>6754</v>
       </c>
       <c r="F15" s="9">
-        <v>28172</v>
+        <v>28174</v>
       </c>
       <c r="G15" s="9">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="H15" s="9">
         <v>517</v>
       </c>
       <c r="I15" s="9">
-        <v>425409</v>
+        <v>425432</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" s="9">
-        <v>370250</v>
+        <v>370254</v>
       </c>
       <c r="D16" s="9">
         <v>5164</v>
@@ -2464,27 +2470,27 @@
         <v>249</v>
       </c>
       <c r="I16" s="9">
-        <v>375414</v>
+        <v>375418</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="9">
-        <v>199922</v>
+        <v>199768</v>
       </c>
       <c r="D17" s="9">
-        <v>4871</v>
+        <v>4867</v>
       </c>
       <c r="E17" s="9">
         <v>2195</v>
       </c>
       <c r="F17" s="9">
-        <v>10362</v>
+        <v>10354</v>
       </c>
       <c r="G17" s="9">
         <v>1728</v>
@@ -2493,47 +2499,47 @@
         <v>398</v>
       </c>
       <c r="I17" s="9">
-        <v>204793</v>
+        <v>204635</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C18" s="9">
-        <v>251821</v>
+        <v>251846</v>
       </c>
       <c r="D18" s="9">
         <v>5494</v>
       </c>
       <c r="E18" s="9">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="F18" s="9">
-        <v>14397</v>
+        <v>14400</v>
       </c>
       <c r="G18" s="9">
         <v>2420</v>
       </c>
       <c r="H18" s="9">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I18" s="9">
-        <v>257315</v>
+        <v>257340</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" s="9">
-        <v>139948</v>
+        <v>139955</v>
       </c>
       <c r="D19" s="9">
         <v>1706</v>
@@ -2542,7 +2548,7 @@
         <v>1062</v>
       </c>
       <c r="F19" s="9">
-        <v>10581</v>
+        <v>10584</v>
       </c>
       <c r="G19" s="9">
         <v>226</v>
@@ -2551,27 +2557,27 @@
         <v>233</v>
       </c>
       <c r="I19" s="9">
-        <v>141654</v>
+        <v>141661</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20" s="9">
-        <v>723335</v>
+        <v>723954</v>
       </c>
       <c r="D20" s="9">
-        <v>7904</v>
+        <v>7913</v>
       </c>
       <c r="E20" s="9">
-        <v>4193</v>
+        <v>4198</v>
       </c>
       <c r="F20" s="9">
-        <v>19975</v>
+        <v>19986</v>
       </c>
       <c r="G20" s="9">
         <v>1259</v>
@@ -2580,27 +2586,27 @@
         <v>716</v>
       </c>
       <c r="I20" s="9">
-        <v>731239</v>
+        <v>731867</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C21" s="9">
-        <v>142230</v>
+        <v>142219</v>
       </c>
       <c r="D21" s="9">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E21" s="9">
         <v>978</v>
       </c>
       <c r="F21" s="9">
-        <v>6000</v>
+        <v>5998</v>
       </c>
       <c r="G21" s="9">
         <v>910</v>
@@ -2609,36 +2615,36 @@
         <v>773</v>
       </c>
       <c r="I21" s="9">
-        <v>143446</v>
+        <v>143434</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="12">
-        <v>7286572</v>
+        <v>7287827</v>
       </c>
       <c r="D22" s="12">
-        <v>118351</v>
+        <v>118363</v>
       </c>
       <c r="E22" s="12">
-        <v>77446</v>
+        <v>77459</v>
       </c>
       <c r="F22" s="12">
-        <v>384459</v>
+        <v>384493</v>
       </c>
       <c r="G22" s="12">
-        <v>63214</v>
+        <v>63215</v>
       </c>
       <c r="H22" s="12">
-        <v>9853</v>
+        <v>9854</v>
       </c>
       <c r="I22" s="12">
-        <v>7404923</v>
+        <v>7406190</v>
       </c>
     </row>
   </sheetData>
@@ -2666,7 +2672,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2692,16 +2698,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2732,13 +2738,13 @@
         <v>35</v>
       </c>
       <c r="C6" s="6">
-        <v>1535</v>
+        <v>1561</v>
       </c>
       <c r="D6" s="6">
-        <v>903</v>
+        <v>1037</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F6" s="6">
         <v>6</v>
@@ -2752,13 +2758,13 @@
         <v>43</v>
       </c>
       <c r="C7" s="9">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D7" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F7" s="9">
         <v>0</v>
@@ -2772,13 +2778,13 @@
         <v>51</v>
       </c>
       <c r="C8" s="9">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="D8" s="9">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F8" s="9">
         <v>1</v>
@@ -2786,19 +2792,19 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="9">
         <v>193</v>
       </c>
       <c r="D9" s="9">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F9" s="9">
         <v>1</v>
@@ -2806,19 +2812,19 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="9">
         <v>161</v>
       </c>
       <c r="D10" s="9">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -2826,19 +2832,19 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" s="9">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D11" s="9">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
@@ -2846,19 +2852,19 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="9">
         <v>75</v>
       </c>
       <c r="D12" s="9">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F12" s="9">
         <v>1</v>
@@ -2866,19 +2872,19 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" s="9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" s="9">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
@@ -2886,19 +2892,19 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" s="9">
         <v>100</v>
       </c>
       <c r="D14" s="9">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -2906,19 +2912,19 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" s="9">
         <v>150</v>
       </c>
       <c r="D15" s="9">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F15" s="9">
         <v>1</v>
@@ -2926,19 +2932,19 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" s="9">
         <v>81</v>
       </c>
       <c r="D16" s="9">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
@@ -2946,10 +2952,10 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="9">
         <v>30</v>
@@ -2958,7 +2964,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F17" s="9">
         <v>1</v>
@@ -2966,10 +2972,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C18" s="9">
         <v>62</v>
@@ -2978,7 +2984,7 @@
         <v>62</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
@@ -2986,19 +2992,19 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" s="9">
         <v>21</v>
       </c>
       <c r="D19" s="9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F19" s="9">
         <v>1</v>
@@ -3006,19 +3012,19 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20" s="9">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D20" s="9">
         <v>27</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -3026,19 +3032,19 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C21" s="9">
         <v>75</v>
       </c>
       <c r="D21" s="9">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F21" s="9">
         <v>0</v>
@@ -3046,19 +3052,19 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="12">
-        <v>1535</v>
+        <v>1561</v>
       </c>
       <c r="D22" s="12">
-        <v>903</v>
+        <v>1037</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F22" s="12">
         <v>6</v>
